--- a/banks/VIDA FINANCIALS.xlsx
+++ b/banks/VIDA FINANCIALS.xlsx
@@ -1,25 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cash Flow Statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CET1 Capital" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CET1 Ratio" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Tier 1 Capital" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Tier 1 Ratio" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Total Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Total Capital Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Total RWAs" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Leverage Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="LCR" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="NSFR" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="MREL Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -192,18 +197,18 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Vida Bank Limited — Cash Flow Summary by Year</a:t>
+              <a:t>Vida Bank Limited — Balance Sheet Summary by Year</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -235,7 +240,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -259,7 +264,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -283,7 +288,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -307,7 +312,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -350,8 +355,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -390,13 +395,583 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Vida Bank Limited — Profit &amp; Loss Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$13:$V$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$14:$V$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$15:$V$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£'000</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Vida Bank Limited — Statement of Changes in Equity Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$19:$AD$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y20</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$20:$AD$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$21:$AD$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y22</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$22:$AD$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£'000</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Vida Bank Limited — Cash Flow Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG26</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$26:$AL$26</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG27</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$27:$AL$27</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG28</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$28:$AL$28</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG29</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$29:$AL$29</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£'000</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -428,30 +1003,30 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q6</f>
+              <f>'Overview'!AO6</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$6:$V$6</f>
+              <f>'Overview'!$AP$6:$AT$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -461,30 +1036,30 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q7</f>
+              <f>'Overview'!AO7</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$7:$V$7</f>
+              <f>'Overview'!$AP$7:$AT$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -494,30 +1069,30 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q8</f>
+              <f>'Overview'!AO8</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$8:$V$8</f>
+              <f>'Overview'!$AP$8:$AT$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -527,30 +1102,30 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q9</f>
+              <f>'Overview'!AO9</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$9:$V$9</f>
+              <f>'Overview'!$AP$9:$AT$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -560,30 +1135,30 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q10</f>
+              <f>'Overview'!AO10</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$10:$V$10</f>
+              <f>'Overview'!$AP$10:$AT$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -593,30 +1168,30 @@
           <order val="5"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q11</f>
+              <f>'Overview'!AO11</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$11:$V$11</f>
+              <f>'Overview'!$AP$11:$AT$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -648,8 +1223,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -688,12 +1263,12 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="4680000"/>
@@ -703,9 +1278,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -715,19 +1290,85 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>64</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="5760000"/>
+    <ext cx="8640000" cy="4680000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>86</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>108</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>130</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="5760000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1025,7 +1666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:AT40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1048,6 +1689,30 @@
     <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
     <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
     <col hidden="1" width="13" customWidth="1" min="22" max="22"/>
+    <col hidden="1" width="13" customWidth="1" min="23" max="23"/>
+    <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
+    <col hidden="1" width="13" customWidth="1" min="25" max="25"/>
+    <col hidden="1" width="13" customWidth="1" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" min="28" max="28"/>
+    <col hidden="1" width="13" customWidth="1" min="29" max="29"/>
+    <col hidden="1" width="13" customWidth="1" min="30" max="30"/>
+    <col hidden="1" width="13" customWidth="1" min="31" max="31"/>
+    <col hidden="1" width="13" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="13" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="13" customWidth="1" min="34" max="34"/>
+    <col hidden="1" width="13" customWidth="1" min="35" max="35"/>
+    <col hidden="1" width="13" customWidth="1" min="36" max="36"/>
+    <col hidden="1" width="13" customWidth="1" min="37" max="37"/>
+    <col hidden="1" width="13" customWidth="1" min="38" max="38"/>
+    <col hidden="1" width="13" customWidth="1" min="39" max="39"/>
+    <col hidden="1" width="13" customWidth="1" min="40" max="40"/>
+    <col hidden="1" width="13" customWidth="1" min="41" max="41"/>
+    <col hidden="1" width="13" customWidth="1" min="42" max="42"/>
+    <col hidden="1" width="13" customWidth="1" min="43" max="43"/>
+    <col hidden="1" width="13" customWidth="1" min="44" max="44"/>
+    <col hidden="1" width="13" customWidth="1" min="45" max="45"/>
+    <col hidden="1" width="13" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1060,14 +1725,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Summary of cash flow and Pillar 3 disclosures across all years covered in this workbook</t>
+          <t>Headline balance sheet, profit &amp; loss, cash flow and Pillar 3 figures across all years covered in this workbook - how the bank is using its money and the risk it is taking with it</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Cash Flow Summary (£'000)</t>
+          <t>Balance Sheet Summary (£'000)</t>
         </is>
       </c>
     </row>
@@ -1127,27 +1792,27 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AT5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -1156,223 +1821,228 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>1766849</v>
+        <v>3476346</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>70662</v>
+        <v>2079467</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>65493</v>
-      </c>
-      <c r="E6" s="5" t="n"/>
+        <v>1780102</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1809020</v>
+      </c>
       <c r="F6" s="5" t="n">
-        <v>-179449</v>
+        <v>1854266</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>-179449</v>
+        <v>1854266</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1809020</v>
       </c>
       <c r="L6" t="n">
-        <v>65493</v>
+        <v>1780102</v>
       </c>
       <c r="M6" t="n">
-        <v>70662</v>
+        <v>2079467</v>
       </c>
       <c r="N6" t="n">
-        <v>1766849</v>
-      </c>
-      <c r="Q6" t="inlineStr">
+        <v>3476346</v>
+      </c>
+      <c r="AO6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="U6" t="n">
+      <c r="AS6" t="n">
         <v>16.2</v>
       </c>
-      <c r="V6" t="n">
+      <c r="AT6" t="n">
         <v>15.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) investing activities</t>
+          <t>Loans to customers</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>-104</v>
+        <v>2301831</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-408</v>
+        <v>1866006</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-698</v>
-      </c>
-      <c r="E7" s="5" t="n"/>
+        <v>1712271</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1761996</v>
+      </c>
       <c r="F7" s="5" t="n">
-        <v>-1757</v>
+        <v>1811577</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) investing activities</t>
+          <t>Loans to customers</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>-1757</v>
+        <v>1811577</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1761996</v>
       </c>
       <c r="L7" t="n">
-        <v>-698</v>
+        <v>1712271</v>
       </c>
       <c r="M7" t="n">
-        <v>-408</v>
+        <v>1866006</v>
       </c>
       <c r="N7" t="n">
-        <v>-104</v>
-      </c>
-      <c r="Q7" t="inlineStr">
+        <v>2301831</v>
+      </c>
+      <c r="AO7" t="inlineStr">
         <is>
           <t>Tier 1 Ratio</t>
         </is>
       </c>
-      <c r="U7" t="n">
+      <c r="AS7" t="n">
         <v>16.2</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AT7" t="n">
         <v>15.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) financing activities</t>
+          <t>Retail deposits</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>-1655356</v>
+        <v>2425702</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>56070</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>-62554</v>
-      </c>
+        <v>173113</v>
+      </c>
+      <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n">
-        <v>176598</v>
-      </c>
+      <c r="F8" s="5" t="n"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) financing activities</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>176598</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-62554</v>
+          <t>Retail deposits</t>
+        </is>
       </c>
       <c r="M8" t="n">
-        <v>56070</v>
+        <v>173113</v>
       </c>
       <c r="N8" t="n">
-        <v>-1655356</v>
-      </c>
-      <c r="Q8" t="inlineStr">
+        <v>2425702</v>
+      </c>
+      <c r="AO8" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="U8" t="n">
+      <c r="AS8" t="n">
         <v>16.2</v>
       </c>
-      <c r="V8" t="n">
+      <c r="AT8" t="n">
         <v>18.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at end of year</t>
+          <t>Total shareholders' equity</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>254874</v>
+        <v>177779</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>143485</v>
+        <v>165080</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>17161</v>
-      </c>
-      <c r="E9" s="5" t="n"/>
+        <v>122069</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>131006</v>
+      </c>
       <c r="F9" s="5" t="n">
-        <v>13500</v>
+        <v>126641</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at end of year</t>
+          <t>Total shareholders' equity</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13500</v>
+        <v>126641</v>
+      </c>
+      <c r="K9" t="n">
+        <v>131006</v>
       </c>
       <c r="L9" t="n">
-        <v>17161</v>
+        <v>122069</v>
       </c>
       <c r="M9" t="n">
-        <v>143485</v>
+        <v>165080</v>
       </c>
       <c r="N9" t="n">
-        <v>254874</v>
-      </c>
-      <c r="Q9" t="inlineStr">
+        <v>177779</v>
+      </c>
+      <c r="AO9" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="U9" t="n">
+      <c r="AS9" t="n">
         <v>6.9</v>
       </c>
-      <c r="V9" t="n">
+      <c r="AT9" t="n">
         <v>4.9</v>
       </c>
     </row>
     <row r="10">
-      <c r="Q10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="U10" t="n">
+      <c r="AS10" t="n">
         <v>1045</v>
       </c>
-      <c r="V10" t="n">
+      <c r="AT10" t="n">
         <v>163</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Pillar 3 Key Metrics</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+          <t>Profit &amp; Loss Summary (£'000)</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
-      <c r="U11" t="n">
+      <c r="AS11" t="n">
         <v>110</v>
       </c>
-      <c r="V11" t="n">
+      <c r="AT11" t="n">
         <v>138</v>
       </c>
     </row>
@@ -1407,129 +2077,763 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Net operating income</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>57655</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>41023</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>38536</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>36024</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>34088</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Net operating income</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>34088</v>
+      </c>
+      <c r="S13" t="n">
+        <v>36024</v>
+      </c>
+      <c r="T13" t="n">
+        <v>38536</v>
+      </c>
+      <c r="U13" t="n">
+        <v>41023</v>
+      </c>
+      <c r="V13" t="n">
+        <v>57655</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Administrative expenses</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>-42450</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-34231</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-32438</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-35502</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-30932</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Administrative expenses</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>-30932</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-35502</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-32438</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-34231</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-42450</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>13097</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>6434</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>6068</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1984</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>4659</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>4659</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1984</v>
+      </c>
+      <c r="T15" t="n">
+        <v>6068</v>
+      </c>
+      <c r="U15" t="n">
+        <v>6434</v>
+      </c>
+      <c r="V15" t="n">
+        <v>13097</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Statement of Changes in Equity Summary (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Opening equity</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>165080</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>122070</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>131006</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>126641</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>124246</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Opening equity</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>124246</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>126641</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>131006</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>122070</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>165080</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income/(loss) for the year</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>12699</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>6434</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-8937</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-5905</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Total comprehensive income/(loss) for the year</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>-5905</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4365</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-8937</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>6434</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>12699</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Other equity movements, net</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>36576</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Other equity movements, net</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>8300</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>36576</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Closing equity</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>177779</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>165080</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>122069</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>131006</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>126641</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Closing equity</t>
+        </is>
+      </c>
+      <c r="Z22" t="n">
+        <v>126641</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>131006</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>122069</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>165080</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>177779</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Cash Flow Summary (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) operating activities</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>1766849</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>70662</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>65493</v>
+      </c>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n">
+        <v>-179449</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) operating activities</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>-179449</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>65493</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>70662</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1766849</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) investing activities</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>-104</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>-408</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>-698</v>
+      </c>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n">
+        <v>-1757</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) investing activities</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>-1757</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>-698</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>-408</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>-104</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) financing activities</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>-1655356</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>56070</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-62554</v>
+      </c>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n">
+        <v>176598</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) financing activities</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>176598</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>-62554</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>56070</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>-1655356</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at end of year</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>254874</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>143485</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>17161</v>
+      </c>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n">
+        <v>13500</v>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at end of year</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>13500</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>17161</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>143485</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>254874</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Pillar 3 Key Metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>15.2%</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>16.2%</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Tier 1 Ratio</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>15.2%</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>16.2%</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>18.3%</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>16.2%</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>4.9%</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>6.9%</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>163%</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>1,045%</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>138%</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>110%</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-    </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="6" t="n"/>
+    </row>
+    <row r="40" ht="45" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. FY2022 cash flow and FY2021-FY2023 Pillar 3 are blank - Vida only became a PRA-authorised bank on 19 November 2024 (no Pillar 3 exists before then), and FY2022's own Annual Report doesn't present a full cash flow statement on a basis comparable to other years - see the Cash Flow Statement sheet's source note for details.</t>
         </is>
@@ -1537,7 +2841,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A40:F40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1545,6 +2849,107 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Vida Bank Limited — Tier 1 Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Vida Group Holdings basis, % of RWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>16.2%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="6" ht="130" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
+FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
+FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
+No Pillar 3 disclosure exists for FY2021-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1564,6 +2969,419 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Vida Bank Limited — Total Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Vida Group Holdings basis, £'000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>202429</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>160316</v>
+      </c>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2025 total capital exceeds Tier 1 capital because the Group issued £35m of qualifying Tier 2 capital during the year to support planned balance sheet expansion; FY2024 had no Tier 2 capital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="130" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
+FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
+FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
+No Pillar 3 disclosure exists for FY2021-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Vida Bank Limited — Total Capital Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Vida Group Holdings basis, % of RWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>18.3%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>16.2%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="6" ht="130" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
+FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
+FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
+No Pillar 3 disclosure exists for FY2021-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Vida Bank Limited — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Vida Group Holdings basis, £'000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1105780</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>986809</v>
+      </c>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="6" ht="130" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
+FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
+FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
+No Pillar 3 disclosure exists for FY2021-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Vida Bank Limited — RWA Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Vida Group Holdings basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>RWA Breakdown</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="120" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>No UK OV1 (RWA-by-risk-category) template, or equivalent RWA breakdown table, exists in either Pillar 3 Disclosures document (2025 or 2024) checked this session - both are short (9-page) documents covering only the KM1 Key Metrics table already used on the other Pillar 3 sheets. Confirmed non-disclosure, not an access gap. No Pillar 3 disclosure exists at all for FY2021-FY2023 (see ENTITY_NOTE on the Cash Flow Statement sheet).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
           <t>Vida Bank Limited — Leverage Ratio</t>
         </is>
       </c>
@@ -1661,7 +3479,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1802,7 +3620,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1935,7 +3753,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2062,6 +3880,1429 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Vida Bank Limited — Company Statement of Financial Position</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Company (non-consolidated) basis, £'000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>254874</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>143485</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>17161</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>14919</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>13500</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Debt securities</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>819770</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>34135</v>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Loans to customers</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>2301831</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>1866006</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>1712271</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1761996</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>1811577</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial instruments</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>10198</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>2123</v>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n">
+        <v>731</v>
+      </c>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Other receivables</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>71715</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>16412</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>34000</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>13982</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>11399</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Deferred taxation asset</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>15299</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>13565</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>13565</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>13565</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>12975</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Investment in subsidiaries</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>1343</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>1551</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>401</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>965</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>2407</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Intangible assets</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>1316</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>2190</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>2704</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>2837</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Corporation tax</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>3476346</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2079467</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1780102</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1809020</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1854266</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Retail deposits</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>2425702</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>173113</v>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Amounts owed to credit institutions</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>40345</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>74254</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>44437</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>15188</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>15336</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Deemed loan due to Group undertakings</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>767720</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>1659540</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>1544083</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>1606178</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>1690865</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial liabilities</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>19403</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>184</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>4727</v>
+      </c>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Other liabilities</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>44269</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>7067</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>64722</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>56584</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>21050</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Provisions</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Corporation tax</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>1128</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>229</v>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>3298567</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1914387</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1658033</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1678014</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>1727625</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Shareholders' equity</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Called up share capital</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>36156</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>241039</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>204462</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>204462</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>204462</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Other reserves</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>-398</v>
+      </c>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Retained profit/(losses)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>142021</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>-75959</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>-82393</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>-73456</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>-77821</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Total shareholders' equity</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>177779</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>165080</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>122069</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>131006</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>126641</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities and equity</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>3476346</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>2079467</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>1780102</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>1809020</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>1854266</v>
+      </c>
+    </row>
+    <row r="32" ht="180" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Vida Bank Limited's own Company (non-consolidated) Statement of Financial Position, £'000:
+FY2025: Vida Bank Limited Annual Report and Accounts 2025 (Company), p.53 - https://www.vidabank.co.uk/media/pkmnxlqg/annual-report-and-accounts-2025-company.pdf
+FY2024: Vida Bank Limited Annual Report and Accounts 2024 (Company), p.71 - https://www.vidabank.co.uk/media/emghy4z2/annual-report-and-accounts-2024-company.pdf
+FY2023: Belmont Green Finance Limited Annual Report and Accounts 2023, p.185 (Company Statement of Financial Position) - https://www.vidabank.co.uk/media/zhoj0swe/annual-report-and-accounts-2023.pdf
+FY2022: taken from the FY2023 Annual Report's own restated FY2022 comparative column (same document/page as above) - Belmont Green's own FY2022 Annual Report was not fetched this session.
+FY2021: Belmont Green Finance Limited Annual Report and Accounts 2021, p.149 (Company Statement of Financial Position) - https://www.vidabank.co.uk/media/p3wau0ms/annual-report-and-accounts-2021.pdf
+Balance Sheet / Statement of Changes in Equity are on Vida Bank Limited's own Company (non-consolidated) basis in every year, matching the Cash Flow Statement sheet's basis (see its own ENTITY_NOTE). Profit &amp; Loss is on the Company basis for FY2025/FY2024 only (Vida's own Company Statement of Comprehensive Income exists for those two years); for FY2023/FY2022/FY2021, the Company took the section 408 Companies Act 2006 exemption and published no separate Company income statement (only a one-line narrative profit/loss-after-tax figure, which ties to the equity ladder's own movement for that year), so the Group/Consolidated income statement is shown instead for those 3 years - a genuine basis difference, not forced to a single basis.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A32:F32"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="64" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Vida Bank Limited — Statement of Comprehensive Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>FY2025/FY2024: Company basis. FY2023-FY2021: Group/Consolidated basis (Company P&amp;L exempted under s.408). £'000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Interest income and similar income</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>171518</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>121718</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>144373</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>99941</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>68551</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Interest expense and similar charges</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>-124229</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>-87898</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>-110660</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>-57037</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>-34046</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Net interest income</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>47289</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>33820</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>33713</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>42904</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>34505</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Other operating income/(expense)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>7035</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>1158</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>920</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-6174</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Net fair value gain/(loss) on financial instruments</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>3331</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>6045</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>3903</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>-706</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-1404</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Net operating income</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>57655</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>41023</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>38536</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>36024</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>34088</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Administrative expenses</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>-42450</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>-34231</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>-32438</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>-35502</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-30932</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Operating profit before impairment</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>15205</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>6792</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>6098</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>522</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3156</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Provisions</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>310</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Impairment (losses)/releases</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>-2736</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>-128</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-55</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>543</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-725</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Profit before taxation</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>12469</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>6664</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>6043</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1375</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2654</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Tax credit/(charge) for the year</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>628</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>-230</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>609</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>13097</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>6434</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>6068</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>1984</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>4659</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedge reserve (losses)/gains</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>-21</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-10468</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>16864</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Tax on items in other comprehensive income</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>-98</v>
+      </c>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Fair value through OCI reserve</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>-279</v>
+      </c>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income/(loss) for the year, net of tax</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>12699</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>6434</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-4400</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>18848</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>4659</v>
+      </c>
+    </row>
+    <row r="24" ht="260" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Sources - £'000. FY2025/FY2024: Vida Bank Limited's own Company Statement of Comprehensive Income. FY2023/FY2022/FY2021: Group/Consolidated Statement of Profit and Loss and Other Comprehensive Income (Company P&amp;L exempted under s.408, see ENTITY_NOTE below):
+FY2025: Vida Bank Limited Annual Report and Accounts 2025 (Company), p.52 - https://www.vidabank.co.uk/media/pkmnxlqg/annual-report-and-accounts-2025-company.pdf
+FY2024: Vida Bank Limited Annual Report and Accounts 2025 (Company), p.52, FY2024 comparative column - https://www.vidabank.co.uk/media/pkmnxlqg/annual-report-and-accounts-2025-company.pdf
+FY2023: Belmont Green Finance Limited Annual Report and Accounts 2023, p.143 (Consolidated Statement of Profit and Loss and Other Comprehensive Income) - https://www.vidabank.co.uk/media/zhoj0swe/annual-report-and-accounts-2023.pdf
+FY2022: taken from the FY2023 Annual Report's own FY2022 comparative column (same document/page as above).
+FY2021: Belmont Green Finance Limited Annual Report and Accounts 2021, p.109 (Consolidated Statement of Comprehensive Income) - https://www.vidabank.co.uk/media/p3wau0ms/annual-report-and-accounts-2021.pdf
+Presentation notes (not silently reconciled): FY2021's Group statement labels its operating-income subtotal "Total income" rather than FY2022-25's "Net operating income" - same position in the statement, different label, reproduced as printed. FY2025's own Statement of Comprehensive Income prints its final row as "Total other comprehensive profit" with a value of 12,699 - this is actually the year's Total comprehensive income (Profit after tax 13,097 less the 3 OCI items above it, -21-98-279=-398, gives exactly 12,699); the source's own row label is internally inconsistent (a subtotal, not "other" comprehensive income), so this row is relabelled "Total comprehensive income for the year, net of tax" here to match the other 4 years' own correctly-labelled totals - the £'000 value itself is reproduced exactly as printed, unchanged.
+Balance Sheet / Statement of Changes in Equity are on Vida Bank Limited's own Company (non-consolidated) basis in every year, matching the Cash Flow Statement sheet's basis (see its own ENTITY_NOTE). Profit &amp; Loss is on the Company basis for FY2025/FY2024 only (Vida's own Company Statement of Comprehensive Income exists for those two years); for FY2023/FY2022/FY2021, the Company took the section 408 Companies Act 2006 exemption and published no separate Company income statement (only a one-line narrative profit/loss-after-tax figure, which ties to the equity ladder's own movement for that year), so the Group/Consolidated income statement is shown instead for those 3 years - a genuine basis difference, not forced to a single basis.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A24:F24"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Vida Bank Limited — Company Statement of Changes in Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Company (non-consolidated) basis, £'000. Chronological, oldest to newest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Called up share capital</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Other reserves</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Balance at 1 January 2021</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>196162</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>-71916</v>
+      </c>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n">
+        <v>124246</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Share issuance</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>8300</v>
+      </c>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n">
+        <v>-5905</v>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n">
+        <v>-5905</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Balance at 31 December 2021</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>204462</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>-77821</v>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n">
+        <v>126641</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n">
+        <v>4365</v>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n">
+        <v>4365</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Balance at 31 December 2022</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>204462</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>-73456</v>
+      </c>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n">
+        <v>131006</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n">
+        <v>-8937</v>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n">
+        <v>-8937</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Balance at 31 December 2023</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>204462</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-82393</v>
+      </c>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n">
+        <v>122069</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Balance at 1 January 2024 (per FY2024 Annual Report - see source note)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>204463</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-82393</v>
+      </c>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n">
+        <v>122070</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n">
+        <v>6434</v>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n">
+        <v>6434</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Share issuance</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>36576</v>
+      </c>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n">
+        <v>36576</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Balance at 31 December 2024</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>241039</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>-75959</v>
+      </c>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n">
+        <v>165080</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n">
+        <v>13097</v>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n">
+        <v>13097</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax on Gilts</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n">
+        <v>-98</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>-98</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Fair value through OCI reserve</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n">
+        <v>-279</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>-279</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Amounts deferred to cash flow hedge reserve, net of tax</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n">
+        <v>-21</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-21</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Share capital reallocation</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>-204883</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>204883</v>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Balance at 31 December 2025</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>36156</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>142021</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>-398</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>177779</v>
+      </c>
+    </row>
+    <row r="23" ht="260" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Vida Bank Limited's own Company (non-consolidated) Statement of Changes in Equity, £'000:
+FY2021 boundary (1 Jan 2021 opening, FY2021 movements, 31 Dec 2021 closing): Belmont Green Finance Limited Annual Report and Accounts 2021, p.150 - https://www.vidabank.co.uk/media/p3wau0ms/annual-report-and-accounts-2021.pdf
+FY2022 boundary: Belmont Green Finance Limited Annual Report and Accounts 2023, p.184 (FY2022 comparative rows) - https://www.vidabank.co.uk/media/zhoj0swe/annual-report-and-accounts-2023.pdf
+FY2023 boundary: same document, p.184 - https://www.vidabank.co.uk/media/zhoj0swe/annual-report-and-accounts-2023.pdf
+FY2024 boundary: Vida Bank Limited Annual Report and Accounts 2024, p.72 - https://www.vidabank.co.uk/media/emghy4z2/annual-report-and-accounts-2024-company.pdf
+FY2025 boundary: Vida Bank Limited Annual Report and Accounts 2025 (Company), p.54 - https://www.vidabank.co.uk/media/pkmnxlqg/annual-report-and-accounts-2025-company.pdf
+Discrepancy flagged, not forced to tie: the FY2024 Annual Report's own opening balance at 1 January 2024 (share capital 204,463 / total equity 122,070) differs by £1k from the FY2023 Annual Report's own closing balance at 31 December 2023 (share capital 204,462 / total equity 122,069) - a genuine £1k rounding artefact between the two source documents, each reproduced exactly as its own report states.
+The FY2025 Statement of Changes in Equity's own "Total comprehensive income" subtotal row is omitted from this ladder: it prints running balances (not that year's movement) in its Retained earnings and Total columns - see the Profit &amp; Loss sheet's own source note for the same issue on that sheet. Every individual movement row above it (Profit for the year, Deferred tax on Gilts, Fair value through OCI reserve, Amounts deferred to cash flow hedge reserve) is reproduced in full and the ladder ties exactly without it.
+Balance Sheet / Statement of Changes in Equity are on Vida Bank Limited's own Company (non-consolidated) basis in every year, matching the Cash Flow Statement sheet's basis (see its own ENTITY_NOTE). Profit &amp; Loss is on the Company basis for FY2025/FY2024 only (Vida's own Company Statement of Comprehensive Income exists for those two years); for FY2023/FY2022/FY2021, the Company took the section 408 Companies Act 2006 exemption and published no separate Company income statement (only a one-line narrative profit/loss-after-tax figure, which ties to the equity ladder's own movement for that year), so the Group/Consolidated income statement is shown instead for those 3 years - a genuine basis difference, not forced to a single basis.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A23:E23"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2452,7 +5693,365 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="64" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Vida Bank Limited — Asset Quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Group/Consolidated basis (see source note), £'000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Gross loans to customers by IFRS 9 stage</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Stage 1 (performing)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>1915462</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1463371</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1254493</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1041635</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>1124656</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Stage 2 (underperforming)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>321347</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>330053</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>392712</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>662983</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>643597</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 (non-performing)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>65403</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>63782</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>51849</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>45129</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>44090</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Total gross loans to customers</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>2302212</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1857206</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1699054</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1749747</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>1812343</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Impairment provision (ECL) by IFRS 9 stage</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Stage 1 provision</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>1671</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>1053</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>647</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Stage 2 provision</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>1555</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>1341</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>1885</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>3443</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>3889</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 provision</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>3865</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>2480</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>2599</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>1835</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>2541</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Total impairment provision</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>7091</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>4874</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>5589</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>5925</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>7647</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Derived ratios</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>NPL ratio (Stage 3 / Total gross loans)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>2.84%</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>3.43%</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>3.05%</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>2.58%</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>2.43%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 coverage ratio (Stage 3 provision / Stage 3 gross)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>3.89%</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>5.01%</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>4.07%</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>5.77%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="200" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Vida Bank Limited's own IFRS 9 stage disclosure (Note 13/14, "Expected credit losses"), £'000, on a Group/Consolidated basis (the only basis at which this note is disclosed in every source document; gross/net loan totals below therefore don't tie exactly to the Balance Sheet sheet's Company-basis "Loans to customers" line - a genuine basis difference, documented not blended):
+FY2025/FY2024: Vida Bank Limited Annual Report and Accounts 2025, p.79-81 (Note 14, Expected credit losses) - https://www.vidabank.co.uk/media/pkmnxlqg/annual-report-and-accounts-2025-company.pdf
+FY2023/FY2022: Belmont Green Finance Limited Annual Report and Accounts 2023, p.168-169 (Note 14, Expected credit losses) - https://www.vidabank.co.uk/media/zhoj0swe/annual-report-and-accounts-2023.pdf
+FY2021: Belmont Green Finance Limited Annual Report and Accounts 2021, p.132-133 (Note 13, Expected credit losses) - https://www.vidabank.co.uk/media/p3wau0ms/annual-report-and-accounts-2021.pdf
+NPL ratio = Stage 3 gross balance / Total gross balance. Coverage ratio = Stage 3 impairment provision / Stage 3 gross balance. Both derived, not separately disclosed by the Bank.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A18:F18"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2544,418 +6143,6 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Vida Bank Limited — CET1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Vida Group Holdings basis, % of RWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>16.2%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-    </row>
-    <row r="6" ht="130" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
-FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
-FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-No Pillar 3 disclosure exists for FY2021-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Vida Bank Limited — Tier 1 Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Vida Group Holdings basis, £'000</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>168319</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>160316</v>
-      </c>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: Equal to CET1 capital in both years - Vida has no Additional Tier 1 (AT1) instruments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="130" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
-FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
-FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-No Pillar 3 disclosure exists for FY2021-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Vida Bank Limited — Tier 1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Vida Group Holdings basis, % of RWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>16.2%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-    </row>
-    <row r="6" ht="130" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
-FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
-FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-No Pillar 3 disclosure exists for FY2021-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Vida Bank Limited — Total Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Vida Group Holdings basis, £'000</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Total capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>202429</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>160316</v>
-      </c>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2025 total capital exceeds Tier 1 capital because the Group issued £35m of qualifying Tier 2 capital during the year to support planned balance sheet expansion; FY2024 had no Tier 2 capital.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="130" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
-FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
-FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-No Pillar 3 disclosure exists for FY2021-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2981,7 +6168,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Vida Bank Limited — Total Capital Ratio</t>
+          <t>Vida Bank Limited — CET1 Ratio</t>
         </is>
       </c>
     </row>
@@ -3027,12 +6214,12 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
+          <t>Common Equity Tier 1 (CET1) ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -3068,7 +6255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3082,7 +6269,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Vida Bank Limited — Total RWAs</t>
+          <t>Vida Bank Limited — Tier 1 Capital</t>
         </is>
       </c>
     </row>
@@ -3128,21 +6315,28 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk-weighted exposure amount</t>
+          <t>Tier 1 capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>1105780</v>
+        <v>168319</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>986809</v>
+        <v>160316</v>
       </c>
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
-    <row r="6" ht="130" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: Equal to CET1 capital in both years - Vida has no Additional Tier 1 (AT1) instruments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="130" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
 FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
@@ -3152,8 +6346,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/VIDA FINANCIALS.xlsx
+++ b/banks/VIDA FINANCIALS.xlsx
@@ -236,7 +236,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!I6</f>
+              <f>'Overview'!L6</f>
             </strRef>
           </tx>
           <spPr>
@@ -246,12 +246,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$J$5:$N$5</f>
+              <f>'Overview'!$M$5:$T$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$J$6:$N$6</f>
+              <f>'Overview'!$M$6:$T$6</f>
             </numRef>
           </val>
         </ser>
@@ -260,7 +260,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!I7</f>
+              <f>'Overview'!L7</f>
             </strRef>
           </tx>
           <spPr>
@@ -270,12 +270,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$J$5:$N$5</f>
+              <f>'Overview'!$M$5:$T$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$J$7:$N$7</f>
+              <f>'Overview'!$M$7:$T$7</f>
             </numRef>
           </val>
         </ser>
@@ -284,7 +284,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!I8</f>
+              <f>'Overview'!L8</f>
             </strRef>
           </tx>
           <spPr>
@@ -294,12 +294,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$J$5:$N$5</f>
+              <f>'Overview'!$M$5:$T$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$J$8:$N$8</f>
+              <f>'Overview'!$M$8:$T$8</f>
             </numRef>
           </val>
         </ser>
@@ -308,7 +308,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!I9</f>
+              <f>'Overview'!L9</f>
             </strRef>
           </tx>
           <spPr>
@@ -318,12 +318,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$J$5:$N$5</f>
+              <f>'Overview'!$M$5:$T$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$J$9:$N$9</f>
+              <f>'Overview'!$M$9:$T$9</f>
             </numRef>
           </val>
         </ser>
@@ -434,7 +434,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q13</f>
+              <f>'Overview'!W13</f>
             </strRef>
           </tx>
           <spPr>
@@ -444,12 +444,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$R$12:$V$12</f>
+              <f>'Overview'!$X$12:$AE$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$13:$V$13</f>
+              <f>'Overview'!$X$13:$AE$13</f>
             </numRef>
           </val>
         </ser>
@@ -458,7 +458,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q14</f>
+              <f>'Overview'!W14</f>
             </strRef>
           </tx>
           <spPr>
@@ -468,12 +468,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$R$12:$V$12</f>
+              <f>'Overview'!$X$12:$AE$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$14:$V$14</f>
+              <f>'Overview'!$X$14:$AE$14</f>
             </numRef>
           </val>
         </ser>
@@ -482,7 +482,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q15</f>
+              <f>'Overview'!W15</f>
             </strRef>
           </tx>
           <spPr>
@@ -492,12 +492,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$R$12:$V$12</f>
+              <f>'Overview'!$X$12:$AE$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$15:$V$15</f>
+              <f>'Overview'!$X$15:$AE$15</f>
             </numRef>
           </val>
         </ser>
@@ -608,7 +608,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Y19</f>
+              <f>'Overview'!AH19</f>
             </strRef>
           </tx>
           <spPr>
@@ -618,12 +618,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$Z$18:$AD$18</f>
+              <f>'Overview'!$AI$18:$AP$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$Z$19:$AD$19</f>
+              <f>'Overview'!$AI$19:$AP$19</f>
             </numRef>
           </val>
         </ser>
@@ -632,7 +632,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!Y20</f>
+              <f>'Overview'!AH20</f>
             </strRef>
           </tx>
           <spPr>
@@ -642,12 +642,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$Z$18:$AD$18</f>
+              <f>'Overview'!$AI$18:$AP$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$Z$20:$AD$20</f>
+              <f>'Overview'!$AI$20:$AP$20</f>
             </numRef>
           </val>
         </ser>
@@ -656,7 +656,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!Y21</f>
+              <f>'Overview'!AH21</f>
             </strRef>
           </tx>
           <spPr>
@@ -666,12 +666,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$Z$18:$AD$18</f>
+              <f>'Overview'!$AI$18:$AP$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$Z$21:$AD$21</f>
+              <f>'Overview'!$AI$21:$AP$21</f>
             </numRef>
           </val>
         </ser>
@@ -680,7 +680,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!Y22</f>
+              <f>'Overview'!AH22</f>
             </strRef>
           </tx>
           <spPr>
@@ -690,12 +690,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$Z$18:$AD$18</f>
+              <f>'Overview'!$AI$18:$AP$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$Z$22:$AD$22</f>
+              <f>'Overview'!$AI$22:$AP$22</f>
             </numRef>
           </val>
         </ser>
@@ -806,7 +806,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!AG26</f>
+              <f>'Overview'!AS26</f>
             </strRef>
           </tx>
           <spPr>
@@ -816,12 +816,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AH$25:$AL$25</f>
+              <f>'Overview'!$AT$25:$BA$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AH$26:$AL$26</f>
+              <f>'Overview'!$AT$26:$BA$26</f>
             </numRef>
           </val>
         </ser>
@@ -830,7 +830,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!AG27</f>
+              <f>'Overview'!AS27</f>
             </strRef>
           </tx>
           <spPr>
@@ -840,12 +840,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AH$25:$AL$25</f>
+              <f>'Overview'!$AT$25:$BA$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AH$27:$AL$27</f>
+              <f>'Overview'!$AT$27:$BA$27</f>
             </numRef>
           </val>
         </ser>
@@ -854,7 +854,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!AG28</f>
+              <f>'Overview'!AS28</f>
             </strRef>
           </tx>
           <spPr>
@@ -864,12 +864,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AH$25:$AL$25</f>
+              <f>'Overview'!$AT$25:$BA$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AH$28:$AL$28</f>
+              <f>'Overview'!$AT$28:$BA$28</f>
             </numRef>
           </val>
         </ser>
@@ -878,7 +878,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!AG29</f>
+              <f>'Overview'!AS29</f>
             </strRef>
           </tx>
           <spPr>
@@ -888,12 +888,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AH$25:$AL$25</f>
+              <f>'Overview'!$AT$25:$BA$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AH$29:$AL$29</f>
+              <f>'Overview'!$AT$29:$BA$29</f>
             </numRef>
           </val>
         </ser>
@@ -1003,7 +1003,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO6</f>
+              <f>'Overview'!BD6</f>
             </strRef>
           </tx>
           <spPr>
@@ -1021,12 +1021,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$BE$5:$BL$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$6:$AT$6</f>
+              <f>'Overview'!$BE$6:$BL$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1036,7 +1036,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO7</f>
+              <f>'Overview'!BD7</f>
             </strRef>
           </tx>
           <spPr>
@@ -1054,12 +1054,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$BE$5:$BL$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$7:$AT$7</f>
+              <f>'Overview'!$BE$7:$BL$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1069,7 +1069,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO8</f>
+              <f>'Overview'!BD8</f>
             </strRef>
           </tx>
           <spPr>
@@ -1087,12 +1087,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$BE$5:$BL$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$8:$AT$8</f>
+              <f>'Overview'!$BE$8:$BL$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1102,7 +1102,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO9</f>
+              <f>'Overview'!BD9</f>
             </strRef>
           </tx>
           <spPr>
@@ -1120,12 +1120,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$BE$5:$BL$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$9:$AT$9</f>
+              <f>'Overview'!$BE$9:$BL$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1135,7 +1135,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO10</f>
+              <f>'Overview'!BD10</f>
             </strRef>
           </tx>
           <spPr>
@@ -1153,12 +1153,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$BE$5:$BL$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$10:$AT$10</f>
+              <f>'Overview'!$BE$10:$BL$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1168,7 +1168,7 @@
           <order val="5"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO11</f>
+              <f>'Overview'!BD11</f>
             </strRef>
           </tx>
           <spPr>
@@ -1186,12 +1186,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$BE$5:$BL$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$11:$AT$11</f>
+              <f>'Overview'!$BE$11:$BL$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1666,7 +1666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT40"/>
+  <dimension ref="A1:BL40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1675,9 +1675,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
-    <col hidden="1" width="13" customWidth="1" min="10" max="10"/>
-    <col hidden="1" width="13" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
     <col hidden="1" width="13" customWidth="1" min="12" max="12"/>
     <col hidden="1" width="13" customWidth="1" min="13" max="13"/>
     <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
@@ -1713,6 +1713,24 @@
     <col hidden="1" width="13" customWidth="1" min="44" max="44"/>
     <col hidden="1" width="13" customWidth="1" min="45" max="45"/>
     <col hidden="1" width="13" customWidth="1" min="46" max="46"/>
+    <col hidden="1" width="13" customWidth="1" min="47" max="47"/>
+    <col hidden="1" width="13" customWidth="1" min="48" max="48"/>
+    <col hidden="1" width="13" customWidth="1" min="49" max="49"/>
+    <col hidden="1" width="13" customWidth="1" min="50" max="50"/>
+    <col hidden="1" width="13" customWidth="1" min="51" max="51"/>
+    <col hidden="1" width="13" customWidth="1" min="52" max="52"/>
+    <col hidden="1" width="13" customWidth="1" min="53" max="53"/>
+    <col hidden="1" width="13" customWidth="1" min="54" max="54"/>
+    <col hidden="1" width="13" customWidth="1" min="55" max="55"/>
+    <col hidden="1" width="13" customWidth="1" min="56" max="56"/>
+    <col hidden="1" width="13" customWidth="1" min="57" max="57"/>
+    <col hidden="1" width="13" customWidth="1" min="58" max="58"/>
+    <col hidden="1" width="13" customWidth="1" min="59" max="59"/>
+    <col hidden="1" width="13" customWidth="1" min="60" max="60"/>
+    <col hidden="1" width="13" customWidth="1" min="61" max="61"/>
+    <col hidden="1" width="13" customWidth="1" min="62" max="62"/>
+    <col hidden="1" width="13" customWidth="1" min="63" max="63"/>
+    <col hidden="1" width="13" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1767,52 +1785,97 @@
           <t>FY2021</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="AQ5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -1839,35 +1902,53 @@
       <c r="F6" s="5" t="n">
         <v>1854266</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="G6" s="5" t="n">
+        <v>1694401</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>1650714</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>1245872</v>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>Total assets</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="M6" t="n">
+        <v>1245872</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1650714</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1694401</v>
+      </c>
+      <c r="P6" t="n">
         <v>1854266</v>
       </c>
-      <c r="K6" t="n">
+      <c r="Q6" t="n">
         <v>1809020</v>
       </c>
-      <c r="L6" t="n">
+      <c r="R6" t="n">
         <v>1780102</v>
       </c>
-      <c r="M6" t="n">
+      <c r="S6" t="n">
         <v>2079467</v>
       </c>
-      <c r="N6" t="n">
+      <c r="T6" t="n">
         <v>3476346</v>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="BD6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="AS6" t="n">
+      <c r="BK6" t="n">
         <v>16.2</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="BL6" t="n">
         <v>15.2</v>
       </c>
     </row>
@@ -1892,35 +1973,53 @@
       <c r="F7" s="5" t="n">
         <v>1811577</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="G7" s="5" t="n">
+        <v>1635572</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1599800</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>1197862</v>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>Loans to customers</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="M7" t="n">
+        <v>1197862</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1599800</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1635572</v>
+      </c>
+      <c r="P7" t="n">
         <v>1811577</v>
       </c>
-      <c r="K7" t="n">
+      <c r="Q7" t="n">
         <v>1761996</v>
       </c>
-      <c r="L7" t="n">
+      <c r="R7" t="n">
         <v>1712271</v>
       </c>
-      <c r="M7" t="n">
+      <c r="S7" t="n">
         <v>1866006</v>
       </c>
-      <c r="N7" t="n">
+      <c r="T7" t="n">
         <v>2301831</v>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="BD7" t="inlineStr">
         <is>
           <t>Tier 1 Ratio</t>
         </is>
       </c>
-      <c r="AS7" t="n">
+      <c r="BK7" t="n">
         <v>16.2</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="BL7" t="n">
         <v>15.2</v>
       </c>
     </row>
@@ -1939,26 +2038,29 @@
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="I8" t="inlineStr">
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>Retail deposits</t>
         </is>
       </c>
-      <c r="M8" t="n">
+      <c r="S8" t="n">
         <v>173113</v>
       </c>
-      <c r="N8" t="n">
+      <c r="T8" t="n">
         <v>2425702</v>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="BD8" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="AS8" t="n">
+      <c r="BK8" t="n">
         <v>16.2</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="BL8" t="n">
         <v>18.3</v>
       </c>
     </row>
@@ -1983,48 +2085,66 @@
       <c r="F9" s="5" t="n">
         <v>126641</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="G9" s="5" t="n">
+        <v>124246</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>115073</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>100178</v>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>Total shareholders' equity</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="M9" t="n">
+        <v>100178</v>
+      </c>
+      <c r="N9" t="n">
+        <v>115073</v>
+      </c>
+      <c r="O9" t="n">
+        <v>124246</v>
+      </c>
+      <c r="P9" t="n">
         <v>126641</v>
       </c>
-      <c r="K9" t="n">
+      <c r="Q9" t="n">
         <v>131006</v>
       </c>
-      <c r="L9" t="n">
+      <c r="R9" t="n">
         <v>122069</v>
       </c>
-      <c r="M9" t="n">
+      <c r="S9" t="n">
         <v>165080</v>
       </c>
-      <c r="N9" t="n">
+      <c r="T9" t="n">
         <v>177779</v>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="BD9" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="AS9" t="n">
+      <c r="BK9" t="n">
         <v>6.9</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="BL9" t="n">
         <v>4.9</v>
       </c>
     </row>
     <row r="10">
-      <c r="AO10" t="inlineStr">
+      <c r="BD10" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="AS10" t="n">
+      <c r="BK10" t="n">
         <v>1045</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="BL10" t="n">
         <v>163</v>
       </c>
     </row>
@@ -2034,15 +2154,15 @@
           <t>Profit &amp; Loss Summary (£'000)</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="BD11" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
-      <c r="AS11" t="n">
+      <c r="BK11" t="n">
         <v>110</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="BL11" t="n">
         <v>138</v>
       </c>
     </row>
@@ -2077,27 +2197,57 @@
           <t>FY2021</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -2124,24 +2274,42 @@
       <c r="F13" s="5" t="n">
         <v>34088</v>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="G13" s="5" t="n">
+        <v>24666</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>-1281</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>16996</v>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>Net operating income</t>
         </is>
       </c>
-      <c r="R13" t="n">
+      <c r="X13" t="n">
+        <v>16996</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-1281</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>24666</v>
+      </c>
+      <c r="AA13" t="n">
         <v>34088</v>
       </c>
-      <c r="S13" t="n">
+      <c r="AB13" t="n">
         <v>36024</v>
       </c>
-      <c r="T13" t="n">
+      <c r="AC13" t="n">
         <v>38536</v>
       </c>
-      <c r="U13" t="n">
+      <c r="AD13" t="n">
         <v>41023</v>
       </c>
-      <c r="V13" t="n">
+      <c r="AE13" t="n">
         <v>57655</v>
       </c>
     </row>
@@ -2166,24 +2334,42 @@
       <c r="F14" s="5" t="n">
         <v>-30932</v>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="G14" s="5" t="n">
+        <v>-28043</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>-31642</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>-25132</v>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>Administrative expenses</t>
         </is>
       </c>
-      <c r="R14" t="n">
+      <c r="X14" t="n">
+        <v>-25132</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-31642</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-28043</v>
+      </c>
+      <c r="AA14" t="n">
         <v>-30932</v>
       </c>
-      <c r="S14" t="n">
+      <c r="AB14" t="n">
         <v>-35502</v>
       </c>
-      <c r="T14" t="n">
+      <c r="AC14" t="n">
         <v>-32438</v>
       </c>
-      <c r="U14" t="n">
+      <c r="AD14" t="n">
         <v>-34231</v>
       </c>
-      <c r="V14" t="n">
+      <c r="AE14" t="n">
         <v>-42450</v>
       </c>
     </row>
@@ -2208,24 +2394,42 @@
       <c r="F15" s="5" t="n">
         <v>4659</v>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="G15" s="5" t="n">
+        <v>-6336</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>-31164</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>-9019</v>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>Profit for the year</t>
         </is>
       </c>
-      <c r="R15" t="n">
+      <c r="X15" t="n">
+        <v>-9019</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-31164</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-6336</v>
+      </c>
+      <c r="AA15" t="n">
         <v>4659</v>
       </c>
-      <c r="S15" t="n">
+      <c r="AB15" t="n">
         <v>1984</v>
       </c>
-      <c r="T15" t="n">
+      <c r="AC15" t="n">
         <v>6068</v>
       </c>
-      <c r="U15" t="n">
+      <c r="AD15" t="n">
         <v>6434</v>
       </c>
-      <c r="V15" t="n">
+      <c r="AE15" t="n">
         <v>13097</v>
       </c>
     </row>
@@ -2267,27 +2471,57 @@
           <t>FY2021</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AM18" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AN18" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AO18" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AP18" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -2314,24 +2548,42 @@
       <c r="F19" s="5" t="n">
         <v>124246</v>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="G19" s="5" t="n">
+        <v>115072</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>100015</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>56846</v>
+      </c>
+      <c r="AH19" t="inlineStr">
         <is>
           <t>Opening equity</t>
         </is>
       </c>
-      <c r="Z19" t="n">
+      <c r="AI19" t="n">
+        <v>56846</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>100015</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>115072</v>
+      </c>
+      <c r="AL19" t="n">
         <v>124246</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AM19" t="n">
         <v>126641</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AN19" t="n">
         <v>131006</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AO19" t="n">
         <v>122070</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AP19" t="n">
         <v>165080</v>
       </c>
     </row>
@@ -2356,24 +2608,42 @@
       <c r="F20" s="5" t="n">
         <v>-5905</v>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="G20" s="5" t="n">
+        <v>-18676</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>-23693</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>-1451</v>
+      </c>
+      <c r="AH20" t="inlineStr">
         <is>
           <t>Total comprehensive income/(loss) for the year</t>
         </is>
       </c>
-      <c r="Z20" t="n">
+      <c r="AI20" t="n">
+        <v>-1451</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>-23693</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>-18676</v>
+      </c>
+      <c r="AL20" t="n">
         <v>-5905</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AM20" t="n">
         <v>4365</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AN20" t="n">
         <v>-8937</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AO20" t="n">
         <v>6434</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AP20" t="n">
         <v>12699</v>
       </c>
     </row>
@@ -2398,24 +2668,42 @@
       <c r="F21" s="5" t="n">
         <v>8300</v>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="G21" s="5" t="n">
+        <v>27850</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>38671</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>44782</v>
+      </c>
+      <c r="AH21" t="inlineStr">
         <is>
           <t>Other equity movements, net</t>
         </is>
       </c>
-      <c r="Z21" t="n">
+      <c r="AI21" t="n">
+        <v>44782</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>38671</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>27850</v>
+      </c>
+      <c r="AL21" t="n">
         <v>8300</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AM21" t="n">
         <v>0</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AN21" t="n">
         <v>0</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AO21" t="n">
         <v>36576</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AP21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2440,24 +2728,42 @@
       <c r="F22" s="5" t="n">
         <v>126641</v>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="G22" s="5" t="n">
+        <v>124246</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>114993</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>100177</v>
+      </c>
+      <c r="AH22" t="inlineStr">
         <is>
           <t>Closing equity</t>
         </is>
       </c>
-      <c r="Z22" t="n">
+      <c r="AI22" t="n">
+        <v>100177</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>114993</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>124246</v>
+      </c>
+      <c r="AL22" t="n">
         <v>126641</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AM22" t="n">
         <v>131006</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AN22" t="n">
         <v>122069</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AO22" t="n">
         <v>165080</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AP22" t="n">
         <v>177779</v>
       </c>
     </row>
@@ -2499,27 +2805,57 @@
           <t>FY2021</t>
         </is>
       </c>
-      <c r="AH25" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
+      <c r="AX25" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="AJ25" t="inlineStr">
+      <c r="AY25" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="AK25" t="inlineStr">
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="AL25" t="inlineStr">
+      <c r="BA25" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -2544,21 +2880,39 @@
       <c r="F26" s="5" t="n">
         <v>-179449</v>
       </c>
-      <c r="AG26" t="inlineStr">
+      <c r="G26" s="5" t="n">
+        <v>-47723</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>-423882</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>-763195</v>
+      </c>
+      <c r="AS26" t="inlineStr">
         <is>
           <t>Net cash from/(used in) operating activities</t>
         </is>
       </c>
-      <c r="AH26" t="n">
+      <c r="AT26" t="n">
+        <v>-763195</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>-423882</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>-47723</v>
+      </c>
+      <c r="AW26" t="n">
         <v>-179449</v>
       </c>
-      <c r="AJ26" t="n">
+      <c r="AY26" t="n">
         <v>65493</v>
       </c>
-      <c r="AK26" t="n">
+      <c r="AZ26" t="n">
         <v>70662</v>
       </c>
-      <c r="AL26" t="n">
+      <c r="BA26" t="n">
         <v>1766849</v>
       </c>
     </row>
@@ -2581,21 +2935,39 @@
       <c r="F27" s="5" t="n">
         <v>-1757</v>
       </c>
-      <c r="AG27" t="inlineStr">
+      <c r="G27" s="5" t="n">
+        <v>-1113</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>-4848</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>-1319</v>
+      </c>
+      <c r="AS27" t="inlineStr">
         <is>
           <t>Net cash from/(used in) investing activities</t>
         </is>
       </c>
-      <c r="AH27" t="n">
+      <c r="AT27" t="n">
+        <v>-1319</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>-4848</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>-1113</v>
+      </c>
+      <c r="AW27" t="n">
         <v>-1757</v>
       </c>
-      <c r="AJ27" t="n">
+      <c r="AY27" t="n">
         <v>-698</v>
       </c>
-      <c r="AK27" t="n">
+      <c r="AZ27" t="n">
         <v>-408</v>
       </c>
-      <c r="AL27" t="n">
+      <c r="BA27" t="n">
         <v>-104</v>
       </c>
     </row>
@@ -2618,21 +2990,39 @@
       <c r="F28" s="5" t="n">
         <v>176598</v>
       </c>
-      <c r="AG28" t="inlineStr">
+      <c r="G28" s="5" t="n">
+        <v>62865</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>427129</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>762126</v>
+      </c>
+      <c r="AS28" t="inlineStr">
         <is>
           <t>Net cash from/(used in) financing activities</t>
         </is>
       </c>
-      <c r="AH28" t="n">
+      <c r="AT28" t="n">
+        <v>762126</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>427129</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>62865</v>
+      </c>
+      <c r="AW28" t="n">
         <v>176598</v>
       </c>
-      <c r="AJ28" t="n">
+      <c r="AY28" t="n">
         <v>-62554</v>
       </c>
-      <c r="AK28" t="n">
+      <c r="AZ28" t="n">
         <v>56070</v>
       </c>
-      <c r="AL28" t="n">
+      <c r="BA28" t="n">
         <v>-1655356</v>
       </c>
     </row>
@@ -2655,21 +3045,39 @@
       <c r="F29" s="5" t="n">
         <v>13500</v>
       </c>
-      <c r="AG29" t="inlineStr">
+      <c r="G29" s="5" t="n">
+        <v>18108</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>4079</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>5680</v>
+      </c>
+      <c r="AS29" t="inlineStr">
         <is>
           <t>Cash and cash equivalents at end of year</t>
         </is>
       </c>
-      <c r="AH29" t="n">
+      <c r="AT29" t="n">
+        <v>5680</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>4079</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>18108</v>
+      </c>
+      <c r="AW29" t="n">
         <v>13500</v>
       </c>
-      <c r="AJ29" t="n">
+      <c r="AY29" t="n">
         <v>17161</v>
       </c>
-      <c r="AK29" t="n">
+      <c r="AZ29" t="n">
         <v>143485</v>
       </c>
-      <c r="AL29" t="n">
+      <c r="BA29" t="n">
         <v>254874</v>
       </c>
     </row>
@@ -2709,6 +3117,21 @@
       <c r="F32" s="4" t="inlineStr">
         <is>
           <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
         </is>
       </c>
     </row>
@@ -2731,6 +3154,9 @@
       <c r="D33" s="6" t="n"/>
       <c r="E33" s="6" t="n"/>
       <c r="F33" s="6" t="n"/>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="6" t="n"/>
+      <c r="I33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -2751,6 +3177,9 @@
       <c r="D34" s="6" t="n"/>
       <c r="E34" s="6" t="n"/>
       <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="6" t="n"/>
+      <c r="I34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -2771,6 +3200,9 @@
       <c r="D35" s="6" t="n"/>
       <c r="E35" s="6" t="n"/>
       <c r="F35" s="6" t="n"/>
+      <c r="G35" s="6" t="n"/>
+      <c r="H35" s="6" t="n"/>
+      <c r="I35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -2791,6 +3223,9 @@
       <c r="D36" s="6" t="n"/>
       <c r="E36" s="6" t="n"/>
       <c r="F36" s="6" t="n"/>
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="6" t="n"/>
+      <c r="I36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -2811,6 +3246,9 @@
       <c r="D37" s="6" t="n"/>
       <c r="E37" s="6" t="n"/>
       <c r="F37" s="6" t="n"/>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="6" t="n"/>
+      <c r="I37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -2831,17 +3269,20 @@
       <c r="D38" s="6" t="n"/>
       <c r="E38" s="6" t="n"/>
       <c r="F38" s="6" t="n"/>
+      <c r="G38" s="6" t="n"/>
+      <c r="H38" s="6" t="n"/>
+      <c r="I38" s="6" t="n"/>
     </row>
     <row r="40" ht="45" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. FY2022 cash flow and FY2021-FY2023 Pillar 3 are blank - Vida only became a PRA-authorised bank on 19 November 2024 (no Pillar 3 exists before then), and FY2022's own Annual Report doesn't present a full cash flow statement on a basis comparable to other years - see the Cash Flow Statement sheet's source note for details.</t>
+          <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. FY2022 cash flow and FY2018-FY2023 Pillar 3 are blank - Vida only became a PRA-authorised bank on 19 November 2024 (no Pillar 3 exists before then; FY2018-FY2020 the entity was regulated only by the FCA, with no banking licence application even complete until later), and FY2022's own Annual Report doesn't present a full cash flow statement on a basis comparable to other years - see the Cash Flow Statement sheet's source note for details. The Balance Sheet/Equity/Cash Flow sheets and the Income Statement/Asset Quality sheets are on different bases (Company vs Group) in most pre-2024 years - see each sheet's own source note.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A40:I40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2854,7 +3295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2863,6 +3304,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2910,6 +3354,21 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -2930,6 +3389,9 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
     </row>
     <row r="6" ht="130" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -2937,13 +3399,13 @@
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
 FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
 FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-No Pillar 3 disclosure exists for FY2021-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet).</t>
+No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:I6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2955,7 +3417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2964,6 +3426,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3011,6 +3476,21 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3027,6 +3507,9 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -3041,14 +3524,14 @@
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
 FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
 FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-No Pillar 3 disclosure exists for FY2021-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet).</t>
+No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A7:I7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3060,7 +3543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3069,6 +3552,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3116,6 +3602,21 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3136,6 +3637,9 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
     </row>
     <row r="6" ht="130" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -3143,13 +3647,13 @@
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
 FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
 FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-No Pillar 3 disclosure exists for FY2021-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet).</t>
+No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:I6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3161,7 +3665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3170,6 +3674,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3217,6 +3724,21 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3233,6 +3755,9 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
     </row>
     <row r="6" ht="130" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -3240,13 +3765,13 @@
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
 FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
 FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-No Pillar 3 disclosure exists for FY2021-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet).</t>
+No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:I6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3258,7 +3783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -3267,6 +3792,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3314,6 +3842,21 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3346,17 +3889,32 @@
           <t>Not publicly disclosed</t>
         </is>
       </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="120" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>No UK OV1 (RWA-by-risk-category) template, or equivalent RWA breakdown table, exists in either Pillar 3 Disclosures document (2025 or 2024) checked this session - both are short (9-page) documents covering only the KM1 Key Metrics table already used on the other Pillar 3 sheets. Confirmed non-disclosure, not an access gap. No Pillar 3 disclosure exists at all for FY2021-FY2023 (see ENTITY_NOTE on the Cash Flow Statement sheet).</t>
+          <t>No UK OV1 (RWA-by-risk-category) template, or equivalent RWA breakdown table, exists in either Pillar 3 Disclosures document (2025 or 2024) checked this session - both are short (9-page) documents covering only the KM1 Key Metrics table already used on the other Pillar 3 sheets. Confirmed non-disclosure, not an access gap. No Pillar 3 disclosure exists at all for FY2018-FY2023 (see ENTITY_NOTE on the Cash Flow Statement sheet).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:I6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3368,7 +3926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3377,6 +3935,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3424,6 +3985,21 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3440,6 +4016,9 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -3460,6 +4039,9 @@
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
     </row>
     <row r="7" ht="130" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
@@ -3467,13 +4049,13 @@
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
 FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
 FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-No Pillar 3 disclosure exists for FY2021-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet).</t>
+No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A7:I7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3485,7 +4067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3494,6 +4076,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3541,6 +4126,21 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3557,6 +4157,9 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -3573,6 +4176,9 @@
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -3593,6 +4199,9 @@
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -3607,14 +4216,14 @@
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
 FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
 FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-No Pillar 3 disclosure exists for FY2021-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet).</t>
+No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A9:I9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3626,7 +4235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3635,6 +4244,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3682,6 +4294,21 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3698,6 +4325,9 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -3714,6 +4344,9 @@
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -3734,6 +4367,9 @@
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
     </row>
     <row r="8" ht="130" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
@@ -3741,13 +4377,13 @@
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
 FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
 FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-No Pillar 3 disclosure exists for FY2021-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet).</t>
+No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A8:I8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3759,7 +4395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3768,6 +4404,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3815,6 +4454,21 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3843,6 +4497,21 @@
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
@@ -3861,14 +4530,14 @@
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
 FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
 FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-No Pillar 3 disclosure exists for FY2021-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet).</t>
+No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A7:I7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3880,7 +4549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -3889,6 +4558,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3934,6 +4606,21 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020 (£'000)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019 (£'000)</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018 (£'000)</t>
         </is>
       </c>
     </row>
@@ -3948,6 +4635,9 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -3969,6 +4659,15 @@
       </c>
       <c r="F5" s="6" t="n">
         <v>13500</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>18109</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>4079</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>5680</v>
       </c>
     </row>
     <row r="6">
@@ -3986,6 +4685,9 @@
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -4007,6 +4709,15 @@
       </c>
       <c r="F7" s="6" t="n">
         <v>1811577</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1635572</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1599800</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>1197862</v>
       </c>
     </row>
     <row r="8">
@@ -4026,6 +4737,9 @@
         <v>731</v>
       </c>
       <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -4048,6 +4762,15 @@
       <c r="F9" s="6" t="n">
         <v>11399</v>
       </c>
+      <c r="G9" s="6" t="n">
+        <v>15207</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>21901</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>25813</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -4069,6 +4792,15 @@
       </c>
       <c r="F10" s="6" t="n">
         <v>12975</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>11602</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>10283</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>6007</v>
       </c>
     </row>
     <row r="11">
@@ -4082,6 +4814,15 @@
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n">
+        <v>9000</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>9000</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -4104,6 +4845,15 @@
       <c r="F12" s="6" t="n">
         <v>2407</v>
       </c>
+      <c r="G12" s="6" t="n">
+        <v>3795</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>5334</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1249</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -4125,6 +4875,15 @@
       </c>
       <c r="F13" s="6" t="n">
         <v>2408</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>1117</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>317</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>261</v>
       </c>
     </row>
     <row r="14">
@@ -4140,6 +4899,9 @@
         <v>25</v>
       </c>
       <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -4161,6 +4923,15 @@
       </c>
       <c r="F15" s="5" t="n">
         <v>1854266</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>1694401</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>1650714</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>1245872</v>
       </c>
     </row>
     <row r="16">
@@ -4174,6 +4945,9 @@
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -4190,6 +4964,9 @@
       <c r="D17" s="6" t="n"/>
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -4212,6 +4989,9 @@
       <c r="F18" s="6" t="n">
         <v>15336</v>
       </c>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -4234,6 +5014,15 @@
       <c r="F19" s="6" t="n">
         <v>1690865</v>
       </c>
+      <c r="G19" s="6" t="n">
+        <v>1521161</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>1484952</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>1108999</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -4252,6 +5041,9 @@
       </c>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -4273,6 +5065,15 @@
       </c>
       <c r="F21" s="6" t="n">
         <v>21050</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>48390</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>50689</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>36696</v>
       </c>
     </row>
     <row r="22">
@@ -4292,6 +5093,11 @@
       <c r="F22" s="6" t="n">
         <v>374</v>
       </c>
+      <c r="G22" s="6" t="n">
+        <v>604</v>
+      </c>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -4308,6 +5114,9 @@
       <c r="D23" s="6" t="n"/>
       <c r="E23" s="6" t="n"/>
       <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -4329,6 +5138,15 @@
       </c>
       <c r="F24" s="5" t="n">
         <v>1727625</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>1570155</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>1535641</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>1145695</v>
       </c>
     </row>
     <row r="25">
@@ -4342,6 +5160,9 @@
       <c r="D25" s="6" t="n"/>
       <c r="E25" s="6" t="n"/>
       <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -4363,6 +5184,15 @@
       </c>
       <c r="F26" s="6" t="n">
         <v>204462</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>196162</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>168313</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>129642</v>
       </c>
     </row>
     <row r="27">
@@ -4378,6 +5208,9 @@
       <c r="D27" s="6" t="n"/>
       <c r="E27" s="6" t="n"/>
       <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -4400,6 +5233,15 @@
       <c r="F28" s="6" t="n">
         <v>-77821</v>
       </c>
+      <c r="G28" s="6" t="n">
+        <v>-71916</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>-53240</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>-29464</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -4422,6 +5264,15 @@
       <c r="F29" s="5" t="n">
         <v>126641</v>
       </c>
+      <c r="G29" s="5" t="n">
+        <v>124246</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>115073</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>100178</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -4443,6 +5294,15 @@
       </c>
       <c r="F30" s="5" t="n">
         <v>1854266</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>1694401</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>1650714</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>1245872</v>
       </c>
     </row>
     <row r="32" ht="180" customHeight="1">
@@ -4454,13 +5314,16 @@
 FY2023: Belmont Green Finance Limited Annual Report and Accounts 2023, p.185 (Company Statement of Financial Position) - https://www.vidabank.co.uk/media/zhoj0swe/annual-report-and-accounts-2023.pdf
 FY2022: taken from the FY2023 Annual Report's own restated FY2022 comparative column (same document/page as above) - Belmont Green's own FY2022 Annual Report was not fetched this session.
 FY2021: Belmont Green Finance Limited Annual Report and Accounts 2021, p.149 (Company Statement of Financial Position) - https://www.vidabank.co.uk/media/p3wau0ms/annual-report-and-accounts-2021.pdf
-Balance Sheet / Statement of Changes in Equity are on Vida Bank Limited's own Company (non-consolidated) basis in every year, matching the Cash Flow Statement sheet's basis (see its own ENTITY_NOTE). Profit &amp; Loss is on the Company basis for FY2025/FY2024 only (Vida's own Company Statement of Comprehensive Income exists for those two years); for FY2023/FY2022/FY2021, the Company took the section 408 Companies Act 2006 exemption and published no separate Company income statement (only a one-line narrative profit/loss-after-tax figure, which ties to the equity ladder's own movement for that year), so the Group/Consolidated income statement is shown instead for those 3 years - a genuine basis difference, not forced to a single basis.</t>
+FY2020: Belmont Green Finance Limited Annual Report and Accounts 2020, Company Statement of Financial Position - https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzMwNjUyMjA5MmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2019: Belmont Green Finance Limited Annual Report and Accounts 2019, Company Statement of Financial Position - https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzI4NjAzOTYwNWFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2018: taken from the FY2019 Annual Report's own restated FY2018 comparative column (same document as above) - see FY2018_RESTATEMENT_NOTE (on the Cash Flow Statement sheet's source note) for why the restated figures are used in place of Belmont Green's originally-filed FY2018 Annual Report (https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzIzMzYzMjc1OWFkaXF6a2N4/document?format=pdf&amp;download=0).
+Balance Sheet / Statement of Changes in Equity are on Vida Bank Limited's own Company (non-consolidated) basis in every year, matching the Cash Flow Statement sheet's basis (see its own ENTITY_NOTE). Profit &amp; Loss is on the Company basis for FY2025/FY2024 only (Vida's own Company Statement of Comprehensive Income exists for those two years); for FY2023/FY2022/FY2021/FY2020/FY2019, the Company took the section 408 Companies Act 2006 exemption and published no separate Company income statement (only a one-line narrative profit/loss-after-tax figure, which ties to the equity ladder's own movement for that year), so the Group/Consolidated income statement is shown instead for those years. FY2018's own Annual Report did present a Company income statement, but it is not used here either, for consistency with every other pre-2024 year's Group-basis figures (see INCOME_STATEMENT_SOURCES for detail) - a genuine basis difference, not forced to a single basis.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A32:I32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4472,7 +5335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -4481,6 +5344,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4493,7 +5359,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FY2025/FY2024: Company basis. FY2023-FY2021: Group/Consolidated basis (Company P&amp;L exempted under s.408). £'000.</t>
+          <t>FY2025/FY2024: Company basis. FY2023-FY2018: Group/Consolidated basis (Company P&amp;L exempted under s.408 in every year except FY2018's own Annual Report, not used here for consistency - see source note). £'000.</t>
         </is>
       </c>
     </row>
@@ -4526,6 +5392,21 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020 (£'000)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019 (£'000)</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018 (£'000)</t>
         </is>
       </c>
     </row>
@@ -4540,6 +5421,9 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -4562,6 +5446,15 @@
       <c r="F5" s="6" t="n">
         <v>68551</v>
       </c>
+      <c r="G5" s="6" t="n">
+        <v>61142</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>49649</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>42042</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -4584,6 +5477,15 @@
       <c r="F6" s="6" t="n">
         <v>-34046</v>
       </c>
+      <c r="G6" s="6" t="n">
+        <v>-37205</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>-47030</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>-24573</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -4606,6 +5508,15 @@
       <c r="F7" s="5" t="n">
         <v>34505</v>
       </c>
+      <c r="G7" s="5" t="n">
+        <v>23937</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>2619</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>17469</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -4628,6 +5539,11 @@
       <c r="F8" s="6" t="n">
         <v>987</v>
       </c>
+      <c r="G8" s="6" t="n">
+        <v>779</v>
+      </c>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -4650,6 +5566,15 @@
       <c r="F9" s="6" t="n">
         <v>-1404</v>
       </c>
+      <c r="G9" s="6" t="n">
+        <v>-50</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-3900</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>-473</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -4672,6 +5597,15 @@
       <c r="F10" s="5" t="n">
         <v>34088</v>
       </c>
+      <c r="G10" s="5" t="n">
+        <v>24666</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-1281</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>16996</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -4694,6 +5628,15 @@
       <c r="F11" s="6" t="n">
         <v>-30932</v>
       </c>
+      <c r="G11" s="6" t="n">
+        <v>-28043</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-31642</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-25132</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -4715,6 +5658,15 @@
       </c>
       <c r="F12" s="5" t="n">
         <v>3156</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>-3377</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-32923</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>-8136</v>
       </c>
     </row>
     <row r="13">
@@ -4734,6 +5686,11 @@
       <c r="F13" s="6" t="n">
         <v>223</v>
       </c>
+      <c r="G13" s="6" t="n">
+        <v>-350</v>
+      </c>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -4756,6 +5713,15 @@
       <c r="F14" s="6" t="n">
         <v>-725</v>
       </c>
+      <c r="G14" s="6" t="n">
+        <v>-3371</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-2402</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-1105</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -4778,6 +5744,15 @@
       <c r="F15" s="5" t="n">
         <v>2654</v>
       </c>
+      <c r="G15" s="5" t="n">
+        <v>-7098</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>-35325</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>-9241</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -4800,6 +5775,15 @@
       <c r="F16" s="6" t="n">
         <v>2005</v>
       </c>
+      <c r="G16" s="6" t="n">
+        <v>762</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>4161</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>222</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -4821,6 +5805,15 @@
       </c>
       <c r="F17" s="5" t="n">
         <v>4659</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-6336</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-31164</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>-9019</v>
       </c>
     </row>
     <row r="18">
@@ -4834,6 +5827,9 @@
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -4856,6 +5852,9 @@
       <c r="F19" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -4870,6 +5869,9 @@
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -4884,6 +5886,9 @@
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="6" t="n"/>
       <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -4906,24 +5911,37 @@
       <c r="F22" s="5" t="n">
         <v>4659</v>
       </c>
+      <c r="G22" s="5" t="n">
+        <v>-6336</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-31164</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>-9019</v>
+      </c>
     </row>
     <row r="24" ht="260" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Sources - £'000. FY2025/FY2024: Vida Bank Limited's own Company Statement of Comprehensive Income. FY2023/FY2022/FY2021: Group/Consolidated Statement of Profit and Loss and Other Comprehensive Income (Company P&amp;L exempted under s.408, see ENTITY_NOTE below):
+          <t>Sources - £'000. FY2025/FY2024: Vida Bank Limited's own Company Statement of Comprehensive Income. FY2023-FY2018: Group/Consolidated Statement of Profit and Loss and Other Comprehensive Income (Company P&amp;L exempted under s.408 in every one of these years - FY2018's own Annual Report is the sole exception, which did present a Company income statement, but it is not used here for consistency with every other year's Group-basis figures; see ENTITY_NOTE below):
 FY2025: Vida Bank Limited Annual Report and Accounts 2025 (Company), p.52 - https://www.vidabank.co.uk/media/pkmnxlqg/annual-report-and-accounts-2025-company.pdf
 FY2024: Vida Bank Limited Annual Report and Accounts 2025 (Company), p.52, FY2024 comparative column - https://www.vidabank.co.uk/media/pkmnxlqg/annual-report-and-accounts-2025-company.pdf
 FY2023: Belmont Green Finance Limited Annual Report and Accounts 2023, p.143 (Consolidated Statement of Profit and Loss and Other Comprehensive Income) - https://www.vidabank.co.uk/media/zhoj0swe/annual-report-and-accounts-2023.pdf
 FY2022: taken from the FY2023 Annual Report's own FY2022 comparative column (same document/page as above).
 FY2021: Belmont Green Finance Limited Annual Report and Accounts 2021, p.109 (Consolidated Statement of Comprehensive Income) - https://www.vidabank.co.uk/media/p3wau0ms/annual-report-and-accounts-2021.pdf
+FY2020: Belmont Green Finance Limited Annual Report and Accounts 2020, Consolidated Statement of Comprehensive Income - https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzMwNjUyMjA5MmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2019: Belmont Green Finance Limited Annual Report and Accounts 2019, Consolidated Statement of Comprehensive Income - https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzI4NjAzOTYwNWFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2018: taken from the FY2019 Annual Report's own FY2018 comparative column (same document as above) - Belmont Green's originally-filed FY2018 Annual Report did present a Company-basis income statement, but it is not used here (see basis note above).
+FY2019's own Annual Report has an internal, unreconciled ~£80k discrepancy between the Loss for the year it reports on this Consolidated Statement of Comprehensive Income (£(31,164)k) and the Loss for the year used on this workbook's own Statement of Changes in Equity and Cash Flow Statement sheets (£(31,084)k, per the same Annual Report's own Statement of Changes in Equity and cash flow note) - both figures are reproduced exactly as printed on their respective source statements rather than forced to agree.
 Presentation notes (not silently reconciled): FY2021's Group statement labels its operating-income subtotal "Total income" rather than FY2022-25's "Net operating income" - same position in the statement, different label, reproduced as printed. FY2025's own Statement of Comprehensive Income prints its final row as "Total other comprehensive profit" with a value of 12,699 - this is actually the year's Total comprehensive income (Profit after tax 13,097 less the 3 OCI items above it, -21-98-279=-398, gives exactly 12,699); the source's own row label is internally inconsistent (a subtotal, not "other" comprehensive income), so this row is relabelled "Total comprehensive income for the year, net of tax" here to match the other 4 years' own correctly-labelled totals - the £'000 value itself is reproduced exactly as printed, unchanged.
-Balance Sheet / Statement of Changes in Equity are on Vida Bank Limited's own Company (non-consolidated) basis in every year, matching the Cash Flow Statement sheet's basis (see its own ENTITY_NOTE). Profit &amp; Loss is on the Company basis for FY2025/FY2024 only (Vida's own Company Statement of Comprehensive Income exists for those two years); for FY2023/FY2022/FY2021, the Company took the section 408 Companies Act 2006 exemption and published no separate Company income statement (only a one-line narrative profit/loss-after-tax figure, which ties to the equity ladder's own movement for that year), so the Group/Consolidated income statement is shown instead for those 3 years - a genuine basis difference, not forced to a single basis.</t>
+Balance Sheet / Statement of Changes in Equity are on Vida Bank Limited's own Company (non-consolidated) basis in every year, matching the Cash Flow Statement sheet's basis (see its own ENTITY_NOTE). Profit &amp; Loss is on the Company basis for FY2025/FY2024 only (Vida's own Company Statement of Comprehensive Income exists for those two years); for FY2023/FY2022/FY2021/FY2020/FY2019, the Company took the section 408 Companies Act 2006 exemption and published no separate Company income statement (only a one-line narrative profit/loss-after-tax figure, which ties to the equity ladder's own movement for that year), so the Group/Consolidated income statement is shown instead for those years. FY2018's own Annual Report did present a Company income statement, but it is not used here either, for consistency with every other pre-2024 year's Group-basis figures (see INCOME_STATEMENT_SOURCES for detail) - a genuine basis difference, not forced to a single basis.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A24:I24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4935,7 +5953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -4989,18 +6007,18 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Balance at 1 January 2021</t>
+          <t>Balance at 1 January 2018</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>196162</v>
+        <v>84860</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>-71916</v>
+        <v>-28014</v>
       </c>
       <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="n">
-        <v>124246</v>
+        <v>56846</v>
       </c>
     </row>
     <row r="5">
@@ -5010,140 +6028,140 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>8300</v>
+        <v>44782</v>
       </c>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6" t="n">
-        <v>8300</v>
+        <v>44782</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Loss for the year</t>
+          <t>Loss for the year (restated)</t>
         </is>
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n">
-        <v>-5905</v>
+        <v>-1451</v>
       </c>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n">
-        <v>-5905</v>
+        <v>-1451</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Balance at 31 December 2021</t>
+          <t>Balance at 31 December 2018</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>204462</v>
+        <v>129642</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-77821</v>
+        <v>-29464</v>
       </c>
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n">
-        <v>126641</v>
+        <v>100177</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Profit for the year</t>
+          <t>Adjustment on initial application of IFRS 16</t>
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n">
-        <v>4365</v>
+        <v>-162</v>
       </c>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n">
-        <v>4365</v>
+        <v>-162</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Balance at 31 December 2022</t>
+          <t>Balance at 1 January 2019 (per FY2019 Annual Report - see source note)</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>204462</v>
+        <v>129641</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>-73456</v>
+        <v>-29547</v>
       </c>
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n">
-        <v>131006</v>
+        <v>100015</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Loss for the year</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n">
-        <v>-8937</v>
-      </c>
+          <t>Share issuance</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>38671</v>
+      </c>
+      <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="n">
-        <v>-8937</v>
+        <v>38671</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Balance at 31 December 2023</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>204462</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>-82393</v>
-      </c>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n">
-        <v>122069</v>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n">
+        <v>-23693</v>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n">
+        <v>-23693</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Balance at 1 January 2024 (per FY2024 Annual Report - see source note)</t>
+          <t>Balance at 31 December 2019 (per FY2019 Annual Report - see source note)</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>204463</v>
+        <v>168313</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>-82393</v>
+        <v>-53240</v>
       </c>
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n">
-        <v>122070</v>
+        <v>114993</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Profit for the year</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n">
-        <v>6434</v>
-      </c>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n">
-        <v>6434</v>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Balance at 1 January 2020 (per FY2020 Annual Report - see source note)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>168312</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-53240</v>
+      </c>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n">
+        <v>115072</v>
       </c>
     </row>
     <row r="14">
@@ -5153,129 +6171,336 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>36576</v>
+        <v>27850</v>
       </c>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n">
-        <v>36576</v>
+        <v>27850</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Balance at 31 December 2024</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>241039</v>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>-75959</v>
-      </c>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n">
-        <v>165080</v>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n">
+        <v>-18676</v>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n">
+        <v>-18676</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Profit for the year</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n">
-        <v>13097</v>
-      </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n">
-        <v>13097</v>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Balance at 31 December 2020</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>196162</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>-71916</v>
+      </c>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n">
+        <v>124246</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Deferred tax on Gilts</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n">
-        <v>-98</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>-98</v>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Balance at 1 January 2021</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>196162</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-71916</v>
+      </c>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n">
+        <v>124246</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fair value through OCI reserve</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n"/>
+          <t>Share issuance</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>8300</v>
+      </c>
       <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n">
-        <v>-279</v>
-      </c>
+      <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n">
-        <v>-279</v>
+        <v>8300</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n">
+        <v>-5905</v>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n">
+        <v>-5905</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Balance at 31 December 2021</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>204462</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-77821</v>
+      </c>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n">
+        <v>126641</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n">
+        <v>4365</v>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n">
+        <v>4365</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Balance at 31 December 2022</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>204462</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-73456</v>
+      </c>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n">
+        <v>131006</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n">
+        <v>-8937</v>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n">
+        <v>-8937</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Balance at 31 December 2023</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>204462</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>-82393</v>
+      </c>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n">
+        <v>122069</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Balance at 1 January 2024 (per FY2024 Annual Report - see source note)</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>204463</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>-82393</v>
+      </c>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n">
+        <v>122070</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n">
+        <v>6434</v>
+      </c>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n">
+        <v>6434</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Share issuance</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>36576</v>
+      </c>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n">
+        <v>36576</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Balance at 31 December 2024</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>241039</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>-75959</v>
+      </c>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n">
+        <v>165080</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n">
+        <v>13097</v>
+      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n">
+        <v>13097</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax on Gilts</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n">
+        <v>-98</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>-98</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Fair value through OCI reserve</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n">
+        <v>-279</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-279</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
           <t>Amounts deferred to cash flow hedge reserve, net of tax</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n">
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n">
         <v>-21</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E32" s="6" t="n">
         <v>-21</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>Share capital reallocation</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B33" s="6" t="n">
         <v>-204883</v>
       </c>
-      <c r="C20" s="6" t="n">
+      <c r="C33" s="6" t="n">
         <v>204883</v>
       </c>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n">
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>Balance at 31 December 2025</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B34" s="5" t="n">
         <v>36156</v>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C34" s="5" t="n">
         <v>142021</v>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="D34" s="5" t="n">
         <v>-398</v>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="E34" s="5" t="n">
         <v>177779</v>
       </c>
     </row>
-    <row r="23" ht="260" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+    <row r="36" ht="260" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>Sources - Vida Bank Limited's own Company (non-consolidated) Statement of Changes in Equity, £'000:
 FY2021 boundary (1 Jan 2021 opening, FY2021 movements, 31 Dec 2021 closing): Belmont Green Finance Limited Annual Report and Accounts 2021, p.150 - https://www.vidabank.co.uk/media/p3wau0ms/annual-report-and-accounts-2021.pdf
@@ -5283,15 +6508,19 @@
 FY2023 boundary: same document, p.184 - https://www.vidabank.co.uk/media/zhoj0swe/annual-report-and-accounts-2023.pdf
 FY2024 boundary: Vida Bank Limited Annual Report and Accounts 2024, p.72 - https://www.vidabank.co.uk/media/emghy4z2/annual-report-and-accounts-2024-company.pdf
 FY2025 boundary: Vida Bank Limited Annual Report and Accounts 2025 (Company), p.54 - https://www.vidabank.co.uk/media/pkmnxlqg/annual-report-and-accounts-2025-company.pdf
-Discrepancy flagged, not forced to tie: the FY2024 Annual Report's own opening balance at 1 January 2024 (share capital 204,463 / total equity 122,070) differs by £1k from the FY2023 Annual Report's own closing balance at 31 December 2023 (share capital 204,462 / total equity 122,069) - a genuine £1k rounding artefact between the two source documents, each reproduced exactly as its own report states.
+FY2018 boundary (1 Jan 2018 opening, FY2018 movements, 31 Dec 2018 closing): taken from the FY2019 Annual Report's own restated FY2018 comparative rows (Company Statement of Changes in Equity) - https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzI4NjAzOTYwNWFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2019 boundary: same FY2019 Annual Report, Company Statement of Changes in Equity - https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzI4NjAzOTYwNWFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2020 boundary: Belmont Green Finance Limited Annual Report and Accounts 2020, Company Statement of Changes in Equity - https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzMwNjUyMjA5MmFkaXF6a2N4/document?format=pdf&amp;download=0
+Discrepancy flagged, not forced to tie: the FY2024 Annual Report's own opening balance at 1 January 2024 (share capital 204,463 / total equity 122,070) differs by £1k from the FY2023 Annual Report's own closing balance at 31 December 2023 (share capital 204,462 / total equity 122,069) - a genuine £1k rounding artefact between the two source documents, each reproduced exactly as its own report states. A similar £1k share-capital rounding artefact exists between the FY2020 Annual Report's own opening 1 January 2020 row (share capital 168,312) and the FY2019 Annual Report's own closing 31 December 2019 row (share capital 168,313), again reproduced exactly as each report states.
+Larger, unreconciled discrepancy flagged (not forced to tie): the FY2019 Annual Report's own 'Balance as at 1 January 2019' row (129,641 / (29,547) / 100,015) does not internally sum (129,641 - 29,547 = 100,094, not 100,015 as printed) and its own 'At 31 December 2019' row (168,313 / (53,240) / 114,993) likewise differs by £80k from this workbook's own Balance Sheet sheet, which uses the same Annual Report's Company Statement of Financial Position total shareholders' equity of £115,073k for 31 December 2019 - both sets of figures are reproduced exactly as printed on their own source statement rather than corrected or blended.
 The FY2025 Statement of Changes in Equity's own "Total comprehensive income" subtotal row is omitted from this ladder: it prints running balances (not that year's movement) in its Retained earnings and Total columns - see the Profit &amp; Loss sheet's own source note for the same issue on that sheet. Every individual movement row above it (Profit for the year, Deferred tax on Gilts, Fair value through OCI reserve, Amounts deferred to cash flow hedge reserve) is reproduced in full and the ladder ties exactly without it.
-Balance Sheet / Statement of Changes in Equity are on Vida Bank Limited's own Company (non-consolidated) basis in every year, matching the Cash Flow Statement sheet's basis (see its own ENTITY_NOTE). Profit &amp; Loss is on the Company basis for FY2025/FY2024 only (Vida's own Company Statement of Comprehensive Income exists for those two years); for FY2023/FY2022/FY2021, the Company took the section 408 Companies Act 2006 exemption and published no separate Company income statement (only a one-line narrative profit/loss-after-tax figure, which ties to the equity ladder's own movement for that year), so the Group/Consolidated income statement is shown instead for those 3 years - a genuine basis difference, not forced to a single basis.</t>
+Balance Sheet / Statement of Changes in Equity are on Vida Bank Limited's own Company (non-consolidated) basis in every year, matching the Cash Flow Statement sheet's basis (see its own ENTITY_NOTE). Profit &amp; Loss is on the Company basis for FY2025/FY2024 only (Vida's own Company Statement of Comprehensive Income exists for those two years); for FY2023/FY2022/FY2021/FY2020/FY2019, the Company took the section 408 Companies Act 2006 exemption and published no separate Company income statement (only a one-line narrative profit/loss-after-tax figure, which ties to the equity ladder's own movement for that year), so the Group/Consolidated income statement is shown instead for those years. FY2018's own Annual Report did present a Company income statement, but it is not used here either, for consistency with every other pre-2024 year's Group-basis figures (see INCOME_STATEMENT_SOURCES for detail) - a genuine basis difference, not forced to a single basis.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A36:E36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5303,7 +6532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -5312,6 +6541,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5357,6 +6589,21 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020 (£'000)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019 (£'000)</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018 (£'000)</t>
         </is>
       </c>
     </row>
@@ -5371,6 +6618,9 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -5390,6 +6640,15 @@
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n">
         <v>-179449</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-47723</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-423882</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>-763195</v>
       </c>
     </row>
     <row r="6">
@@ -5403,6 +6662,9 @@
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -5423,6 +6685,15 @@
       <c r="F7" s="6" t="n">
         <v>-190</v>
       </c>
+      <c r="G7" s="6" t="n">
+        <v>-119</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-4537</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-1319</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -5443,6 +6714,15 @@
       <c r="F8" s="6" t="n">
         <v>-1567</v>
       </c>
+      <c r="G8" s="6" t="n">
+        <v>-994</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-311</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -5462,6 +6742,15 @@
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n">
         <v>-1757</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>-1113</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>-4848</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>-1319</v>
       </c>
     </row>
     <row r="10">
@@ -5475,6 +6764,9 @@
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -5489,6 +6781,15 @@
       <c r="F11" s="6" t="n">
         <v>8300</v>
       </c>
+      <c r="G11" s="6" t="n">
+        <v>27850</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>38671</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>44782</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -5509,185 +6810,270 @@
       <c r="F12" s="6" t="n">
         <v>169705</v>
       </c>
+      <c r="G12" s="6" t="n">
+        <v>36209</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>392814</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>723148</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Repayment of loans</t>
+          <t>Loan to/from subsidiary undertakings</t>
         </is>
       </c>
       <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n">
-        <v>-25000</v>
-      </c>
+      <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n">
+        <v>-4356</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-5804</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Issuance of Tier 2 subordinated liabilities</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>35000</v>
-      </c>
-      <c r="C14" s="6" t="n"/>
+          <t>Repayment of loans</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n">
+        <v>-25000</v>
+      </c>
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Repayment of lease liabilities</t>
+          <t>Issuance of Tier 2 subordinated liabilities</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>-479</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>-225</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>-446</v>
-      </c>
+        <v>35000</v>
+      </c>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
       <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n">
-        <v>-1407</v>
-      </c>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Movement in debt securities</t>
+          <t>Repayment of lease liabilities</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>-785634</v>
+        <v>-479</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>-34135</v>
-      </c>
-      <c r="D16" s="6" t="n"/>
+        <v>-225</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>-446</v>
+      </c>
       <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
+      <c r="F16" s="6" t="n">
+        <v>-1407</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-1194</v>
+      </c>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Other movements</t>
+          <t>Movement in debt securities</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0</v>
+        <v>-785634</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>-27</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>-12</v>
-      </c>
+        <v>-34135</v>
+      </c>
+      <c r="D17" s="6" t="n"/>
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Net cash flows (used in)/generated from financing activities</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>-1655356</v>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>56070</v>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>-62554</v>
-      </c>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n">
-        <v>176598</v>
-      </c>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Other movements</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>-27</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>-12</v>
+      </c>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Net increase/(decrease) in cash and cash equivalents</t>
+          <t>Net cash flows (used in)/generated from financing activities</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>111389</v>
+        <v>-1655356</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>126324</v>
+        <v>56070</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2241</v>
+        <v>-62554</v>
       </c>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n">
+        <v>176598</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>62865</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>427129</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>762126</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Net increase/(decrease) in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>111389</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>126324</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>2241</v>
+      </c>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n">
         <v>-4608</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="G20" s="5" t="n">
+        <v>14029</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>-1601</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>-2389</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Cash and cash equivalents at the beginning of the year</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B21" s="6" t="n">
         <v>143485</v>
       </c>
-      <c r="C20" s="6" t="n">
+      <c r="C21" s="6" t="n">
         <v>17161</v>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D21" s="6" t="n">
         <v>14920</v>
       </c>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n">
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n">
         <v>18108</v>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="G21" s="6" t="n">
+        <v>4079</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>5680</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>8069</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Cash and cash equivalents at the end of the year</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B22" s="5" t="n">
         <v>254874</v>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C22" s="5" t="n">
         <v>143485</v>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="D22" s="5" t="n">
         <v>17161</v>
       </c>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n">
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n">
         <v>13500</v>
       </c>
-    </row>
-    <row r="23" ht="280" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="G22" s="5" t="n">
+        <v>18108</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>4079</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>5680</v>
+      </c>
+    </row>
+    <row r="24" ht="280" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Sources - all figures are Vida Bank Limited's own Company (non-consolidated) cash flow statement, £'000:
 FY2025: Vida Bank Limited Annual Report and Accounts 2025 (Company), p.55 (Statement of Cash Flows) - https://www.vidabank.co.uk/media/pkmnxlqg/annual-report-and-accounts-2025-company.pdf
 FY2024: Vida Bank Limited Annual Report and Accounts 2024 (Company), p.73 (Statement of Cash Flows) - https://www.vidabank.co.uk/media/emghy4z2/annual-report-and-accounts-2024-company.pdf
 FY2023: taken from Vida Bank Limited's FY2024 Annual Report's own FY2023 comparative column (p.73, same document as above) - Belmont Green Finance Limited's own FY2023 Annual Report does not present a comparable Company-basis statement (see ENTITY_NOTE/FY2022_GAP_NOTE).
 FY2021: Belmont Green Finance Limited (Vida) Annual Report and Accounts 2021, p.150 (Company Statement of Cash Flows) - https://www.vidabank.co.uk/media/p3wau0ms/annual-report-and-accounts-2021.pdf
-ENTITY NOTE: the company (FRN 738741, Companies House 09837692) was named 'Belmont Green Finance Limited' (trading as Vida / Vida Homeloans) through its FY2023 Annual Report, and was renamed 'Vida Bank Limited' after receiving its PRA banking licence on 19 November 2024. This workbook uses 'Vida Bank Limited' throughout since that is its current name. Pre-authorisation (FY2021-FY2023), the business was funded mainly through mortgage securitisation (numerous 'Tower Bridge Funding' special-purpose vehicles) rather than retail deposits; the FY2023 Annual Report's own commentary describes the business as still 'preparing for the banking licence'. Cash flow figures below are on the Company's own (non-consolidated/solo) basis in every populated year - this is the only basis for which a full three-part cash flow statement (operating/investing/financing) could be found in every report; the Consolidated (Group) statement of financial position was reported each year, but the FY2022 and FY2023 Annual Reports' own primary financial statements do not include a full Group cash flow statement, only a partial 'Net cash flow from operating activities' reconciliation note (Note 25) on the Group basis - see FY2022_GAP_NOTE below.
-FY2022 is blank on this sheet: neither the FY2022 nor FY2023 Annual Report presents a full three-part Company cash flow statement for FY2022 (checked both directly - https://www.vidabank.co.uk/media/zhoj0swe/annual-report-and-accounts-2023.pdf - and via the FY2023 report's own prior-year comparative column, which is likewise not present.) The FY2023 Annual Report's Note 25 gives only a partial Group-basis operating reconciliation ending at 'Net cash flows from operating activities: £68,297k' for FY2022 - not on the same (Company) basis as every other populated year here and with no investing/financing breakdown at all, so it is not shown rather than presented as a misleadingly partial column.</t>
+FY2020: Belmont Green Finance Limited Annual Report and Accounts 2020 (Company Statement of Cash Flows) - https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzMwNjUyMjA5MmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2019: Belmont Green Finance Limited Annual Report and Accounts 2019 (Company Statement of Cash Flows, Note 35-37 breakdown) - https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzI4NjAzOTYwNWFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2018: taken from the FY2019 Annual Report's own restated FY2018 comparative column (same document/notes as above) - see FY2018_RESTATEMENT_NOTE for why the restated figures are used in place of Belmont Green's originally-filed FY2018 Annual Report (https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzIzMzYzMjc1OWFkaXF6a2N4/document?format=pdf&amp;download=0).
+ENTITY NOTE: the company (FRN 738741, Companies House 09837692) was named 'Belmont Green Finance Limited' (trading as Vida / Vida Homeloans) through its FY2023 Annual Report, and was renamed 'Vida Bank Limited' after receiving its PRA banking licence on 19 November 2024. This workbook uses 'Vida Bank Limited' throughout since that is its current name. Pre-authorisation (FY2018-FY2023), the business was funded mainly through mortgage securitisation (numerous 'Tower Bridge Funding' special-purpose vehicles) and warehouse facilities rather than retail deposits; the FY2023 Annual Report's own commentary describes the business as still 'preparing for the banking licence'. FY2018-FY2020 the company was regulated only by the FCA (mortgage lending/administration permissions) - not the PRA - and had no banking licence and no deposit-taking business at all; its own FY2019 and FY2020 Annual Reports both still describe the banking licence application as in progress/delayed. Cash flow figures below are on the Company's own (non-consolidated/solo) basis in every populated year - this is the only basis for which a full three-part cash flow statement (operating/investing/financing) could be found in every report; the Consolidated (Group) statement of financial position was reported each year from FY2019 onwards, but the FY2022 and FY2023 Annual Reports' own primary financial statements do not include a full Group cash flow statement, only a partial 'Net cash flow from operating activities' reconciliation note (Note 25) on the Group basis - see FY2022_GAP_NOTE below. FY2018's own Annual Report only presented Company-only financial statements (no Group/consolidated accounts were filed for FY2018); Group consolidated accounts for Belmont Green Finance Limited first appear in the FY2019 Annual Report, which also restates FY2018's Company-basis Balance Sheet, Cash Flow Statement and Statement of Changes in Equity figures - see FY2018_RESTATEMENT_NOTE below for why this workbook uses those restated figures rather than the originally-filed FY2018 Annual Report's own (much smaller) figures.
+FY2022 is blank on this sheet: neither the FY2022 nor FY2023 Annual Report presents a full three-part Company cash flow statement for FY2022 (checked both directly - https://www.vidabank.co.uk/media/zhoj0swe/annual-report-and-accounts-2023.pdf - and via the FY2023 report's own prior-year comparative column, which is likewise not present.) The FY2023 Annual Report's Note 25 gives only a partial Group-basis operating reconciliation ending at 'Net cash flows from operating activities: £68,297k' for FY2022 - not on the same (Company) basis as every other populated year here and with no investing/financing breakdown at all, so it is not shown rather than presented as a misleadingly partial column.
+FY2018 RESTATEMENT NOTE: Belmont Green Finance Limited's own, originally-filed FY2018 Annual Report (https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzIzMzYzMjc1OWFkaXF6a2N4/document?format=pdf&amp;download=0) reported total Company assets of only £132,973k, Loans to customers of just £450k (almost all mortgage exposure sat in warehouse/securitisation special-purpose vehicles, recognised via 'Other receivables' subordinated loan notes rather than on the Company's own balance sheet), and a full three-part Company cash flow statement with operating activities of £(45,851)k / financing activities of £44,782k. The subsequent FY2019 Annual Report's Note 28(d) explains that this presentation was reassessed: 'following a thorough analysis and in accordance with IFRS9, it has been established that BGFL retains substantial risks and rewards' of the securitised mortgage assets, so the FY2019 Annual Report's own restated FY2018 comparative brings the securitised loan book onto the Company's balance sheet (Loans to customers restated to £1,197,862k) with an offsetting 'Deemed loan due to Group undertakings' liability, and correspondingly grosses up the FY2018 Company cash flow statement's operating and financing activities (to £(763,195)k and £762,125k respectively) with no change to the net cash movement or cash balances. This workbook uses the FY2019 Annual Report's restated FY2018 figures throughout the Balance Sheet, Cash Flow Statement and Statement of Changes in Equity sheets, for consistency with FY2019 onwards' presentation (which uses the same 'Deemed loan due to Group undertakings' convention) - not the originally-filed FY2018 Annual Report's figures, which are noted here for transparency rather than blended in.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A24:I24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5699,7 +7085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -5708,6 +7094,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5753,6 +7142,21 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020 (£'000)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019 (£'000)</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018 (£'000)</t>
         </is>
       </c>
     </row>
@@ -5767,6 +7171,9 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -5789,6 +7196,15 @@
       <c r="F5" s="6" t="n">
         <v>1124656</v>
       </c>
+      <c r="G5" s="6" t="n">
+        <v>1150485</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>1411656</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>1080264</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -5811,6 +7227,15 @@
       <c r="F6" s="6" t="n">
         <v>643597</v>
       </c>
+      <c r="G6" s="6" t="n">
+        <v>455349</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>184957</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>109901</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -5833,6 +7258,15 @@
       <c r="F7" s="6" t="n">
         <v>44090</v>
       </c>
+      <c r="G7" s="6" t="n">
+        <v>35694</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>7654</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>2354</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -5854,6 +7288,15 @@
       </c>
       <c r="F8" s="5" t="n">
         <v>1812343</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>1641528</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>1604267</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>1192519</v>
       </c>
     </row>
     <row r="9">
@@ -5867,6 +7310,9 @@
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -5889,6 +7335,15 @@
       <c r="F10" s="6" t="n">
         <v>1217</v>
       </c>
+      <c r="G10" s="6" t="n">
+        <v>898</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>661</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>549</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -5911,6 +7366,15 @@
       <c r="F11" s="6" t="n">
         <v>3889</v>
       </c>
+      <c r="G11" s="6" t="n">
+        <v>3834</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1550</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>966</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -5933,6 +7397,15 @@
       <c r="F12" s="6" t="n">
         <v>2541</v>
       </c>
+      <c r="G12" s="6" t="n">
+        <v>2739</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1889</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>183</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -5954,6 +7427,15 @@
       </c>
       <c r="F13" s="5" t="n">
         <v>7647</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>7471</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>4100</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>1698</v>
       </c>
     </row>
     <row r="14">
@@ -5967,6 +7449,9 @@
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -5999,6 +7484,21 @@
           <t>2.43%</t>
         </is>
       </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>2.17%</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -6029,6 +7529,21 @@
       <c r="F16" s="6" t="inlineStr">
         <is>
           <t>5.77%</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>7.67%</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>24.68%</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>7.77%</t>
         </is>
       </c>
     </row>
@@ -6039,13 +7554,15 @@
 FY2025/FY2024: Vida Bank Limited Annual Report and Accounts 2025, p.79-81 (Note 14, Expected credit losses) - https://www.vidabank.co.uk/media/pkmnxlqg/annual-report-and-accounts-2025-company.pdf
 FY2023/FY2022: Belmont Green Finance Limited Annual Report and Accounts 2023, p.168-169 (Note 14, Expected credit losses) - https://www.vidabank.co.uk/media/zhoj0swe/annual-report-and-accounts-2023.pdf
 FY2021: Belmont Green Finance Limited Annual Report and Accounts 2021, p.132-133 (Note 13, Expected credit losses) - https://www.vidabank.co.uk/media/p3wau0ms/annual-report-and-accounts-2021.pdf
+FY2020/FY2019: Belmont Green Finance Limited Annual Report and Accounts 2020, Note 13 (Expected credit losses) and Note 23 (Risk management - loans to customers by IFRS 9 stage, Low/High risk sub-bucketed within Stage 1/Stage 2, summed here into the single Stage 1/Stage 2 rows used throughout this sheet) - https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzMwNjUyMjA5MmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2018: Belmont Green Finance Limited Annual Report and Accounts 2019, FY2018 comparative column of the same Note 23-equivalent risk management table (Low/High risk sub-buckets summed the same way) - https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzI4NjAzOTYwNWFkaXF6a2N4/document?format=pdf&amp;download=0. Belmont Green's own originally-filed FY2018 Annual Report does not disclose an IFRS 9 stage split at all (only £450k of loans sat on the Company balance sheet that year - see FY2018_RESTATEMENT_NOTE on the Cash Flow Statement sheet), so the FY2019 Annual Report's restated comparative is the only source for FY2018 on this sheet.
 NPL ratio = Stage 3 gross balance / Total gross balance. Coverage ratio = Stage 3 impairment provision / Stage 3 gross balance. Both derived, not separately disclosed by the Bank.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A18:I18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6057,7 +7574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -6066,6 +7583,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6113,6 +7633,21 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -6129,6 +7664,9 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
     </row>
     <row r="6" ht="130" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -6136,13 +7674,13 @@
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
 FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
 FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-No Pillar 3 disclosure exists for FY2021-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet).</t>
+No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:I6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6154,7 +7692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -6163,6 +7701,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6210,6 +7751,21 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -6230,6 +7786,9 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
     </row>
     <row r="6" ht="130" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -6237,13 +7796,13 @@
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
 FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
 FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-No Pillar 3 disclosure exists for FY2021-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet).</t>
+No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:I6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6255,7 +7814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -6264,6 +7823,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6311,6 +7873,21 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -6327,6 +7904,9 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -6341,14 +7921,14 @@
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
 FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
 FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-No Pillar 3 disclosure exists for FY2021-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet).</t>
+No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A7:I7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/VIDA FINANCIALS.xlsx
+++ b/banks/VIDA FINANCIALS.xlsx
@@ -4549,7 +4549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -4673,7 +4673,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Debt securities</t>
+          <t>Total debt securities</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
@@ -4692,50 +4692,34 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Loans to customers</t>
+          <t>Debt securities - UK Government securities (FVOCI)</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>2301831</v>
+        <v>537441</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>1866006</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>1712271</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>1761996</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>1811577</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>1635572</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>1599800</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>1197862</v>
-      </c>
+        <v>34135</v>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Derivative financial instruments</t>
+          <t>Debt securities - Supranational bonds (FVOCI)</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>10198</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>2123</v>
-      </c>
+        <v>167080</v>
+      </c>
+      <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n">
-        <v>731</v>
-      </c>
+      <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
       <c r="G8" s="6" t="n"/>
       <c r="H8" s="6" t="n"/>
@@ -4744,301 +4728,293 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Other receivables</t>
+          <t>Debt securities - Covered bonds (FVOCI)</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>71715</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>16412</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>34000</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>13982</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>11399</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>15207</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>21901</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>25813</v>
-      </c>
+        <v>115248</v>
+      </c>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Deferred taxation asset</t>
+          <t>Loans to customers</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>15299</v>
+        <v>2301831</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>13565</v>
+        <v>1866006</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>13565</v>
+        <v>1712271</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>13565</v>
+        <v>1761996</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>12975</v>
+        <v>1811577</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>11602</v>
+        <v>1635572</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>10283</v>
+        <v>1599800</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>6007</v>
+        <v>1197862</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Investment in subsidiaries</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
+          <t>Derivative financial instruments</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>10198</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>2123</v>
+      </c>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
+      <c r="E11" s="6" t="n">
+        <v>731</v>
+      </c>
       <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n">
-        <v>9000</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>9000</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>9000</v>
-      </c>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Property, plant and equipment</t>
+          <t>Other receivables</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>1343</v>
+        <v>71715</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>1551</v>
+        <v>16412</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>401</v>
+        <v>34000</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>965</v>
+        <v>13982</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>2407</v>
+        <v>11399</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>3795</v>
+        <v>15207</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>5334</v>
+        <v>21901</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>1249</v>
+        <v>25813</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Intangible assets</t>
+          <t>Deferred taxation asset</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>1316</v>
+        <v>15299</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>2190</v>
+        <v>13565</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2704</v>
+        <v>13565</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2837</v>
+        <v>13565</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>2408</v>
+        <v>12975</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1117</v>
+        <v>11602</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>317</v>
+        <v>10283</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>261</v>
+        <v>6007</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Corporation tax</t>
+          <t>Investment in subsidiaries</t>
         </is>
       </c>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n">
-        <v>25</v>
-      </c>
+      <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="6" t="n"/>
+      <c r="G14" s="6" t="n">
+        <v>9000</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>9000</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Total assets</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>3476346</v>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>2079467</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>1780102</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>1809020</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>1854266</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>1694401</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>1650714</v>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v>1245872</v>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>1343</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>1551</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>401</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>965</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>2407</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>3795</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>5334</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1249</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Liabilities</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="6" t="n"/>
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Intangible assets</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>1316</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>2190</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>2704</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>2837</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>2408</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>1117</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>317</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>261</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Retail deposits</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n">
-        <v>2425702</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>173113</v>
-      </c>
+          <t>Corporation tax</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
+      <c r="E17" s="6" t="n">
+        <v>25</v>
+      </c>
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="6" t="n"/>
       <c r="H17" s="6" t="n"/>
       <c r="I17" s="6" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Amounts owed to credit institutions</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>40345</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>74254</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>44437</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>15188</v>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>15336</v>
-      </c>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-      <c r="I18" s="6" t="n"/>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>3476346</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2079467</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1780102</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1809020</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1854266</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>1694401</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>1650714</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>1245872</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Deemed loan due to Group undertakings</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>767720</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>1659540</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>1544083</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>1606178</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>1690865</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>1521161</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>1484952</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>1108999</v>
-      </c>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Derivative financial liabilities</t>
+          <t>Retail deposits</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>19403</v>
+        <v>2425702</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>184</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>4727</v>
-      </c>
+        <v>173113</v>
+      </c>
+      <c r="D20" s="6" t="n"/>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
@@ -5048,70 +5024,74 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Other liabilities</t>
+          <t>Amounts owed to credit institutions</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>44269</v>
+        <v>40345</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>7067</v>
+        <v>74254</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>64722</v>
+        <v>44437</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>56584</v>
+        <v>15188</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>21050</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>48390</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>50689</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>36696</v>
-      </c>
+        <v>15336</v>
+      </c>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Provisions</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
+          <t>Deemed loan due to Group undertakings</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>767720</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>1659540</v>
+      </c>
       <c r="D22" s="6" t="n">
-        <v>64</v>
+        <v>1544083</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>64</v>
+        <v>1606178</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>374</v>
+        <v>1690865</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>604</v>
-      </c>
-      <c r="H22" s="6" t="n"/>
-      <c r="I22" s="6" t="n"/>
+        <v>1521161</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>1484952</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>1108999</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Corporation tax</t>
+          <t>Derivative financial liabilities</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>1128</v>
+        <v>19403</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>229</v>
-      </c>
-      <c r="D23" s="6" t="n"/>
+        <v>184</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>4727</v>
+      </c>
       <c r="E23" s="6" t="n"/>
       <c r="F23" s="6" t="n"/>
       <c r="G23" s="6" t="n"/>
@@ -5119,194 +5099,267 @@
       <c r="I23" s="6" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Total liabilities</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>3298567</v>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>1914387</v>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>1658033</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>1678014</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>1727625</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>1570155</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>1535641</v>
-      </c>
-      <c r="I24" s="5" t="n">
-        <v>1145695</v>
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Other liabilities</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>44269</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>7067</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>64722</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>56584</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>21050</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>48390</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>50689</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>36696</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Shareholders' equity</t>
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Provisions</t>
         </is>
       </c>
       <c r="B25" s="6" t="n"/>
       <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="n"/>
-      <c r="G25" s="6" t="n"/>
+      <c r="D25" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>374</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>604</v>
+      </c>
       <c r="H25" s="6" t="n"/>
       <c r="I25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
+          <t>Corporation tax</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>1128</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>229</v>
+      </c>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>3298567</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>1914387</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>1658033</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>1678014</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>1727625</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>1570155</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>1535641</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>1145695</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Shareholders' equity</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
           <t>Called up share capital</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B29" s="6" t="n">
         <v>36156</v>
       </c>
-      <c r="C26" s="6" t="n">
+      <c r="C29" s="6" t="n">
         <v>241039</v>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D29" s="6" t="n">
         <v>204462</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E29" s="6" t="n">
         <v>204462</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="F29" s="6" t="n">
         <v>204462</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="G29" s="6" t="n">
         <v>196162</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="H29" s="6" t="n">
         <v>168313</v>
       </c>
-      <c r="I26" s="6" t="n">
+      <c r="I29" s="6" t="n">
         <v>129642</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Other reserves</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B30" s="6" t="n">
         <v>-398</v>
       </c>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-      <c r="I27" s="6" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Retained profit/(losses)</t>
         </is>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B31" s="6" t="n">
         <v>142021</v>
       </c>
-      <c r="C28" s="6" t="n">
+      <c r="C31" s="6" t="n">
         <v>-75959</v>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D31" s="6" t="n">
         <v>-82393</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E31" s="6" t="n">
         <v>-73456</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F31" s="6" t="n">
         <v>-77821</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="G31" s="6" t="n">
         <v>-71916</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="H31" s="6" t="n">
         <v>-53240</v>
       </c>
-      <c r="I28" s="6" t="n">
+      <c r="I31" s="6" t="n">
         <v>-29464</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>Total shareholders' equity</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B32" s="5" t="n">
         <v>177779</v>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C32" s="5" t="n">
         <v>165080</v>
       </c>
-      <c r="D29" s="5" t="n">
+      <c r="D32" s="5" t="n">
         <v>122069</v>
       </c>
-      <c r="E29" s="5" t="n">
+      <c r="E32" s="5" t="n">
         <v>131006</v>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="F32" s="5" t="n">
         <v>126641</v>
       </c>
-      <c r="G29" s="5" t="n">
+      <c r="G32" s="5" t="n">
         <v>124246</v>
       </c>
-      <c r="H29" s="5" t="n">
+      <c r="H32" s="5" t="n">
         <v>115073</v>
       </c>
-      <c r="I29" s="5" t="n">
+      <c r="I32" s="5" t="n">
         <v>100178</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>Total liabilities and equity</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B33" s="5" t="n">
         <v>3476346</v>
       </c>
-      <c r="C30" s="5" t="n">
+      <c r="C33" s="5" t="n">
         <v>2079467</v>
       </c>
-      <c r="D30" s="5" t="n">
+      <c r="D33" s="5" t="n">
         <v>1780102</v>
       </c>
-      <c r="E30" s="5" t="n">
+      <c r="E33" s="5" t="n">
         <v>1809020</v>
       </c>
-      <c r="F30" s="5" t="n">
+      <c r="F33" s="5" t="n">
         <v>1854266</v>
       </c>
-      <c r="G30" s="5" t="n">
+      <c r="G33" s="5" t="n">
         <v>1694401</v>
       </c>
-      <c r="H30" s="5" t="n">
+      <c r="H33" s="5" t="n">
         <v>1650714</v>
       </c>
-      <c r="I30" s="5" t="n">
+      <c r="I33" s="5" t="n">
         <v>1245872</v>
       </c>
     </row>
-    <row r="32" ht="180" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
+    <row r="35" ht="180" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>Sources - Vida Bank Limited's own Company (non-consolidated) Statement of Financial Position, £'000:
 FY2025: Vida Bank Limited Annual Report and Accounts 2025 (Company), p.53 - https://www.vidabank.co.uk/media/pkmnxlqg/annual-report-and-accounts-2025-company.pdf
@@ -5317,13 +5370,16 @@
 FY2020: Belmont Green Finance Limited Annual Report and Accounts 2020, Company Statement of Financial Position - https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzMwNjUyMjA5MmFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2019: Belmont Green Finance Limited Annual Report and Accounts 2019, Company Statement of Financial Position - https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzI4NjAzOTYwNWFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2018: taken from the FY2019 Annual Report's own restated FY2018 comparative column (same document as above) - see FY2018_RESTATEMENT_NOTE (on the Cash Flow Statement sheet's source note) for why the restated figures are used in place of Belmont Green's originally-filed FY2018 Annual Report (https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzIzMzYzMjc1OWFkaXF6a2N4/document?format=pdf&amp;download=0).
+DEBT SECURITIES BREAKDOWN: the 'Debt securities - ...' sub-rows below the headline 'Total debt securities' line are transcribed from each year's own Note 15 'Debt securities'. All debt securities are held at fair value through other comprehensive income (FVOCI) in both years - Note 11 'Financial instruments' (FY2025 AR, pp.75-76) shows the full £819,770k FY2025 balance and £34,135k FY2024 balance classified entirely as FVOCI, with nothing at amortised cost or FVTPL - so no measurement-basis split applies. Note 15 does split by issuer type:
+FY2025: UK Government securities £537,441k, Supranational bonds £167,080k, Covered bonds £115,248k - Note 15, p.81 - https://www.vidabank.co.uk/media/pkmnxlqg/annual-report-and-accounts-2025-company.pdf. These three lines sum to £819,769k against the note's own stated total of £819,770k - a £1k rounding difference present in the source document itself, not a transcription error (the UK Government securities sub-row above is left at the source's own £537,441k rather than plugged to force an exact tie-out).
+FY2024: 100% UK Government securities (labelled 'Gilts' in this year's own note) - Note 15, p.102 - https://www.vidabank.co.uk/media/emghy4z2/annual-report-and-accounts-2024-company.pdf. No issuer-type split applies for FY2024 since the full £34,135k balance is one category.
 Balance Sheet / Statement of Changes in Equity are on Vida Bank Limited's own Company (non-consolidated) basis in every year, matching the Cash Flow Statement sheet's basis (see its own ENTITY_NOTE). Profit &amp; Loss is on the Company basis for FY2025/FY2024 only (Vida's own Company Statement of Comprehensive Income exists for those two years); for FY2023/FY2022/FY2021/FY2020/FY2019, the Company took the section 408 Companies Act 2006 exemption and published no separate Company income statement (only a one-line narrative profit/loss-after-tax figure, which ties to the equity ladder's own movement for that year), so the Group/Consolidated income statement is shown instead for those years. FY2018's own Annual Report did present a Company income statement, but it is not used here either, for consistency with every other pre-2024 year's Group-basis figures (see INCOME_STATEMENT_SOURCES for detail) - a genuine basis difference, not forced to a single basis.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A35:I35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5608,33 +5664,33 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Administrative expenses</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="5" t="n">
         <v>-42450</v>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="5" t="n">
         <v>-34231</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="5" t="n">
         <v>-32438</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="5" t="n">
         <v>-35502</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="5" t="n">
         <v>-30932</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="5" t="n">
         <v>-28043</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="5" t="n">
         <v>-31642</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="5" t="n">
         <v>-25132</v>
       </c>
     </row>

--- a/banks/VIDA FINANCIALS.xlsx
+++ b/banks/VIDA FINANCIALS.xlsx
@@ -3386,12 +3386,36 @@
           <t>16.2%</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="130" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -3399,7 +3423,12 @@
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
 FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
 FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.</t>
+BASIS DETERMINATION, made 2026-09-15 by reading section 1.3 'Scope' of both reports directly (they are word-for-word identical on this point). Verbatim: 'VGHL is a financial holding company and it is a CRR consolidation entity. This Pillar 3 report is prepared on a consolidated basis. Vida Bank Limited ("VBL") is the principal regulated subsidiary of the Group. The same basis of consolidation is used for the preparation of the Group's Annual Report and Accounts as is used for regulatory reporting.' Section 1.2 'Basis of Disclosure' adds, equally verbatim: 'Regulatory ratios are presented on a Group-basis only.' Three consequences follow, and they are why the figures above are kept rather than demoted to memo rows. (1) VGHL is not an incidental parent that merely happens to contain the bank - it is the CRR CONSOLIDATION ENTITY, i.e. the level at which the PRA actually sets and measures Vida's regulatory capital requirement, with VBL as the principal regulated subsidiary. This is the smallest regulatory group VBL belongs to. (2) No VBL-solo ratio exists to prefer over it: 'Group-basis only' is the publisher's own statement that the solo figures are not disclosed anywhere, so the choice is between the consolidated figure and nothing at all - not between a group figure and a suppressed entity figure. (3) The Group and the Annual Report use the same basis of consolidation, so these ratios are reconcilable to the accounts in this workbook rather than sitting on an unrelated perimeter. Accordingly every Pillar 3 sheet in this workbook carries the subtitle 'Vida Group Holdings basis' so the reader is never shown a consolidated ratio labelled as an entity one - the project rule this workbook observes is that group figures are never SUBSTITUTED for entity figures unlabelled, which is a different thing from refusing to report the only regulatory ratio that exists. Note also that both reports are reduced-scope Article 433b disclosures ('small and non-complex institution', UK CRR Article 4(145)), which is why the metric set here is narrower than a large bank's - it is a permitted reduction, not an omission.
+No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.
+RE-VERIFIED 2026-09-12 (disclosure audit): the pre-authorisation gap is STRUCTURAL, independently confirmed against the Companies House register rather than the workbook's own prior claim. Company 09837692 was incorporated 22 October 2015 and traded as 'Belmont Green Finance Ltd' (22 Oct 2015 - 10 Jun 2019) and then 'Belmont Green Finance Limited' (10 Jun 2019 - 25 Nov 2024), only taking the name 'Vida Bank Limited' on 25 November 2024 - six days after the 19 November 2024 PRA authorisation. No Pillar 3 obligation can therefore exist for FY2018-FY2023, so those years are blank by regulation, not by omission.
+SDDT - EXPLICIT NEGATIVE, recorded 2026-09-15 (cross-bank SDDT date-fit pass) so that a future pass does not wrongly apply the Small Domestic Deposit Taker exemption to this workbook's gap years. Vida DOES hold the SDDT opt-in, but it is far too recent to explain anything here. The Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv) carries three SDDT rows for FRN 738741, 'Vida Bank Limited': (a) 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub rule 'Ru 3.1', waiver ref 'A00011924P.pdf', START DATE 03/04/2026, no end date; plus two eligibility-criteria modifications under sub rules 'Ru 1.2' and 'Ru 2.1(9)', both ref 'A00010069P.pdf', start 25/03/2026, end 25/03/2029. Only row (a) matters: Rule 3.1 is the actual opt-in that removes the Pillar 3 disclosure obligation, whereas rules 1.2 and 2.1(9) merely modify eligibility CRITERIA (2.1(9) waives the 'any parent undertaking of the firm is a UK undertaking' test) and are not themselves evidence of any disclosure exemption.
+DATE FIT - IT DOES NOT FIT. Vida's accounting reference date is 31 DECEMBER, confirmed at Companies House (company 09837692, an unbroken run of accounts to 31 December from 2019 to 2025). The outstanding Pillar 3 gap years are FY2021, FY2022 and FY2023, which ended 31 December 2021, 2022 and 2023 respectively. The Rule 3.1 modification began 3 APRIL 2026 - between two and four and a half years AFTER every one of those year-ends, and after the FY2025 year-end too. A modification cannot explain a gap that predates it, so the SDDT regime explains NONE of the FY2021-FY2023 blanks.
+Those gaps already have a different and fully sufficient explanation, set out immediately above, and it is left exactly as it stands: the entity was not PRA-authorised as a deposit-taker until 19 November 2024, so no Pillar 3 obligation existed in any of those years. That is a structural pre-authorisation absence, not an exemption. The register finding changes no cell in this workbook. Its only forward-looking value is that from 3 April 2026 Vida is an SDDT, so Pillar 3 documents of the kind used for FY2024 and FY2025 should not be expected for FY2026 onward. Note finally that this is the SDDT DISCLOSURE exemption, which is in force now - not the separate SDDT CAPITAL regime that begins 1 January 2027; the two are easy to conflate and must not be.</t>
         </is>
       </c>
     </row>
@@ -3504,12 +3533,36 @@
       <c r="C4" s="6" t="n">
         <v>160316</v>
       </c>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -3524,7 +3577,12 @@
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
 FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
 FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.</t>
+BASIS DETERMINATION, made 2026-09-15 by reading section 1.3 'Scope' of both reports directly (they are word-for-word identical on this point). Verbatim: 'VGHL is a financial holding company and it is a CRR consolidation entity. This Pillar 3 report is prepared on a consolidated basis. Vida Bank Limited ("VBL") is the principal regulated subsidiary of the Group. The same basis of consolidation is used for the preparation of the Group's Annual Report and Accounts as is used for regulatory reporting.' Section 1.2 'Basis of Disclosure' adds, equally verbatim: 'Regulatory ratios are presented on a Group-basis only.' Three consequences follow, and they are why the figures above are kept rather than demoted to memo rows. (1) VGHL is not an incidental parent that merely happens to contain the bank - it is the CRR CONSOLIDATION ENTITY, i.e. the level at which the PRA actually sets and measures Vida's regulatory capital requirement, with VBL as the principal regulated subsidiary. This is the smallest regulatory group VBL belongs to. (2) No VBL-solo ratio exists to prefer over it: 'Group-basis only' is the publisher's own statement that the solo figures are not disclosed anywhere, so the choice is between the consolidated figure and nothing at all - not between a group figure and a suppressed entity figure. (3) The Group and the Annual Report use the same basis of consolidation, so these ratios are reconcilable to the accounts in this workbook rather than sitting on an unrelated perimeter. Accordingly every Pillar 3 sheet in this workbook carries the subtitle 'Vida Group Holdings basis' so the reader is never shown a consolidated ratio labelled as an entity one - the project rule this workbook observes is that group figures are never SUBSTITUTED for entity figures unlabelled, which is a different thing from refusing to report the only regulatory ratio that exists. Note also that both reports are reduced-scope Article 433b disclosures ('small and non-complex institution', UK CRR Article 4(145)), which is why the metric set here is narrower than a large bank's - it is a permitted reduction, not an omission.
+No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.
+RE-VERIFIED 2026-09-12 (disclosure audit): the pre-authorisation gap is STRUCTURAL, independently confirmed against the Companies House register rather than the workbook's own prior claim. Company 09837692 was incorporated 22 October 2015 and traded as 'Belmont Green Finance Ltd' (22 Oct 2015 - 10 Jun 2019) and then 'Belmont Green Finance Limited' (10 Jun 2019 - 25 Nov 2024), only taking the name 'Vida Bank Limited' on 25 November 2024 - six days after the 19 November 2024 PRA authorisation. No Pillar 3 obligation can therefore exist for FY2018-FY2023, so those years are blank by regulation, not by omission.
+SDDT - EXPLICIT NEGATIVE, recorded 2026-09-15 (cross-bank SDDT date-fit pass) so that a future pass does not wrongly apply the Small Domestic Deposit Taker exemption to this workbook's gap years. Vida DOES hold the SDDT opt-in, but it is far too recent to explain anything here. The Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv) carries three SDDT rows for FRN 738741, 'Vida Bank Limited': (a) 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub rule 'Ru 3.1', waiver ref 'A00011924P.pdf', START DATE 03/04/2026, no end date; plus two eligibility-criteria modifications under sub rules 'Ru 1.2' and 'Ru 2.1(9)', both ref 'A00010069P.pdf', start 25/03/2026, end 25/03/2029. Only row (a) matters: Rule 3.1 is the actual opt-in that removes the Pillar 3 disclosure obligation, whereas rules 1.2 and 2.1(9) merely modify eligibility CRITERIA (2.1(9) waives the 'any parent undertaking of the firm is a UK undertaking' test) and are not themselves evidence of any disclosure exemption.
+DATE FIT - IT DOES NOT FIT. Vida's accounting reference date is 31 DECEMBER, confirmed at Companies House (company 09837692, an unbroken run of accounts to 31 December from 2019 to 2025). The outstanding Pillar 3 gap years are FY2021, FY2022 and FY2023, which ended 31 December 2021, 2022 and 2023 respectively. The Rule 3.1 modification began 3 APRIL 2026 - between two and four and a half years AFTER every one of those year-ends, and after the FY2025 year-end too. A modification cannot explain a gap that predates it, so the SDDT regime explains NONE of the FY2021-FY2023 blanks.
+Those gaps already have a different and fully sufficient explanation, set out immediately above, and it is left exactly as it stands: the entity was not PRA-authorised as a deposit-taker until 19 November 2024, so no Pillar 3 obligation existed in any of those years. That is a structural pre-authorisation absence, not an exemption. The register finding changes no cell in this workbook. Its only forward-looking value is that from 3 April 2026 Vida is an SDDT, so Pillar 3 documents of the kind used for FY2024 and FY2025 should not be expected for FY2026 onward. Note finally that this is the SDDT DISCLOSURE exemption, which is in force now - not the separate SDDT CAPITAL regime that begins 1 January 2027; the two are easy to conflate and must not be.</t>
         </is>
       </c>
     </row>
@@ -3634,12 +3692,36 @@
           <t>16.2%</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="130" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -3647,7 +3729,12 @@
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
 FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
 FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.</t>
+BASIS DETERMINATION, made 2026-09-15 by reading section 1.3 'Scope' of both reports directly (they are word-for-word identical on this point). Verbatim: 'VGHL is a financial holding company and it is a CRR consolidation entity. This Pillar 3 report is prepared on a consolidated basis. Vida Bank Limited ("VBL") is the principal regulated subsidiary of the Group. The same basis of consolidation is used for the preparation of the Group's Annual Report and Accounts as is used for regulatory reporting.' Section 1.2 'Basis of Disclosure' adds, equally verbatim: 'Regulatory ratios are presented on a Group-basis only.' Three consequences follow, and they are why the figures above are kept rather than demoted to memo rows. (1) VGHL is not an incidental parent that merely happens to contain the bank - it is the CRR CONSOLIDATION ENTITY, i.e. the level at which the PRA actually sets and measures Vida's regulatory capital requirement, with VBL as the principal regulated subsidiary. This is the smallest regulatory group VBL belongs to. (2) No VBL-solo ratio exists to prefer over it: 'Group-basis only' is the publisher's own statement that the solo figures are not disclosed anywhere, so the choice is between the consolidated figure and nothing at all - not between a group figure and a suppressed entity figure. (3) The Group and the Annual Report use the same basis of consolidation, so these ratios are reconcilable to the accounts in this workbook rather than sitting on an unrelated perimeter. Accordingly every Pillar 3 sheet in this workbook carries the subtitle 'Vida Group Holdings basis' so the reader is never shown a consolidated ratio labelled as an entity one - the project rule this workbook observes is that group figures are never SUBSTITUTED for entity figures unlabelled, which is a different thing from refusing to report the only regulatory ratio that exists. Note also that both reports are reduced-scope Article 433b disclosures ('small and non-complex institution', UK CRR Article 4(145)), which is why the metric set here is narrower than a large bank's - it is a permitted reduction, not an omission.
+No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.
+RE-VERIFIED 2026-09-12 (disclosure audit): the pre-authorisation gap is STRUCTURAL, independently confirmed against the Companies House register rather than the workbook's own prior claim. Company 09837692 was incorporated 22 October 2015 and traded as 'Belmont Green Finance Ltd' (22 Oct 2015 - 10 Jun 2019) and then 'Belmont Green Finance Limited' (10 Jun 2019 - 25 Nov 2024), only taking the name 'Vida Bank Limited' on 25 November 2024 - six days after the 19 November 2024 PRA authorisation. No Pillar 3 obligation can therefore exist for FY2018-FY2023, so those years are blank by regulation, not by omission.
+SDDT - EXPLICIT NEGATIVE, recorded 2026-09-15 (cross-bank SDDT date-fit pass) so that a future pass does not wrongly apply the Small Domestic Deposit Taker exemption to this workbook's gap years. Vida DOES hold the SDDT opt-in, but it is far too recent to explain anything here. The Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv) carries three SDDT rows for FRN 738741, 'Vida Bank Limited': (a) 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub rule 'Ru 3.1', waiver ref 'A00011924P.pdf', START DATE 03/04/2026, no end date; plus two eligibility-criteria modifications under sub rules 'Ru 1.2' and 'Ru 2.1(9)', both ref 'A00010069P.pdf', start 25/03/2026, end 25/03/2029. Only row (a) matters: Rule 3.1 is the actual opt-in that removes the Pillar 3 disclosure obligation, whereas rules 1.2 and 2.1(9) merely modify eligibility CRITERIA (2.1(9) waives the 'any parent undertaking of the firm is a UK undertaking' test) and are not themselves evidence of any disclosure exemption.
+DATE FIT - IT DOES NOT FIT. Vida's accounting reference date is 31 DECEMBER, confirmed at Companies House (company 09837692, an unbroken run of accounts to 31 December from 2019 to 2025). The outstanding Pillar 3 gap years are FY2021, FY2022 and FY2023, which ended 31 December 2021, 2022 and 2023 respectively. The Rule 3.1 modification began 3 APRIL 2026 - between two and four and a half years AFTER every one of those year-ends, and after the FY2025 year-end too. A modification cannot explain a gap that predates it, so the SDDT regime explains NONE of the FY2021-FY2023 blanks.
+Those gaps already have a different and fully sufficient explanation, set out immediately above, and it is left exactly as it stands: the entity was not PRA-authorised as a deposit-taker until 19 November 2024, so no Pillar 3 obligation existed in any of those years. That is a structural pre-authorisation absence, not an exemption. The register finding changes no cell in this workbook. Its only forward-looking value is that from 3 April 2026 Vida is an SDDT, so Pillar 3 documents of the kind used for FY2024 and FY2025 should not be expected for FY2026 onward. Note finally that this is the SDDT DISCLOSURE exemption, which is in force now - not the separate SDDT CAPITAL regime that begins 1 January 2027; the two are easy to conflate and must not be.</t>
         </is>
       </c>
     </row>
@@ -3752,12 +3839,36 @@
       <c r="C4" s="6" t="n">
         <v>986809</v>
       </c>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="130" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -3765,7 +3876,12 @@
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
 FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
 FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.</t>
+BASIS DETERMINATION, made 2026-09-15 by reading section 1.3 'Scope' of both reports directly (they are word-for-word identical on this point). Verbatim: 'VGHL is a financial holding company and it is a CRR consolidation entity. This Pillar 3 report is prepared on a consolidated basis. Vida Bank Limited ("VBL") is the principal regulated subsidiary of the Group. The same basis of consolidation is used for the preparation of the Group's Annual Report and Accounts as is used for regulatory reporting.' Section 1.2 'Basis of Disclosure' adds, equally verbatim: 'Regulatory ratios are presented on a Group-basis only.' Three consequences follow, and they are why the figures above are kept rather than demoted to memo rows. (1) VGHL is not an incidental parent that merely happens to contain the bank - it is the CRR CONSOLIDATION ENTITY, i.e. the level at which the PRA actually sets and measures Vida's regulatory capital requirement, with VBL as the principal regulated subsidiary. This is the smallest regulatory group VBL belongs to. (2) No VBL-solo ratio exists to prefer over it: 'Group-basis only' is the publisher's own statement that the solo figures are not disclosed anywhere, so the choice is between the consolidated figure and nothing at all - not between a group figure and a suppressed entity figure. (3) The Group and the Annual Report use the same basis of consolidation, so these ratios are reconcilable to the accounts in this workbook rather than sitting on an unrelated perimeter. Accordingly every Pillar 3 sheet in this workbook carries the subtitle 'Vida Group Holdings basis' so the reader is never shown a consolidated ratio labelled as an entity one - the project rule this workbook observes is that group figures are never SUBSTITUTED for entity figures unlabelled, which is a different thing from refusing to report the only regulatory ratio that exists. Note also that both reports are reduced-scope Article 433b disclosures ('small and non-complex institution', UK CRR Article 4(145)), which is why the metric set here is narrower than a large bank's - it is a permitted reduction, not an omission.
+No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.
+RE-VERIFIED 2026-09-12 (disclosure audit): the pre-authorisation gap is STRUCTURAL, independently confirmed against the Companies House register rather than the workbook's own prior claim. Company 09837692 was incorporated 22 October 2015 and traded as 'Belmont Green Finance Ltd' (22 Oct 2015 - 10 Jun 2019) and then 'Belmont Green Finance Limited' (10 Jun 2019 - 25 Nov 2024), only taking the name 'Vida Bank Limited' on 25 November 2024 - six days after the 19 November 2024 PRA authorisation. No Pillar 3 obligation can therefore exist for FY2018-FY2023, so those years are blank by regulation, not by omission.
+SDDT - EXPLICIT NEGATIVE, recorded 2026-09-15 (cross-bank SDDT date-fit pass) so that a future pass does not wrongly apply the Small Domestic Deposit Taker exemption to this workbook's gap years. Vida DOES hold the SDDT opt-in, but it is far too recent to explain anything here. The Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv) carries three SDDT rows for FRN 738741, 'Vida Bank Limited': (a) 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub rule 'Ru 3.1', waiver ref 'A00011924P.pdf', START DATE 03/04/2026, no end date; plus two eligibility-criteria modifications under sub rules 'Ru 1.2' and 'Ru 2.1(9)', both ref 'A00010069P.pdf', start 25/03/2026, end 25/03/2029. Only row (a) matters: Rule 3.1 is the actual opt-in that removes the Pillar 3 disclosure obligation, whereas rules 1.2 and 2.1(9) merely modify eligibility CRITERIA (2.1(9) waives the 'any parent undertaking of the firm is a UK undertaking' test) and are not themselves evidence of any disclosure exemption.
+DATE FIT - IT DOES NOT FIT. Vida's accounting reference date is 31 DECEMBER, confirmed at Companies House (company 09837692, an unbroken run of accounts to 31 December from 2019 to 2025). The outstanding Pillar 3 gap years are FY2021, FY2022 and FY2023, which ended 31 December 2021, 2022 and 2023 respectively. The Rule 3.1 modification began 3 APRIL 2026 - between two and four and a half years AFTER every one of those year-ends, and after the FY2025 year-end too. A modification cannot explain a gap that predates it, so the SDDT regime explains NONE of the FY2021-FY2023 blanks.
+Those gaps already have a different and fully sufficient explanation, set out immediately above, and it is left exactly as it stands: the entity was not PRA-authorised as a deposit-taker until 19 November 2024, so no Pillar 3 obligation existed in any of those years. That is a structural pre-authorisation absence, not an exemption. The register finding changes no cell in this workbook. Its only forward-looking value is that from 3 April 2026 Vida is an SDDT, so Pillar 3 documents of the kind used for FY2024 and FY2025 should not be expected for FY2026 onward. Note finally that this is the SDDT DISCLOSURE exemption, which is in force now - not the separate SDDT CAPITAL regime that begins 1 January 2027; the two are easy to conflate and must not be.</t>
         </is>
       </c>
     </row>
@@ -3783,10 +3899,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="68" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -3807,7 +3923,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Vida Group Holdings basis</t>
+          <t>Vida Group Holdings (Group/consolidated) basis, £'000. Table (OV1) - RWEAs by risk type, as disclosed. FY2018-FY2023: no Pillar 3 disclosure exists at all (see ENTITY_NOTE).</t>
         </is>
       </c>
     </row>
@@ -3819,102 +3935,208 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2025 (£'000)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2024 (£'000)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2023 (£'000)</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2022 (£'000)</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY2021 (£'000)</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>FY2020</t>
+          <t>FY2020 (£'000)</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>FY2019</t>
+          <t>FY2019 (£'000)</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>FY2018</t>
+          <t>FY2018 (£'000)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>RWA Breakdown</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="120" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>No UK OV1 (RWA-by-risk-category) template, or equivalent RWA breakdown table, exists in either Pillar 3 Disclosures document (2025 or 2024) checked this session - both are short (9-page) documents covering only the KM1 Key Metrics table already used on the other Pillar 3 sheets. Confirmed non-disclosure, not an access gap. No Pillar 3 disclosure exists at all for FY2018-FY2023 (see ENTITY_NOTE on the Cash Flow Statement sheet).</t>
+          <t>Credit risk (excluding CCR)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>936924</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>766886</v>
+      </c>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Counterparty credit risk (CCR), of which credit valuation adjustment (CVA)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>83044</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>155027</v>
+      </c>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Securitisation exposures in the non-trading book (after the cap)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>6391</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Operational risk</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>79420</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>64896</v>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Total risk weighted exposure amount (Table OV1)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1105779</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>986809</v>
+      </c>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable - entity was not a PRA-authorised bank</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable (no banking licence held in these years)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="200" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures, Table (OV1) 'RWEAs and total own funds requirements by risk type', £'000, as disclosed (DIRECTLY DISCLOSED, not derived):
+FY2025 &amp; FY2024: Vida Group Holdings plc Pillar 3 Disclosures 2025, section 3.2 'Risk-Weighted Exposures', Table (OV1), p.6 - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf. FY2024's category rows sum exactly to that table's own stated Total (986,809), matching the Total RWAs sheet's FY2024 figure exactly. FY2025's category rows sum to 1,105,779 - £1k below the table's own stated Total (1,105,780) and the Total RWAs sheet's own FY2025 figure - a one £'000 rounding artifact in the source table itself (each row independently rounded to the nearest £'000 before summing), not a transcription error here; the TOTAL row above shows the reconciling sum of the category rows, not the source's stated Total, per this project's convention of the category breakdown always ticking to its own components.
+This table was not identified in an earlier review of these documents (which found only the KM1 Key Metrics table used on the other Pillar 3 sheets) - a 2026-09-08 re-check located it in section 3.2 of the FY2025 report (which also carries the FY2024 comparative column, so the standalone FY2024 report did not need separately re-checking for this sheet).
+FY2018-FY2023: no Pillar 3 disclosure exists at all for any year before FY2024 (Pillar 3 only applies once the entity holds a banking licence, obtained 19 November 2024) - see ENTITY_NOTE on the Cash Flow Statement sheet.
+2026-09-15: those pre-licence years are now marked explicitly as 'Not applicable' in the rows above, rather than being left as empty cells. They were previously blank, which made them indistinguishable from a bank that simply has not been researched yet - an audit of RWA Breakdown coverage counted them as open, chaseable gaps when in fact no document can ever exist for them. This follows the same convention already used in build_afin_bank.py for the identical situation. Corroborating evidence for the licence date: Companies House (company 09837692) shows the entity's first full bank accounts made up to 31 December 2024, and FY2024 is the first year for which any Pillar 3 disclosure of any kind exists.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A12:I12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4013,12 +4235,36 @@
       <c r="C4" s="6" t="n">
         <v>2331835</v>
       </c>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -4036,12 +4282,36 @@
           <t>6.9%</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="130" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
@@ -4049,7 +4319,12 @@
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
 FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
 FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.</t>
+BASIS DETERMINATION, made 2026-09-15 by reading section 1.3 'Scope' of both reports directly (they are word-for-word identical on this point). Verbatim: 'VGHL is a financial holding company and it is a CRR consolidation entity. This Pillar 3 report is prepared on a consolidated basis. Vida Bank Limited ("VBL") is the principal regulated subsidiary of the Group. The same basis of consolidation is used for the preparation of the Group's Annual Report and Accounts as is used for regulatory reporting.' Section 1.2 'Basis of Disclosure' adds, equally verbatim: 'Regulatory ratios are presented on a Group-basis only.' Three consequences follow, and they are why the figures above are kept rather than demoted to memo rows. (1) VGHL is not an incidental parent that merely happens to contain the bank - it is the CRR CONSOLIDATION ENTITY, i.e. the level at which the PRA actually sets and measures Vida's regulatory capital requirement, with VBL as the principal regulated subsidiary. This is the smallest regulatory group VBL belongs to. (2) No VBL-solo ratio exists to prefer over it: 'Group-basis only' is the publisher's own statement that the solo figures are not disclosed anywhere, so the choice is between the consolidated figure and nothing at all - not between a group figure and a suppressed entity figure. (3) The Group and the Annual Report use the same basis of consolidation, so these ratios are reconcilable to the accounts in this workbook rather than sitting on an unrelated perimeter. Accordingly every Pillar 3 sheet in this workbook carries the subtitle 'Vida Group Holdings basis' so the reader is never shown a consolidated ratio labelled as an entity one - the project rule this workbook observes is that group figures are never SUBSTITUTED for entity figures unlabelled, which is a different thing from refusing to report the only regulatory ratio that exists. Note also that both reports are reduced-scope Article 433b disclosures ('small and non-complex institution', UK CRR Article 4(145)), which is why the metric set here is narrower than a large bank's - it is a permitted reduction, not an omission.
+No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.
+RE-VERIFIED 2026-09-12 (disclosure audit): the pre-authorisation gap is STRUCTURAL, independently confirmed against the Companies House register rather than the workbook's own prior claim. Company 09837692 was incorporated 22 October 2015 and traded as 'Belmont Green Finance Ltd' (22 Oct 2015 - 10 Jun 2019) and then 'Belmont Green Finance Limited' (10 Jun 2019 - 25 Nov 2024), only taking the name 'Vida Bank Limited' on 25 November 2024 - six days after the 19 November 2024 PRA authorisation. No Pillar 3 obligation can therefore exist for FY2018-FY2023, so those years are blank by regulation, not by omission.
+SDDT - EXPLICIT NEGATIVE, recorded 2026-09-15 (cross-bank SDDT date-fit pass) so that a future pass does not wrongly apply the Small Domestic Deposit Taker exemption to this workbook's gap years. Vida DOES hold the SDDT opt-in, but it is far too recent to explain anything here. The Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv) carries three SDDT rows for FRN 738741, 'Vida Bank Limited': (a) 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub rule 'Ru 3.1', waiver ref 'A00011924P.pdf', START DATE 03/04/2026, no end date; plus two eligibility-criteria modifications under sub rules 'Ru 1.2' and 'Ru 2.1(9)', both ref 'A00010069P.pdf', start 25/03/2026, end 25/03/2029. Only row (a) matters: Rule 3.1 is the actual opt-in that removes the Pillar 3 disclosure obligation, whereas rules 1.2 and 2.1(9) merely modify eligibility CRITERIA (2.1(9) waives the 'any parent undertaking of the firm is a UK undertaking' test) and are not themselves evidence of any disclosure exemption.
+DATE FIT - IT DOES NOT FIT. Vida's accounting reference date is 31 DECEMBER, confirmed at Companies House (company 09837692, an unbroken run of accounts to 31 December from 2019 to 2025). The outstanding Pillar 3 gap years are FY2021, FY2022 and FY2023, which ended 31 December 2021, 2022 and 2023 respectively. The Rule 3.1 modification began 3 APRIL 2026 - between two and four and a half years AFTER every one of those year-ends, and after the FY2025 year-end too. A modification cannot explain a gap that predates it, so the SDDT regime explains NONE of the FY2021-FY2023 blanks.
+Those gaps already have a different and fully sufficient explanation, set out immediately above, and it is left exactly as it stands: the entity was not PRA-authorised as a deposit-taker until 19 November 2024, so no Pillar 3 obligation existed in any of those years. That is a structural pre-authorisation absence, not an exemption. The register finding changes no cell in this workbook. Its only forward-looking value is that from 3 April 2026 Vida is an SDDT, so Pillar 3 documents of the kind used for FY2024 and FY2025 should not be expected for FY2026 onward. Note finally that this is the SDDT DISCLOSURE exemption, which is in force now - not the separate SDDT CAPITAL regime that begins 1 January 2027; the two are easy to conflate and must not be.</t>
         </is>
       </c>
     </row>
@@ -4154,12 +4429,36 @@
       <c r="C4" s="6" t="n">
         <v>167705</v>
       </c>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -4173,12 +4472,36 @@
       <c r="C5" s="6" t="n">
         <v>16046</v>
       </c>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -4196,12 +4519,36 @@
           <t>1,045%</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -4216,7 +4563,12 @@
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
 FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
 FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.</t>
+BASIS DETERMINATION, made 2026-09-15 by reading section 1.3 'Scope' of both reports directly (they are word-for-word identical on this point). Verbatim: 'VGHL is a financial holding company and it is a CRR consolidation entity. This Pillar 3 report is prepared on a consolidated basis. Vida Bank Limited ("VBL") is the principal regulated subsidiary of the Group. The same basis of consolidation is used for the preparation of the Group's Annual Report and Accounts as is used for regulatory reporting.' Section 1.2 'Basis of Disclosure' adds, equally verbatim: 'Regulatory ratios are presented on a Group-basis only.' Three consequences follow, and they are why the figures above are kept rather than demoted to memo rows. (1) VGHL is not an incidental parent that merely happens to contain the bank - it is the CRR CONSOLIDATION ENTITY, i.e. the level at which the PRA actually sets and measures Vida's regulatory capital requirement, with VBL as the principal regulated subsidiary. This is the smallest regulatory group VBL belongs to. (2) No VBL-solo ratio exists to prefer over it: 'Group-basis only' is the publisher's own statement that the solo figures are not disclosed anywhere, so the choice is between the consolidated figure and nothing at all - not between a group figure and a suppressed entity figure. (3) The Group and the Annual Report use the same basis of consolidation, so these ratios are reconcilable to the accounts in this workbook rather than sitting on an unrelated perimeter. Accordingly every Pillar 3 sheet in this workbook carries the subtitle 'Vida Group Holdings basis' so the reader is never shown a consolidated ratio labelled as an entity one - the project rule this workbook observes is that group figures are never SUBSTITUTED for entity figures unlabelled, which is a different thing from refusing to report the only regulatory ratio that exists. Note also that both reports are reduced-scope Article 433b disclosures ('small and non-complex institution', UK CRR Article 4(145)), which is why the metric set here is narrower than a large bank's - it is a permitted reduction, not an omission.
+No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.
+RE-VERIFIED 2026-09-12 (disclosure audit): the pre-authorisation gap is STRUCTURAL, independently confirmed against the Companies House register rather than the workbook's own prior claim. Company 09837692 was incorporated 22 October 2015 and traded as 'Belmont Green Finance Ltd' (22 Oct 2015 - 10 Jun 2019) and then 'Belmont Green Finance Limited' (10 Jun 2019 - 25 Nov 2024), only taking the name 'Vida Bank Limited' on 25 November 2024 - six days after the 19 November 2024 PRA authorisation. No Pillar 3 obligation can therefore exist for FY2018-FY2023, so those years are blank by regulation, not by omission.
+SDDT - EXPLICIT NEGATIVE, recorded 2026-09-15 (cross-bank SDDT date-fit pass) so that a future pass does not wrongly apply the Small Domestic Deposit Taker exemption to this workbook's gap years. Vida DOES hold the SDDT opt-in, but it is far too recent to explain anything here. The Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv) carries three SDDT rows for FRN 738741, 'Vida Bank Limited': (a) 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub rule 'Ru 3.1', waiver ref 'A00011924P.pdf', START DATE 03/04/2026, no end date; plus two eligibility-criteria modifications under sub rules 'Ru 1.2' and 'Ru 2.1(9)', both ref 'A00010069P.pdf', start 25/03/2026, end 25/03/2029. Only row (a) matters: Rule 3.1 is the actual opt-in that removes the Pillar 3 disclosure obligation, whereas rules 1.2 and 2.1(9) merely modify eligibility CRITERIA (2.1(9) waives the 'any parent undertaking of the firm is a UK undertaking' test) and are not themselves evidence of any disclosure exemption.
+DATE FIT - IT DOES NOT FIT. Vida's accounting reference date is 31 DECEMBER, confirmed at Companies House (company 09837692, an unbroken run of accounts to 31 December from 2019 to 2025). The outstanding Pillar 3 gap years are FY2021, FY2022 and FY2023, which ended 31 December 2021, 2022 and 2023 respectively. The Rule 3.1 modification began 3 APRIL 2026 - between two and four and a half years AFTER every one of those year-ends, and after the FY2025 year-end too. A modification cannot explain a gap that predates it, so the SDDT regime explains NONE of the FY2021-FY2023 blanks.
+Those gaps already have a different and fully sufficient explanation, set out immediately above, and it is left exactly as it stands: the entity was not PRA-authorised as a deposit-taker until 19 November 2024, so no Pillar 3 obligation existed in any of those years. That is a structural pre-authorisation absence, not an exemption. The register finding changes no cell in this workbook. Its only forward-looking value is that from 3 April 2026 Vida is an SDDT, so Pillar 3 documents of the kind used for FY2024 and FY2025 should not be expected for FY2026 onward. Note finally that this is the SDDT DISCLOSURE exemption, which is in force now - not the separate SDDT CAPITAL regime that begins 1 January 2027; the two are easy to conflate and must not be.</t>
         </is>
       </c>
     </row>
@@ -4322,12 +4674,36 @@
       <c r="C4" s="6" t="n">
         <v>2016146</v>
       </c>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -4341,12 +4717,36 @@
       <c r="C5" s="6" t="n">
         <v>1830180</v>
       </c>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -4364,12 +4764,36 @@
           <t>110%</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="130" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
@@ -4377,7 +4801,12 @@
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
 FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
 FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.</t>
+BASIS DETERMINATION, made 2026-09-15 by reading section 1.3 'Scope' of both reports directly (they are word-for-word identical on this point). Verbatim: 'VGHL is a financial holding company and it is a CRR consolidation entity. This Pillar 3 report is prepared on a consolidated basis. Vida Bank Limited ("VBL") is the principal regulated subsidiary of the Group. The same basis of consolidation is used for the preparation of the Group's Annual Report and Accounts as is used for regulatory reporting.' Section 1.2 'Basis of Disclosure' adds, equally verbatim: 'Regulatory ratios are presented on a Group-basis only.' Three consequences follow, and they are why the figures above are kept rather than demoted to memo rows. (1) VGHL is not an incidental parent that merely happens to contain the bank - it is the CRR CONSOLIDATION ENTITY, i.e. the level at which the PRA actually sets and measures Vida's regulatory capital requirement, with VBL as the principal regulated subsidiary. This is the smallest regulatory group VBL belongs to. (2) No VBL-solo ratio exists to prefer over it: 'Group-basis only' is the publisher's own statement that the solo figures are not disclosed anywhere, so the choice is between the consolidated figure and nothing at all - not between a group figure and a suppressed entity figure. (3) The Group and the Annual Report use the same basis of consolidation, so these ratios are reconcilable to the accounts in this workbook rather than sitting on an unrelated perimeter. Accordingly every Pillar 3 sheet in this workbook carries the subtitle 'Vida Group Holdings basis' so the reader is never shown a consolidated ratio labelled as an entity one - the project rule this workbook observes is that group figures are never SUBSTITUTED for entity figures unlabelled, which is a different thing from refusing to report the only regulatory ratio that exists. Note also that both reports are reduced-scope Article 433b disclosures ('small and non-complex institution', UK CRR Article 4(145)), which is why the metric set here is narrower than a large bank's - it is a permitted reduction, not an omission.
+No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.
+RE-VERIFIED 2026-09-12 (disclosure audit): the pre-authorisation gap is STRUCTURAL, independently confirmed against the Companies House register rather than the workbook's own prior claim. Company 09837692 was incorporated 22 October 2015 and traded as 'Belmont Green Finance Ltd' (22 Oct 2015 - 10 Jun 2019) and then 'Belmont Green Finance Limited' (10 Jun 2019 - 25 Nov 2024), only taking the name 'Vida Bank Limited' on 25 November 2024 - six days after the 19 November 2024 PRA authorisation. No Pillar 3 obligation can therefore exist for FY2018-FY2023, so those years are blank by regulation, not by omission.
+SDDT - EXPLICIT NEGATIVE, recorded 2026-09-15 (cross-bank SDDT date-fit pass) so that a future pass does not wrongly apply the Small Domestic Deposit Taker exemption to this workbook's gap years. Vida DOES hold the SDDT opt-in, but it is far too recent to explain anything here. The Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv) carries three SDDT rows for FRN 738741, 'Vida Bank Limited': (a) 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub rule 'Ru 3.1', waiver ref 'A00011924P.pdf', START DATE 03/04/2026, no end date; plus two eligibility-criteria modifications under sub rules 'Ru 1.2' and 'Ru 2.1(9)', both ref 'A00010069P.pdf', start 25/03/2026, end 25/03/2029. Only row (a) matters: Rule 3.1 is the actual opt-in that removes the Pillar 3 disclosure obligation, whereas rules 1.2 and 2.1(9) merely modify eligibility CRITERIA (2.1(9) waives the 'any parent undertaking of the firm is a UK undertaking' test) and are not themselves evidence of any disclosure exemption.
+DATE FIT - IT DOES NOT FIT. Vida's accounting reference date is 31 DECEMBER, confirmed at Companies House (company 09837692, an unbroken run of accounts to 31 December from 2019 to 2025). The outstanding Pillar 3 gap years are FY2021, FY2022 and FY2023, which ended 31 December 2021, 2022 and 2023 respectively. The Rule 3.1 modification began 3 APRIL 2026 - between two and four and a half years AFTER every one of those year-ends, and after the FY2025 year-end too. A modification cannot explain a gap that predates it, so the SDDT regime explains NONE of the FY2021-FY2023 blanks.
+Those gaps already have a different and fully sufficient explanation, set out immediately above, and it is left exactly as it stands: the entity was not PRA-authorised as a deposit-taker until 19 November 2024, so no Pillar 3 obligation existed in any of those years. That is a structural pre-authorisation absence, not an exemption. The register finding changes no cell in this workbook. Its only forward-looking value is that from 3 April 2026 Vida is an SDDT, so Pillar 3 documents of the kind used for FY2024 and FY2025 should not be expected for FY2026 onward. Note finally that this is the SDDT DISCLOSURE exemption, which is in force now - not the separate SDDT CAPITAL regime that begins 1 January 2027; the two are easy to conflate and must not be.</t>
         </is>
       </c>
     </row>
@@ -4488,39 +4917,39 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: No MREL disclosure (numeric or qualitative) found in either Pillar 3 report - Vida is a small, recently-authorised bank and does not appear to be within scope of an MREL-above-minimum-capital requirement based on its own disclosures.</t>
+          <t>Note: FY2025/FY2024: no MREL disclosure (numeric or qualitative) found in either Pillar 3 report - Vida is a small, recently-authorised bank and does not appear to be within scope of an MREL-above-minimum-capital requirement based on its own disclosures. FY2018-FY2023 read 'Not applicable' rather than 'Not disclosed' because the entity held no banking licence in those years, so no MREL requirement could attach to it in the first place - the two are different findings and were previously conflated here.</t>
         </is>
       </c>
     </row>
@@ -4530,7 +4959,12 @@
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
 FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
 FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.</t>
+BASIS DETERMINATION, made 2026-09-15 by reading section 1.3 'Scope' of both reports directly (they are word-for-word identical on this point). Verbatim: 'VGHL is a financial holding company and it is a CRR consolidation entity. This Pillar 3 report is prepared on a consolidated basis. Vida Bank Limited ("VBL") is the principal regulated subsidiary of the Group. The same basis of consolidation is used for the preparation of the Group's Annual Report and Accounts as is used for regulatory reporting.' Section 1.2 'Basis of Disclosure' adds, equally verbatim: 'Regulatory ratios are presented on a Group-basis only.' Three consequences follow, and they are why the figures above are kept rather than demoted to memo rows. (1) VGHL is not an incidental parent that merely happens to contain the bank - it is the CRR CONSOLIDATION ENTITY, i.e. the level at which the PRA actually sets and measures Vida's regulatory capital requirement, with VBL as the principal regulated subsidiary. This is the smallest regulatory group VBL belongs to. (2) No VBL-solo ratio exists to prefer over it: 'Group-basis only' is the publisher's own statement that the solo figures are not disclosed anywhere, so the choice is between the consolidated figure and nothing at all - not between a group figure and a suppressed entity figure. (3) The Group and the Annual Report use the same basis of consolidation, so these ratios are reconcilable to the accounts in this workbook rather than sitting on an unrelated perimeter. Accordingly every Pillar 3 sheet in this workbook carries the subtitle 'Vida Group Holdings basis' so the reader is never shown a consolidated ratio labelled as an entity one - the project rule this workbook observes is that group figures are never SUBSTITUTED for entity figures unlabelled, which is a different thing from refusing to report the only regulatory ratio that exists. Note also that both reports are reduced-scope Article 433b disclosures ('small and non-complex institution', UK CRR Article 4(145)), which is why the metric set here is narrower than a large bank's - it is a permitted reduction, not an omission.
+No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.
+RE-VERIFIED 2026-09-12 (disclosure audit): the pre-authorisation gap is STRUCTURAL, independently confirmed against the Companies House register rather than the workbook's own prior claim. Company 09837692 was incorporated 22 October 2015 and traded as 'Belmont Green Finance Ltd' (22 Oct 2015 - 10 Jun 2019) and then 'Belmont Green Finance Limited' (10 Jun 2019 - 25 Nov 2024), only taking the name 'Vida Bank Limited' on 25 November 2024 - six days after the 19 November 2024 PRA authorisation. No Pillar 3 obligation can therefore exist for FY2018-FY2023, so those years are blank by regulation, not by omission.
+SDDT - EXPLICIT NEGATIVE, recorded 2026-09-15 (cross-bank SDDT date-fit pass) so that a future pass does not wrongly apply the Small Domestic Deposit Taker exemption to this workbook's gap years. Vida DOES hold the SDDT opt-in, but it is far too recent to explain anything here. The Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv) carries three SDDT rows for FRN 738741, 'Vida Bank Limited': (a) 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub rule 'Ru 3.1', waiver ref 'A00011924P.pdf', START DATE 03/04/2026, no end date; plus two eligibility-criteria modifications under sub rules 'Ru 1.2' and 'Ru 2.1(9)', both ref 'A00010069P.pdf', start 25/03/2026, end 25/03/2029. Only row (a) matters: Rule 3.1 is the actual opt-in that removes the Pillar 3 disclosure obligation, whereas rules 1.2 and 2.1(9) merely modify eligibility CRITERIA (2.1(9) waives the 'any parent undertaking of the firm is a UK undertaking' test) and are not themselves evidence of any disclosure exemption.
+DATE FIT - IT DOES NOT FIT. Vida's accounting reference date is 31 DECEMBER, confirmed at Companies House (company 09837692, an unbroken run of accounts to 31 December from 2019 to 2025). The outstanding Pillar 3 gap years are FY2021, FY2022 and FY2023, which ended 31 December 2021, 2022 and 2023 respectively. The Rule 3.1 modification began 3 APRIL 2026 - between two and four and a half years AFTER every one of those year-ends, and after the FY2025 year-end too. A modification cannot explain a gap that predates it, so the SDDT regime explains NONE of the FY2021-FY2023 blanks.
+Those gaps already have a different and fully sufficient explanation, set out immediately above, and it is left exactly as it stands: the entity was not PRA-authorised as a deposit-taker until 19 November 2024, so no Pillar 3 obligation existed in any of those years. That is a structural pre-authorisation absence, not an exemption. The register finding changes no cell in this workbook. Its only forward-looking value is that from 3 April 2026 Vida is an SDDT, so Pillar 3 documents of the kind used for FY2024 and FY2025 should not be expected for FY2026 onward. Note finally that this is the SDDT DISCLOSURE exemption, which is in force now - not the separate SDDT CAPITAL regime that begins 1 January 2027; the two are easy to conflate and must not be.</t>
         </is>
       </c>
     </row>
@@ -7717,12 +8151,36 @@
       <c r="C4" s="6" t="n">
         <v>160316</v>
       </c>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="130" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -7730,7 +8188,12 @@
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
 FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
 FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.</t>
+BASIS DETERMINATION, made 2026-09-15 by reading section 1.3 'Scope' of both reports directly (they are word-for-word identical on this point). Verbatim: 'VGHL is a financial holding company and it is a CRR consolidation entity. This Pillar 3 report is prepared on a consolidated basis. Vida Bank Limited ("VBL") is the principal regulated subsidiary of the Group. The same basis of consolidation is used for the preparation of the Group's Annual Report and Accounts as is used for regulatory reporting.' Section 1.2 'Basis of Disclosure' adds, equally verbatim: 'Regulatory ratios are presented on a Group-basis only.' Three consequences follow, and they are why the figures above are kept rather than demoted to memo rows. (1) VGHL is not an incidental parent that merely happens to contain the bank - it is the CRR CONSOLIDATION ENTITY, i.e. the level at which the PRA actually sets and measures Vida's regulatory capital requirement, with VBL as the principal regulated subsidiary. This is the smallest regulatory group VBL belongs to. (2) No VBL-solo ratio exists to prefer over it: 'Group-basis only' is the publisher's own statement that the solo figures are not disclosed anywhere, so the choice is between the consolidated figure and nothing at all - not between a group figure and a suppressed entity figure. (3) The Group and the Annual Report use the same basis of consolidation, so these ratios are reconcilable to the accounts in this workbook rather than sitting on an unrelated perimeter. Accordingly every Pillar 3 sheet in this workbook carries the subtitle 'Vida Group Holdings basis' so the reader is never shown a consolidated ratio labelled as an entity one - the project rule this workbook observes is that group figures are never SUBSTITUTED for entity figures unlabelled, which is a different thing from refusing to report the only regulatory ratio that exists. Note also that both reports are reduced-scope Article 433b disclosures ('small and non-complex institution', UK CRR Article 4(145)), which is why the metric set here is narrower than a large bank's - it is a permitted reduction, not an omission.
+No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.
+RE-VERIFIED 2026-09-12 (disclosure audit): the pre-authorisation gap is STRUCTURAL, independently confirmed against the Companies House register rather than the workbook's own prior claim. Company 09837692 was incorporated 22 October 2015 and traded as 'Belmont Green Finance Ltd' (22 Oct 2015 - 10 Jun 2019) and then 'Belmont Green Finance Limited' (10 Jun 2019 - 25 Nov 2024), only taking the name 'Vida Bank Limited' on 25 November 2024 - six days after the 19 November 2024 PRA authorisation. No Pillar 3 obligation can therefore exist for FY2018-FY2023, so those years are blank by regulation, not by omission.
+SDDT - EXPLICIT NEGATIVE, recorded 2026-09-15 (cross-bank SDDT date-fit pass) so that a future pass does not wrongly apply the Small Domestic Deposit Taker exemption to this workbook's gap years. Vida DOES hold the SDDT opt-in, but it is far too recent to explain anything here. The Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv) carries three SDDT rows for FRN 738741, 'Vida Bank Limited': (a) 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub rule 'Ru 3.1', waiver ref 'A00011924P.pdf', START DATE 03/04/2026, no end date; plus two eligibility-criteria modifications under sub rules 'Ru 1.2' and 'Ru 2.1(9)', both ref 'A00010069P.pdf', start 25/03/2026, end 25/03/2029. Only row (a) matters: Rule 3.1 is the actual opt-in that removes the Pillar 3 disclosure obligation, whereas rules 1.2 and 2.1(9) merely modify eligibility CRITERIA (2.1(9) waives the 'any parent undertaking of the firm is a UK undertaking' test) and are not themselves evidence of any disclosure exemption.
+DATE FIT - IT DOES NOT FIT. Vida's accounting reference date is 31 DECEMBER, confirmed at Companies House (company 09837692, an unbroken run of accounts to 31 December from 2019 to 2025). The outstanding Pillar 3 gap years are FY2021, FY2022 and FY2023, which ended 31 December 2021, 2022 and 2023 respectively. The Rule 3.1 modification began 3 APRIL 2026 - between two and four and a half years AFTER every one of those year-ends, and after the FY2025 year-end too. A modification cannot explain a gap that predates it, so the SDDT regime explains NONE of the FY2021-FY2023 blanks.
+Those gaps already have a different and fully sufficient explanation, set out immediately above, and it is left exactly as it stands: the entity was not PRA-authorised as a deposit-taker until 19 November 2024, so no Pillar 3 obligation existed in any of those years. That is a structural pre-authorisation absence, not an exemption. The register finding changes no cell in this workbook. Its only forward-looking value is that from 3 April 2026 Vida is an SDDT, so Pillar 3 documents of the kind used for FY2024 and FY2025 should not be expected for FY2026 onward. Note finally that this is the SDDT DISCLOSURE exemption, which is in force now - not the separate SDDT CAPITAL regime that begins 1 January 2027; the two are easy to conflate and must not be.</t>
         </is>
       </c>
     </row>
@@ -7839,12 +8302,36 @@
           <t>16.2%</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="130" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -7852,7 +8339,12 @@
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
 FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
 FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.</t>
+BASIS DETERMINATION, made 2026-09-15 by reading section 1.3 'Scope' of both reports directly (they are word-for-word identical on this point). Verbatim: 'VGHL is a financial holding company and it is a CRR consolidation entity. This Pillar 3 report is prepared on a consolidated basis. Vida Bank Limited ("VBL") is the principal regulated subsidiary of the Group. The same basis of consolidation is used for the preparation of the Group's Annual Report and Accounts as is used for regulatory reporting.' Section 1.2 'Basis of Disclosure' adds, equally verbatim: 'Regulatory ratios are presented on a Group-basis only.' Three consequences follow, and they are why the figures above are kept rather than demoted to memo rows. (1) VGHL is not an incidental parent that merely happens to contain the bank - it is the CRR CONSOLIDATION ENTITY, i.e. the level at which the PRA actually sets and measures Vida's regulatory capital requirement, with VBL as the principal regulated subsidiary. This is the smallest regulatory group VBL belongs to. (2) No VBL-solo ratio exists to prefer over it: 'Group-basis only' is the publisher's own statement that the solo figures are not disclosed anywhere, so the choice is between the consolidated figure and nothing at all - not between a group figure and a suppressed entity figure. (3) The Group and the Annual Report use the same basis of consolidation, so these ratios are reconcilable to the accounts in this workbook rather than sitting on an unrelated perimeter. Accordingly every Pillar 3 sheet in this workbook carries the subtitle 'Vida Group Holdings basis' so the reader is never shown a consolidated ratio labelled as an entity one - the project rule this workbook observes is that group figures are never SUBSTITUTED for entity figures unlabelled, which is a different thing from refusing to report the only regulatory ratio that exists. Note also that both reports are reduced-scope Article 433b disclosures ('small and non-complex institution', UK CRR Article 4(145)), which is why the metric set here is narrower than a large bank's - it is a permitted reduction, not an omission.
+No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.
+RE-VERIFIED 2026-09-12 (disclosure audit): the pre-authorisation gap is STRUCTURAL, independently confirmed against the Companies House register rather than the workbook's own prior claim. Company 09837692 was incorporated 22 October 2015 and traded as 'Belmont Green Finance Ltd' (22 Oct 2015 - 10 Jun 2019) and then 'Belmont Green Finance Limited' (10 Jun 2019 - 25 Nov 2024), only taking the name 'Vida Bank Limited' on 25 November 2024 - six days after the 19 November 2024 PRA authorisation. No Pillar 3 obligation can therefore exist for FY2018-FY2023, so those years are blank by regulation, not by omission.
+SDDT - EXPLICIT NEGATIVE, recorded 2026-09-15 (cross-bank SDDT date-fit pass) so that a future pass does not wrongly apply the Small Domestic Deposit Taker exemption to this workbook's gap years. Vida DOES hold the SDDT opt-in, but it is far too recent to explain anything here. The Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv) carries three SDDT rows for FRN 738741, 'Vida Bank Limited': (a) 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub rule 'Ru 3.1', waiver ref 'A00011924P.pdf', START DATE 03/04/2026, no end date; plus two eligibility-criteria modifications under sub rules 'Ru 1.2' and 'Ru 2.1(9)', both ref 'A00010069P.pdf', start 25/03/2026, end 25/03/2029. Only row (a) matters: Rule 3.1 is the actual opt-in that removes the Pillar 3 disclosure obligation, whereas rules 1.2 and 2.1(9) merely modify eligibility CRITERIA (2.1(9) waives the 'any parent undertaking of the firm is a UK undertaking' test) and are not themselves evidence of any disclosure exemption.
+DATE FIT - IT DOES NOT FIT. Vida's accounting reference date is 31 DECEMBER, confirmed at Companies House (company 09837692, an unbroken run of accounts to 31 December from 2019 to 2025). The outstanding Pillar 3 gap years are FY2021, FY2022 and FY2023, which ended 31 December 2021, 2022 and 2023 respectively. The Rule 3.1 modification began 3 APRIL 2026 - between two and four and a half years AFTER every one of those year-ends, and after the FY2025 year-end too. A modification cannot explain a gap that predates it, so the SDDT regime explains NONE of the FY2021-FY2023 blanks.
+Those gaps already have a different and fully sufficient explanation, set out immediately above, and it is left exactly as it stands: the entity was not PRA-authorised as a deposit-taker until 19 November 2024, so no Pillar 3 obligation existed in any of those years. That is a structural pre-authorisation absence, not an exemption. The register finding changes no cell in this workbook. Its only forward-looking value is that from 3 April 2026 Vida is an SDDT, so Pillar 3 documents of the kind used for FY2024 and FY2025 should not be expected for FY2026 onward. Note finally that this is the SDDT DISCLOSURE exemption, which is in force now - not the separate SDDT CAPITAL regime that begins 1 January 2027; the two are easy to conflate and must not be.</t>
         </is>
       </c>
     </row>
@@ -7957,12 +8449,36 @@
       <c r="C4" s="6" t="n">
         <v>160316</v>
       </c>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -7977,7 +8493,12 @@
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
 FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
 FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.</t>
+BASIS DETERMINATION, made 2026-09-15 by reading section 1.3 'Scope' of both reports directly (they are word-for-word identical on this point). Verbatim: 'VGHL is a financial holding company and it is a CRR consolidation entity. This Pillar 3 report is prepared on a consolidated basis. Vida Bank Limited ("VBL") is the principal regulated subsidiary of the Group. The same basis of consolidation is used for the preparation of the Group's Annual Report and Accounts as is used for regulatory reporting.' Section 1.2 'Basis of Disclosure' adds, equally verbatim: 'Regulatory ratios are presented on a Group-basis only.' Three consequences follow, and they are why the figures above are kept rather than demoted to memo rows. (1) VGHL is not an incidental parent that merely happens to contain the bank - it is the CRR CONSOLIDATION ENTITY, i.e. the level at which the PRA actually sets and measures Vida's regulatory capital requirement, with VBL as the principal regulated subsidiary. This is the smallest regulatory group VBL belongs to. (2) No VBL-solo ratio exists to prefer over it: 'Group-basis only' is the publisher's own statement that the solo figures are not disclosed anywhere, so the choice is between the consolidated figure and nothing at all - not between a group figure and a suppressed entity figure. (3) The Group and the Annual Report use the same basis of consolidation, so these ratios are reconcilable to the accounts in this workbook rather than sitting on an unrelated perimeter. Accordingly every Pillar 3 sheet in this workbook carries the subtitle 'Vida Group Holdings basis' so the reader is never shown a consolidated ratio labelled as an entity one - the project rule this workbook observes is that group figures are never SUBSTITUTED for entity figures unlabelled, which is a different thing from refusing to report the only regulatory ratio that exists. Note also that both reports are reduced-scope Article 433b disclosures ('small and non-complex institution', UK CRR Article 4(145)), which is why the metric set here is narrower than a large bank's - it is a permitted reduction, not an omission.
+No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.
+RE-VERIFIED 2026-09-12 (disclosure audit): the pre-authorisation gap is STRUCTURAL, independently confirmed against the Companies House register rather than the workbook's own prior claim. Company 09837692 was incorporated 22 October 2015 and traded as 'Belmont Green Finance Ltd' (22 Oct 2015 - 10 Jun 2019) and then 'Belmont Green Finance Limited' (10 Jun 2019 - 25 Nov 2024), only taking the name 'Vida Bank Limited' on 25 November 2024 - six days after the 19 November 2024 PRA authorisation. No Pillar 3 obligation can therefore exist for FY2018-FY2023, so those years are blank by regulation, not by omission.
+SDDT - EXPLICIT NEGATIVE, recorded 2026-09-15 (cross-bank SDDT date-fit pass) so that a future pass does not wrongly apply the Small Domestic Deposit Taker exemption to this workbook's gap years. Vida DOES hold the SDDT opt-in, but it is far too recent to explain anything here. The Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv) carries three SDDT rows for FRN 738741, 'Vida Bank Limited': (a) 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub rule 'Ru 3.1', waiver ref 'A00011924P.pdf', START DATE 03/04/2026, no end date; plus two eligibility-criteria modifications under sub rules 'Ru 1.2' and 'Ru 2.1(9)', both ref 'A00010069P.pdf', start 25/03/2026, end 25/03/2029. Only row (a) matters: Rule 3.1 is the actual opt-in that removes the Pillar 3 disclosure obligation, whereas rules 1.2 and 2.1(9) merely modify eligibility CRITERIA (2.1(9) waives the 'any parent undertaking of the firm is a UK undertaking' test) and are not themselves evidence of any disclosure exemption.
+DATE FIT - IT DOES NOT FIT. Vida's accounting reference date is 31 DECEMBER, confirmed at Companies House (company 09837692, an unbroken run of accounts to 31 December from 2019 to 2025). The outstanding Pillar 3 gap years are FY2021, FY2022 and FY2023, which ended 31 December 2021, 2022 and 2023 respectively. The Rule 3.1 modification began 3 APRIL 2026 - between two and four and a half years AFTER every one of those year-ends, and after the FY2025 year-end too. A modification cannot explain a gap that predates it, so the SDDT regime explains NONE of the FY2021-FY2023 blanks.
+Those gaps already have a different and fully sufficient explanation, set out immediately above, and it is left exactly as it stands: the entity was not PRA-authorised as a deposit-taker until 19 November 2024, so no Pillar 3 obligation existed in any of those years. That is a structural pre-authorisation absence, not an exemption. The register finding changes no cell in this workbook. Its only forward-looking value is that from 3 April 2026 Vida is an SDDT, so Pillar 3 documents of the kind used for FY2024 and FY2025 should not be expected for FY2026 onward. Note finally that this is the SDDT DISCLOSURE exemption, which is in force now - not the separate SDDT CAPITAL regime that begins 1 January 2027; the two are easy to conflate and must not be.</t>
         </is>
       </c>
     </row>

--- a/banks/VIDA FINANCIALS.xlsx
+++ b/banks/VIDA FINANCIALS.xlsx
@@ -13,18 +13,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3295,6 +3296,161 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Vida Bank Limited — Tier 1 Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Vida Group Holdings basis, £'000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>168319</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>160316</v>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: Equal to CET1 capital in both years - Vida has no Additional Tier 1 (AT1) instruments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="130" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
+FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
+FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
+BASIS DETERMINATION, made 2026-09-15 by reading section 1.3 'Scope' of both reports directly (they are word-for-word identical on this point). Verbatim: 'VGHL is a financial holding company and it is a CRR consolidation entity. This Pillar 3 report is prepared on a consolidated basis. Vida Bank Limited ("VBL") is the principal regulated subsidiary of the Group. The same basis of consolidation is used for the preparation of the Group's Annual Report and Accounts as is used for regulatory reporting.' Section 1.2 'Basis of Disclosure' adds, equally verbatim: 'Regulatory ratios are presented on a Group-basis only.' Three consequences follow, and they are why the figures above are kept rather than demoted to memo rows. (1) VGHL is not an incidental parent that merely happens to contain the bank - it is the CRR CONSOLIDATION ENTITY, i.e. the level at which the PRA actually sets and measures Vida's regulatory capital requirement, with VBL as the principal regulated subsidiary. This is the smallest regulatory group VBL belongs to. (2) No VBL-solo ratio exists to prefer over it: 'Group-basis only' is the publisher's own statement that the solo figures are not disclosed anywhere, so the choice is between the consolidated figure and nothing at all - not between a group figure and a suppressed entity figure. (3) The Group and the Annual Report use the same basis of consolidation, so these ratios are reconcilable to the accounts in this workbook rather than sitting on an unrelated perimeter. Accordingly every Pillar 3 sheet in this workbook carries the subtitle 'Vida Group Holdings basis' so the reader is never shown a consolidated ratio labelled as an entity one - the project rule this workbook observes is that group figures are never SUBSTITUTED for entity figures unlabelled, which is a different thing from refusing to report the only regulatory ratio that exists. Note also that both reports are reduced-scope Article 433b disclosures ('small and non-complex institution', UK CRR Article 4(145)), which is why the metric set here is narrower than a large bank's - it is a permitted reduction, not an omission.
+No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.
+RE-VERIFIED 2026-09-12 (disclosure audit): the pre-authorisation gap is STRUCTURAL, independently confirmed against the Companies House register rather than the workbook's own prior claim. Company 09837692 was incorporated 22 October 2015 and traded as 'Belmont Green Finance Ltd' (22 Oct 2015 - 10 Jun 2019) and then 'Belmont Green Finance Limited' (10 Jun 2019 - 25 Nov 2024), only taking the name 'Vida Bank Limited' on 25 November 2024 - six days after the 19 November 2024 PRA authorisation. No Pillar 3 obligation can therefore exist for FY2018-FY2023, so those years are blank by regulation, not by omission.
+SDDT - EXPLICIT NEGATIVE, recorded 2026-09-15 (cross-bank SDDT date-fit pass) so that a future pass does not wrongly apply the Small Domestic Deposit Taker exemption to this workbook's gap years. Vida DOES hold the SDDT opt-in, but it is far too recent to explain anything here. The Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv) carries three SDDT rows for FRN 738741, 'Vida Bank Limited': (a) 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub rule 'Ru 3.1', waiver ref 'A00011924P.pdf', START DATE 03/04/2026, no end date; plus two eligibility-criteria modifications under sub rules 'Ru 1.2' and 'Ru 2.1(9)', both ref 'A00010069P.pdf', start 25/03/2026, end 25/03/2029. Only row (a) matters: Rule 3.1 is the actual opt-in that removes the Pillar 3 disclosure obligation, whereas rules 1.2 and 2.1(9) merely modify eligibility CRITERIA (2.1(9) waives the 'any parent undertaking of the firm is a UK undertaking' test) and are not themselves evidence of any disclosure exemption.
+DATE FIT - IT DOES NOT FIT. Vida's accounting reference date is 31 DECEMBER, confirmed at Companies House (company 09837692, an unbroken run of accounts to 31 December from 2019 to 2025). The outstanding Pillar 3 gap years are FY2021, FY2022 and FY2023, which ended 31 December 2021, 2022 and 2023 respectively. The Rule 3.1 modification began 3 APRIL 2026 - between two and four and a half years AFTER every one of those year-ends, and after the FY2025 year-end too. A modification cannot explain a gap that predates it, so the SDDT regime explains NONE of the FY2021-FY2023 blanks.
+Those gaps already have a different and fully sufficient explanation, set out immediately above, and it is left exactly as it stands: the entity was not PRA-authorised as a deposit-taker until 19 November 2024, so no Pillar 3 obligation existed in any of those years. That is a structural pre-authorisation absence, not an exemption. The register finding changes no cell in this workbook. Its only forward-looking value is that from 3 April 2026 Vida is an SDDT, so Pillar 3 documents of the kind used for FY2024 and FY2025 should not be expected for FY2026 onward. Note finally that this is the SDDT DISCLOSURE exemption, which is in force now - not the separate SDDT CAPITAL regime that begins 1 January 2027; the two are easy to conflate and must not be.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A7:I7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3440,7 +3596,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3590,157 +3746,6 @@
   <mergeCells count="2">
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A7:I7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Vida Bank Limited — Total Capital Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Vida Group Holdings basis, % of RWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Total capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>18.3%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>16.2%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="130" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
-FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
-FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-BASIS DETERMINATION, made 2026-09-15 by reading section 1.3 'Scope' of both reports directly (they are word-for-word identical on this point). Verbatim: 'VGHL is a financial holding company and it is a CRR consolidation entity. This Pillar 3 report is prepared on a consolidated basis. Vida Bank Limited ("VBL") is the principal regulated subsidiary of the Group. The same basis of consolidation is used for the preparation of the Group's Annual Report and Accounts as is used for regulatory reporting.' Section 1.2 'Basis of Disclosure' adds, equally verbatim: 'Regulatory ratios are presented on a Group-basis only.' Three consequences follow, and they are why the figures above are kept rather than demoted to memo rows. (1) VGHL is not an incidental parent that merely happens to contain the bank - it is the CRR CONSOLIDATION ENTITY, i.e. the level at which the PRA actually sets and measures Vida's regulatory capital requirement, with VBL as the principal regulated subsidiary. This is the smallest regulatory group VBL belongs to. (2) No VBL-solo ratio exists to prefer over it: 'Group-basis only' is the publisher's own statement that the solo figures are not disclosed anywhere, so the choice is between the consolidated figure and nothing at all - not between a group figure and a suppressed entity figure. (3) The Group and the Annual Report use the same basis of consolidation, so these ratios are reconcilable to the accounts in this workbook rather than sitting on an unrelated perimeter. Accordingly every Pillar 3 sheet in this workbook carries the subtitle 'Vida Group Holdings basis' so the reader is never shown a consolidated ratio labelled as an entity one - the project rule this workbook observes is that group figures are never SUBSTITUTED for entity figures unlabelled, which is a different thing from refusing to report the only regulatory ratio that exists. Note also that both reports are reduced-scope Article 433b disclosures ('small and non-complex institution', UK CRR Article 4(145)), which is why the metric set here is narrower than a large bank's - it is a permitted reduction, not an omission.
-No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.
-RE-VERIFIED 2026-09-12 (disclosure audit): the pre-authorisation gap is STRUCTURAL, independently confirmed against the Companies House register rather than the workbook's own prior claim. Company 09837692 was incorporated 22 October 2015 and traded as 'Belmont Green Finance Ltd' (22 Oct 2015 - 10 Jun 2019) and then 'Belmont Green Finance Limited' (10 Jun 2019 - 25 Nov 2024), only taking the name 'Vida Bank Limited' on 25 November 2024 - six days after the 19 November 2024 PRA authorisation. No Pillar 3 obligation can therefore exist for FY2018-FY2023, so those years are blank by regulation, not by omission.
-SDDT - EXPLICIT NEGATIVE, recorded 2026-09-15 (cross-bank SDDT date-fit pass) so that a future pass does not wrongly apply the Small Domestic Deposit Taker exemption to this workbook's gap years. Vida DOES hold the SDDT opt-in, but it is far too recent to explain anything here. The Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv) carries three SDDT rows for FRN 738741, 'Vida Bank Limited': (a) 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub rule 'Ru 3.1', waiver ref 'A00011924P.pdf', START DATE 03/04/2026, no end date; plus two eligibility-criteria modifications under sub rules 'Ru 1.2' and 'Ru 2.1(9)', both ref 'A00010069P.pdf', start 25/03/2026, end 25/03/2029. Only row (a) matters: Rule 3.1 is the actual opt-in that removes the Pillar 3 disclosure obligation, whereas rules 1.2 and 2.1(9) merely modify eligibility CRITERIA (2.1(9) waives the 'any parent undertaking of the firm is a UK undertaking' test) and are not themselves evidence of any disclosure exemption.
-DATE FIT - IT DOES NOT FIT. Vida's accounting reference date is 31 DECEMBER, confirmed at Companies House (company 09837692, an unbroken run of accounts to 31 December from 2019 to 2025). The outstanding Pillar 3 gap years are FY2021, FY2022 and FY2023, which ended 31 December 2021, 2022 and 2023 respectively. The Rule 3.1 modification began 3 APRIL 2026 - between two and four and a half years AFTER every one of those year-ends, and after the FY2025 year-end too. A modification cannot explain a gap that predates it, so the SDDT regime explains NONE of the FY2021-FY2023 blanks.
-Those gaps already have a different and fully sufficient explanation, set out immediately above, and it is left exactly as it stands: the entity was not PRA-authorised as a deposit-taker until 19 November 2024, so no Pillar 3 obligation existed in any of those years. That is a structural pre-authorisation absence, not an exemption. The register finding changes no cell in this workbook. Its only forward-looking value is that from 3 April 2026 Vida is an SDDT, so Pillar 3 documents of the kind used for FY2024 and FY2025 should not be expected for FY2026 onward. Note finally that this is the SDDT DISCLOSURE exemption, which is in force now - not the separate SDDT CAPITAL regime that begins 1 January 2027; the two are easy to conflate and must not be.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:I6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3769,14 +3774,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Vida Bank Limited — Total RWAs</t>
+          <t>Vida Bank Limited — Total Capital Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Vida Group Holdings basis, £'000</t>
+          <t>Vida Group Holdings basis, % of RWA</t>
         </is>
       </c>
     </row>
@@ -3830,14 +3835,18 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk-weighted exposure amount</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>1105780</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>986809</v>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>18.3%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>16.2%</t>
+        </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
@@ -3894,6 +3903,153 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Vida Bank Limited — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Vida Group Holdings basis, £'000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1105780</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>986809</v>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="130" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
+FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
+FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
+BASIS DETERMINATION, made 2026-09-15 by reading section 1.3 'Scope' of both reports directly (they are word-for-word identical on this point). Verbatim: 'VGHL is a financial holding company and it is a CRR consolidation entity. This Pillar 3 report is prepared on a consolidated basis. Vida Bank Limited ("VBL") is the principal regulated subsidiary of the Group. The same basis of consolidation is used for the preparation of the Group's Annual Report and Accounts as is used for regulatory reporting.' Section 1.2 'Basis of Disclosure' adds, equally verbatim: 'Regulatory ratios are presented on a Group-basis only.' Three consequences follow, and they are why the figures above are kept rather than demoted to memo rows. (1) VGHL is not an incidental parent that merely happens to contain the bank - it is the CRR CONSOLIDATION ENTITY, i.e. the level at which the PRA actually sets and measures Vida's regulatory capital requirement, with VBL as the principal regulated subsidiary. This is the smallest regulatory group VBL belongs to. (2) No VBL-solo ratio exists to prefer over it: 'Group-basis only' is the publisher's own statement that the solo figures are not disclosed anywhere, so the choice is between the consolidated figure and nothing at all - not between a group figure and a suppressed entity figure. (3) The Group and the Annual Report use the same basis of consolidation, so these ratios are reconcilable to the accounts in this workbook rather than sitting on an unrelated perimeter. Accordingly every Pillar 3 sheet in this workbook carries the subtitle 'Vida Group Holdings basis' so the reader is never shown a consolidated ratio labelled as an entity one - the project rule this workbook observes is that group figures are never SUBSTITUTED for entity figures unlabelled, which is a different thing from refusing to report the only regulatory ratio that exists. Note also that both reports are reduced-scope Article 433b disclosures ('small and non-complex institution', UK CRR Article 4(145)), which is why the metric set here is narrower than a large bank's - it is a permitted reduction, not an omission.
+No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.
+RE-VERIFIED 2026-09-12 (disclosure audit): the pre-authorisation gap is STRUCTURAL, independently confirmed against the Companies House register rather than the workbook's own prior claim. Company 09837692 was incorporated 22 October 2015 and traded as 'Belmont Green Finance Ltd' (22 Oct 2015 - 10 Jun 2019) and then 'Belmont Green Finance Limited' (10 Jun 2019 - 25 Nov 2024), only taking the name 'Vida Bank Limited' on 25 November 2024 - six days after the 19 November 2024 PRA authorisation. No Pillar 3 obligation can therefore exist for FY2018-FY2023, so those years are blank by regulation, not by omission.
+SDDT - EXPLICIT NEGATIVE, recorded 2026-09-15 (cross-bank SDDT date-fit pass) so that a future pass does not wrongly apply the Small Domestic Deposit Taker exemption to this workbook's gap years. Vida DOES hold the SDDT opt-in, but it is far too recent to explain anything here. The Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv) carries three SDDT rows for FRN 738741, 'Vida Bank Limited': (a) 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub rule 'Ru 3.1', waiver ref 'A00011924P.pdf', START DATE 03/04/2026, no end date; plus two eligibility-criteria modifications under sub rules 'Ru 1.2' and 'Ru 2.1(9)', both ref 'A00010069P.pdf', start 25/03/2026, end 25/03/2029. Only row (a) matters: Rule 3.1 is the actual opt-in that removes the Pillar 3 disclosure obligation, whereas rules 1.2 and 2.1(9) merely modify eligibility CRITERIA (2.1(9) waives the 'any parent undertaking of the firm is a UK undertaking' test) and are not themselves evidence of any disclosure exemption.
+DATE FIT - IT DOES NOT FIT. Vida's accounting reference date is 31 DECEMBER, confirmed at Companies House (company 09837692, an unbroken run of accounts to 31 December from 2019 to 2025). The outstanding Pillar 3 gap years are FY2021, FY2022 and FY2023, which ended 31 December 2021, 2022 and 2023 respectively. The Rule 3.1 modification began 3 APRIL 2026 - between two and four and a half years AFTER every one of those year-ends, and after the FY2025 year-end too. A modification cannot explain a gap that predates it, so the SDDT regime explains NONE of the FY2021-FY2023 blanks.
+Those gaps already have a different and fully sufficient explanation, set out immediately above, and it is left exactly as it stands: the entity was not PRA-authorised as a deposit-taker until 19 November 2024, so no Pillar 3 obligation existed in any of those years. That is a structural pre-authorisation absence, not an exemption. The register finding changes no cell in this workbook. Its only forward-looking value is that from 3 April 2026 Vida is an SDDT, so Pillar 3 documents of the kind used for FY2024 and FY2025 should not be expected for FY2026 onward. Note finally that this is the SDDT DISCLOSURE exemption, which is in force now - not the separate SDDT CAPITAL regime that begins 1 January 2027; the two are easy to conflate and must not be.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:I6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4142,7 +4298,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4336,7 +4492,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4581,7 +4737,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4818,7 +4974,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8064,10 +8220,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -8081,21 +8237,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Vida Bank Limited — CET1 Capital</t>
+          <t>Vida Bank Limited — KM1 Key Metrics</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Vida Group Holdings basis, £'000</t>
+          <t>Vida Group Holdings (CRR consolidation entity) basis - the bank's own published UK KM1 table, reproduced whole in its own row order, labels and precision. The bank prints no template row numbers; amounts £'000, ratios as printed. FY2018-FY2023 are blank because no Pillar 3 disclosure of any kind exists for them (pre-authorisation) - see source note.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Line item</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -8140,66 +8296,630 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Available own funds (£'000)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Common Equity Tier 1 (CET1) capital (£'000)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>168319</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C5" s="6" t="n">
         <v>160316</v>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="130" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
-FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
-FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-BASIS DETERMINATION, made 2026-09-15 by reading section 1.3 'Scope' of both reports directly (they are word-for-word identical on this point). Verbatim: 'VGHL is a financial holding company and it is a CRR consolidation entity. This Pillar 3 report is prepared on a consolidated basis. Vida Bank Limited ("VBL") is the principal regulated subsidiary of the Group. The same basis of consolidation is used for the preparation of the Group's Annual Report and Accounts as is used for regulatory reporting.' Section 1.2 'Basis of Disclosure' adds, equally verbatim: 'Regulatory ratios are presented on a Group-basis only.' Three consequences follow, and they are why the figures above are kept rather than demoted to memo rows. (1) VGHL is not an incidental parent that merely happens to contain the bank - it is the CRR CONSOLIDATION ENTITY, i.e. the level at which the PRA actually sets and measures Vida's regulatory capital requirement, with VBL as the principal regulated subsidiary. This is the smallest regulatory group VBL belongs to. (2) No VBL-solo ratio exists to prefer over it: 'Group-basis only' is the publisher's own statement that the solo figures are not disclosed anywhere, so the choice is between the consolidated figure and nothing at all - not between a group figure and a suppressed entity figure. (3) The Group and the Annual Report use the same basis of consolidation, so these ratios are reconcilable to the accounts in this workbook rather than sitting on an unrelated perimeter. Accordingly every Pillar 3 sheet in this workbook carries the subtitle 'Vida Group Holdings basis' so the reader is never shown a consolidated ratio labelled as an entity one - the project rule this workbook observes is that group figures are never SUBSTITUTED for entity figures unlabelled, which is a different thing from refusing to report the only regulatory ratio that exists. Note also that both reports are reduced-scope Article 433b disclosures ('small and non-complex institution', UK CRR Article 4(145)), which is why the metric set here is narrower than a large bank's - it is a permitted reduction, not an omission.
-No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.
-RE-VERIFIED 2026-09-12 (disclosure audit): the pre-authorisation gap is STRUCTURAL, independently confirmed against the Companies House register rather than the workbook's own prior claim. Company 09837692 was incorporated 22 October 2015 and traded as 'Belmont Green Finance Ltd' (22 Oct 2015 - 10 Jun 2019) and then 'Belmont Green Finance Limited' (10 Jun 2019 - 25 Nov 2024), only taking the name 'Vida Bank Limited' on 25 November 2024 - six days after the 19 November 2024 PRA authorisation. No Pillar 3 obligation can therefore exist for FY2018-FY2023, so those years are blank by regulation, not by omission.
-SDDT - EXPLICIT NEGATIVE, recorded 2026-09-15 (cross-bank SDDT date-fit pass) so that a future pass does not wrongly apply the Small Domestic Deposit Taker exemption to this workbook's gap years. Vida DOES hold the SDDT opt-in, but it is far too recent to explain anything here. The Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv) carries three SDDT rows for FRN 738741, 'Vida Bank Limited': (a) 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub rule 'Ru 3.1', waiver ref 'A00011924P.pdf', START DATE 03/04/2026, no end date; plus two eligibility-criteria modifications under sub rules 'Ru 1.2' and 'Ru 2.1(9)', both ref 'A00010069P.pdf', start 25/03/2026, end 25/03/2029. Only row (a) matters: Rule 3.1 is the actual opt-in that removes the Pillar 3 disclosure obligation, whereas rules 1.2 and 2.1(9) merely modify eligibility CRITERIA (2.1(9) waives the 'any parent undertaking of the firm is a UK undertaking' test) and are not themselves evidence of any disclosure exemption.
-DATE FIT - IT DOES NOT FIT. Vida's accounting reference date is 31 DECEMBER, confirmed at Companies House (company 09837692, an unbroken run of accounts to 31 December from 2019 to 2025). The outstanding Pillar 3 gap years are FY2021, FY2022 and FY2023, which ended 31 December 2021, 2022 and 2023 respectively. The Rule 3.1 modification began 3 APRIL 2026 - between two and four and a half years AFTER every one of those year-ends, and after the FY2025 year-end too. A modification cannot explain a gap that predates it, so the SDDT regime explains NONE of the FY2021-FY2023 blanks.
-Those gaps already have a different and fully sufficient explanation, set out immediately above, and it is left exactly as it stands: the entity was not PRA-authorised as a deposit-taker until 19 November 2024, so no Pillar 3 obligation existed in any of those years. That is a structural pre-authorisation absence, not an exemption. The register finding changes no cell in this workbook. Its only forward-looking value is that from 3 April 2026 Vida is an SDDT, so Pillar 3 documents of the kind used for FY2024 and FY2025 should not be expected for FY2026 onward. Note finally that this is the SDDT DISCLOSURE exemption, which is in force now - not the separate SDDT CAPITAL regime that begins 1 January 2027; the two are easy to conflate and must not be.</t>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 capital (£'000)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>168319</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>160316</v>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Total capital (£'000)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>202429</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>160316</v>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Risk-weighted exposure (£'000)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount (£'000)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>1105780</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>986809</v>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Capital ratios</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Common Equity Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>16.2%</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>16.2%</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Total capital ratio (%)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>18.3%</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>16.2%</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Additional own funds requirements</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Additional own funds requirements (%)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Total own funds requirements (%)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>9.2%</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>9.2%</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Combined buffer requirement</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Capital conservation buffer (%)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Institution specific countercyclical capital buffer (%)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Combined buffer requirement (%)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Overall capital requirements (%)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>13.6%</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>13.6%</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Leverage ratio</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Total exposure measure excluding claims on central banks (£'000)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>3440332</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>2331835</v>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Leverage ratio excluding claims on central banks (%)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>4.9%</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>6.9%</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Liquidity coverage ratio</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Total high-quality liquid assets (HQLA) (weighted value - average) (£'000)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>1073005</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>167705</v>
+      </c>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Cash outflows - total weighted value (£'000)</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>747252</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>64182</v>
+      </c>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Cash inflows - total weighted value (£'000)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>77815</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>205580</v>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Total net cash outflows (adjusted value) (£'000)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>669438</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>16046</v>
+      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Liquidity coverage ratio (%)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>163%</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>1,045%</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Net stable funding ratio</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Total available stable funding (£'000)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>2377496</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>2016146</v>
+      </c>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Total required stable funding (£'000)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>1719626</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>1830180</v>
+      </c>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="6" t="n"/>
+      <c r="I33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Net stable funding ratio (%)</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>138%</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>110%</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="6" t="n"/>
+      <c r="I34" s="6" t="n"/>
+    </row>
+    <row r="36" ht="560" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Vida's own published UK KM1 'Key metrics' table, reproduced whole in the bank's own row order, row labels and printed precision. Entity/basis: Vida Group Holdings Limited (FY2024 edition) / Vida Group Holdings plc (FY2025 edition) CONSOLIDATED - the CRR consolidation entity, with Vida Bank Limited as its principal regulated subsidiary. Both editions state 'Regulatory ratios are presented on a Group-basis only', so no Vida-Bank-Limited-solo KM1 exists to prefer; this is the same basis every other Pillar 3 sheet in this workbook uses (see the metric sheets' own BASIS DETERMINATION note).
+FY2025: Vida Group Holdings Limited Pillar 3 Disclosures 31 December 2025, section 3.1 'Key Metrics', PRINTED PAGE 5 (the page's own footer reads '5|Page') - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
+FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 31 December 2024, section 3.1 'Key Metrics', PRINTED PAGE 5 (footer '5|Page') - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
+Each year is taken from its OWN edition. The FY2025 edition also prints a 31 Dec 2024 comparative column and it agrees with the FY2024 edition digit-for-digit on every one of the 23 rows, so nothing here depends on which edition a FY2024 figure came from.
+COLUMN ORDER: both editions print the OLDER year on the LEFT (the FY2025 edition's header block reads '31 Dec 2024   31 Dec 2025'). This sheet keeps the workbook's standard most-recent-first column order, which reorders columns but not rows - no row, label, figure or precision is altered.
+THE TABLE IS UNNUMBERED, AND IT IS STILL THE TEMPLATE. Vida prints no template row numbers at all (no '1', no 'UK 7a'), but the table carries the UK KM1 row set in template order - available own funds, risk-weighted exposure amount, the three capital ratios, the additional own-funds (SREP) requirement, the combined buffer build-up, leverage, LCR and NSFR - and the bank's own sentence above it names it: 'The key metrics table (KM1) covering capital, leverage and liquidity is set out below.' Both editions are reduced-scope Article 433b disclosures ('small and non-complex institution', UK CRR Article 4(145)), and both say 'Specific rows and columns in the tables prescribed by the PRA have been omitted where these are not applicable to the Group' - so the shorter row set is a permitted reduction of the prescribed template, not a different table and not an omission.
+NO MISSING-VALUE GLYPHS: neither edition prints a dash, an 'n/a' or a zero anywhere in this table. Every row the bank printed carries a figure in every column it printed.
+UNITS: the bank declares £'000 on its own block captions ('Available own funds (£’000)', 'Risk-weighted exposure (£’000)') and again on most individual rows. Each amount row below carries its own '(£'000)' so the unit never has to be inferred from how far a lookup walks. The bank's own table mixes a typewriter apostrophe and a typographic one for the same unit within a single page; the typewriter form is used throughout here, which is a glyph choice in an annotation and changes no wording and no figure.
+FY2018-FY2023 ARE BLANK BECAUSE NO PILLAR 3 DISCLOSURE OF ANY KIND EXISTS FOR THEM, on any basis, in any edition. The entity was not PRA-authorised as a deposit-taker until 19 November 2024, so no Pillar 3 obligation could attach to any earlier year; FY2018-FY2020 it was FCA-regulated only. FY2024 is the first year for which any Pillar 3 document exists, and no later edition prints a pre-FY2024 comparative that could fill those columns. This is a structural pre-authorisation absence, not an exemption - see the ENTITY_NOTE on the Cash Flow Statement sheet and the SDDT date-fit note on the metric sheets, which records that Vida's Rule 3.1 SDDT modification began 3 April 2026 and therefore explains none of these blanks.
+LATEST-EDITION CHECK, 2026-09-17: checked Vida's own site (www.vidabank.co.uk -&gt; About Vida Bank -&gt; Investors -&gt; Debt Investors), not a cached citation list. The newest ANNUAL Pillar 3 is the 31 December 2025 edition used above, and the newest Annual Report is the 2025 Annual Report and Accounts already used throughout this workbook - so no year is missing. The site additionally carries an INTERIM Pillar 3 as at 30 June 2026 (https://www.vidabank.co.uk/media/g1vnsxxu/pillar-3-disclosures-30-june-2026.pdf), published alongside a 30 June 2026 Interim Report. It falls outside this workbook's financial years (Vida's year-end is 31 December) and so adds no column, but its 31 Dec 2025 comparative was read as an independent second transcription of the whole FY2025 column.
+WHAT THAT SECOND OPINION FOUND - RECORDED, NOT RECONCILED. The interim edition reproduces the FY2025 capital and leverage block exactly: CET1 168,319, Tier 1 168,319, Total capital 202,429, RWEA 1,105,780, ratios 15.2% / 15.2% / 18.3%, leverage exposure 3,440,332 and leverage ratio 4.9%. It differs in two places, both of which are the interim edition changing how it MEASURES a row rather than correcting a figure, so the FY2025 column below stays exactly as Vida's own FY2025 edition printed it. (1) The SREP block is presented differently: the FY2025 edition prints one combined 'Additional own funds requirements (%)' of 1.2% and a 9.2% total, while the interim edition splits the same requirement into 'Additional CET1 SREP requirements 0.66% / Additional AT1 SREP requirements 0.22% / Additional T2 SREP requirements 0.30%' with a 9.18% total - the components sum to 1.18%, i.e. the same requirement shown to two decimals instead of one. (2) The LIQUIDITY rows are on a different averaging window. The interim edition footnotes its LCR as 'the simple average of month end observations over the preceding 12 months' and its NSFR as 'the simple average of quarter end observations over the preceding 4 quarter ends', and on that basis restates 31 Dec 2025 to HQLA 612,552 / outflows 330,304 / inflows 101,370 / net outflows 252,077 / LCR 528%, and NSFR 2,327,088 / 1,646,865 / 142%, against the 1,073,005 / 747,252 / 77,815 / 669,438 / 163% and 2,377,496 / 1,719,626 / 138% that the FY2025 annual edition printed for the same date. Two printings of one date on two bases is a documented divergence, not a transcription error in either; each year's own edition governs its own column.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A36:I36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8228,14 +8948,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Vida Bank Limited — CET1 Ratio</t>
+          <t>Vida Bank Limited — CET1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Vida Group Holdings basis, % of RWA</t>
+          <t>Vida Group Holdings basis, £'000</t>
         </is>
       </c>
     </row>
@@ -8289,18 +9009,14 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Common Equity Tier 1 (CET1) ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>16.2%</t>
-        </is>
+          <t>Common Equity Tier 1 (CET1) capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>168319</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>160316</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
@@ -8362,7 +9078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -8379,14 +9095,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Vida Bank Limited — Tier 1 Capital</t>
+          <t>Vida Bank Limited — CET1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Vida Group Holdings basis, £'000</t>
+          <t>Vida Group Holdings basis, % of RWA</t>
         </is>
       </c>
     </row>
@@ -8440,14 +9156,18 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>168319</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>160316</v>
+          <t>Common Equity Tier 1 (CET1) ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>16.2%</t>
+        </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
@@ -8480,15 +9200,8 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: Equal to CET1 capital in both years - Vida has no Additional Tier 1 (AT1) instruments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="130" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="6" ht="130" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
 FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
@@ -8503,9 +9216,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A7:I7"/>
+  <mergeCells count="1">
+    <mergeCell ref="A6:I6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/VIDA FINANCIALS.xlsx
+++ b/banks/VIDA FINANCIALS.xlsx
@@ -1748,6 +1748,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -5955,7 +5956,7 @@
 FY2025: Vida Bank Limited Annual Report and Accounts 2025 (Company), p.53 - https://www.vidabank.co.uk/media/pkmnxlqg/annual-report-and-accounts-2025-company.pdf
 FY2024: Vida Bank Limited Annual Report and Accounts 2024 (Company), p.71 - https://www.vidabank.co.uk/media/emghy4z2/annual-report-and-accounts-2024-company.pdf
 FY2023: Belmont Green Finance Limited Annual Report and Accounts 2023, p.185 (Company Statement of Financial Position) - https://www.vidabank.co.uk/media/zhoj0swe/annual-report-and-accounts-2023.pdf
-FY2022: taken from the FY2023 Annual Report's own restated FY2022 comparative column (same document/page as above) - Belmont Green's own FY2022 Annual Report was not fetched this session.
+FY2022: taken from the FY2023 Annual Report's own restated FY2022 comparative column (same document/page as above). Belmont Green's own FY2022 Annual Report has since been located and read (2026-09-18, see the Cash Flow Statement sheet's FY2022_FOUND_NOTE); its own Company Statement of Financial Position is on printed p.159 and its figures were superseded by the FY2023 report's restatement, so the restated comparative is retained here deliberately rather than for want of the original.
 FY2021: Belmont Green Finance Limited Annual Report and Accounts 2021, p.149 (Company Statement of Financial Position) - https://www.vidabank.co.uk/media/p3wau0ms/annual-report-and-accounts-2021.pdf
 FY2020: Belmont Green Finance Limited Annual Report and Accounts 2020, Company Statement of Financial Position - https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzMwNjUyMjA5MmFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2019: Belmont Green Finance Limited Annual Report and Accounts 2019, Company Statement of Financial Position - https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzI4NjAzOTYwNWFkaXF6a2N4/document?format=pdf&amp;download=0
@@ -7202,7 +7203,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Company (non-consolidated) basis, £'000. FY2022 blank - see source note at bottom.</t>
+          <t>Company (non-consolidated) basis, £'000. Every year FY2018-FY2025 is populated; see the source note for FY2022's own two documented divergences and the FY2018 restatement.</t>
         </is>
       </c>
     </row>
@@ -7283,7 +7284,9 @@
       <c r="D5" s="5" t="n">
         <v>65493</v>
       </c>
-      <c r="E5" s="5" t="n"/>
+      <c r="E5" s="5" t="n">
+        <v>35347</v>
+      </c>
       <c r="F5" s="5" t="n">
         <v>-179449</v>
       </c>
@@ -7327,7 +7330,9 @@
       <c r="D7" s="6" t="n">
         <v>-24</v>
       </c>
-      <c r="E7" s="6" t="n"/>
+      <c r="E7" s="6" t="n">
+        <v>-131</v>
+      </c>
       <c r="F7" s="6" t="n">
         <v>-190</v>
       </c>
@@ -7356,7 +7361,9 @@
       <c r="D8" s="6" t="n">
         <v>-674</v>
       </c>
-      <c r="E8" s="6" t="n"/>
+      <c r="E8" s="6" t="n">
+        <v>-1040</v>
+      </c>
       <c r="F8" s="6" t="n">
         <v>-1567</v>
       </c>
@@ -7385,7 +7392,9 @@
       <c r="D9" s="5" t="n">
         <v>-698</v>
       </c>
-      <c r="E9" s="5" t="n"/>
+      <c r="E9" s="5" t="n">
+        <v>-1171</v>
+      </c>
       <c r="F9" s="5" t="n">
         <v>-1757</v>
       </c>
@@ -7423,7 +7432,11 @@
       <c r="B11" s="6" t="n"/>
       <c r="C11" s="6" t="n"/>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F11" s="6" t="n">
         <v>8300</v>
       </c>
@@ -7452,7 +7465,9 @@
       <c r="D12" s="6" t="n">
         <v>-62096</v>
       </c>
-      <c r="E12" s="6" t="n"/>
+      <c r="E12" s="6" t="n">
+        <v>-31392</v>
+      </c>
       <c r="F12" s="6" t="n">
         <v>169705</v>
       </c>
@@ -7534,7 +7549,9 @@
       <c r="D16" s="6" t="n">
         <v>-446</v>
       </c>
-      <c r="E16" s="6" t="n"/>
+      <c r="E16" s="6" t="n">
+        <v>-1365</v>
+      </c>
       <c r="F16" s="6" t="n">
         <v>-1407</v>
       </c>
@@ -7599,7 +7616,9 @@
       <c r="D19" s="5" t="n">
         <v>-62554</v>
       </c>
-      <c r="E19" s="5" t="n"/>
+      <c r="E19" s="5" t="n">
+        <v>-32755</v>
+      </c>
       <c r="F19" s="5" t="n">
         <v>176598</v>
       </c>
@@ -7628,7 +7647,9 @@
       <c r="D20" s="5" t="n">
         <v>2241</v>
       </c>
-      <c r="E20" s="5" t="n"/>
+      <c r="E20" s="5" t="n">
+        <v>1419</v>
+      </c>
       <c r="F20" s="5" t="n">
         <v>-4608</v>
       </c>
@@ -7657,7 +7678,9 @@
       <c r="D21" s="6" t="n">
         <v>14920</v>
       </c>
-      <c r="E21" s="6" t="n"/>
+      <c r="E21" s="6" t="n">
+        <v>13500</v>
+      </c>
       <c r="F21" s="6" t="n">
         <v>18108</v>
       </c>
@@ -7686,7 +7709,9 @@
       <c r="D22" s="5" t="n">
         <v>17161</v>
       </c>
-      <c r="E22" s="5" t="n"/>
+      <c r="E22" s="5" t="n">
+        <v>14919</v>
+      </c>
       <c r="F22" s="5" t="n">
         <v>13500</v>
       </c>
@@ -7706,13 +7731,19 @@
           <t>Sources - all figures are Vida Bank Limited's own Company (non-consolidated) cash flow statement, £'000:
 FY2025: Vida Bank Limited Annual Report and Accounts 2025 (Company), p.55 (Statement of Cash Flows) - https://www.vidabank.co.uk/media/pkmnxlqg/annual-report-and-accounts-2025-company.pdf
 FY2024: Vida Bank Limited Annual Report and Accounts 2024 (Company), p.73 (Statement of Cash Flows) - https://www.vidabank.co.uk/media/emghy4z2/annual-report-and-accounts-2024-company.pdf
-FY2023: taken from Vida Bank Limited's FY2024 Annual Report's own FY2023 comparative column (p.73, same document as above) - Belmont Green Finance Limited's own FY2023 Annual Report does not present a comparable Company-basis statement (see ENTITY_NOTE/FY2022_GAP_NOTE).
+FY2023: taken from Vida Bank Limited's FY2024 Annual Report's own FY2023 comparative column (p.73, same document as above) - Belmont Green Finance Limited's own FY2023 Annual Report does not present a comparable Company-basis statement (see ENTITY_NOTE/FY2022_FOUND_NOTE).
+FY2022: Belmont Green Finance Limited Annual Report and Accounts 2022, printed p.161 / PDF p.161 (the Company cash flow statement, printed under the running head 'Notes to the Company Financial Statements (continued)'; the operating-activities reconciliation behind it is Note 34 on printed p.164) - https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzM4Nzk2MDY5OWFkaXF6a2N4/document?format=pdf&amp;download=0 (Companies House copy, image-only scan, read by OCR and confirmed against a 300 dpi page render - see FY2022_FOUND_NOTE).
 FY2021: Belmont Green Finance Limited (Vida) Annual Report and Accounts 2021, p.150 (Company Statement of Cash Flows) - https://www.vidabank.co.uk/media/p3wau0ms/annual-report-and-accounts-2021.pdf
 FY2020: Belmont Green Finance Limited Annual Report and Accounts 2020 (Company Statement of Cash Flows) - https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzMwNjUyMjA5MmFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2019: Belmont Green Finance Limited Annual Report and Accounts 2019 (Company Statement of Cash Flows, Note 35-37 breakdown) - https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzI4NjAzOTYwNWFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2018: taken from the FY2019 Annual Report's own restated FY2018 comparative column (same document/notes as above) - see FY2018_RESTATEMENT_NOTE for why the restated figures are used in place of Belmont Green's originally-filed FY2018 Annual Report (https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzIzMzYzMjc1OWFkaXF6a2N4/document?format=pdf&amp;download=0).
-ENTITY NOTE: the company (FRN 738741, Companies House 09837692) was named 'Belmont Green Finance Limited' (trading as Vida / Vida Homeloans) through its FY2023 Annual Report, and was renamed 'Vida Bank Limited' after receiving its PRA banking licence on 19 November 2024. This workbook uses 'Vida Bank Limited' throughout since that is its current name. Pre-authorisation (FY2018-FY2023), the business was funded mainly through mortgage securitisation (numerous 'Tower Bridge Funding' special-purpose vehicles) and warehouse facilities rather than retail deposits; the FY2023 Annual Report's own commentary describes the business as still 'preparing for the banking licence'. FY2018-FY2020 the company was regulated only by the FCA (mortgage lending/administration permissions) - not the PRA - and had no banking licence and no deposit-taking business at all; its own FY2019 and FY2020 Annual Reports both still describe the banking licence application as in progress/delayed. Cash flow figures below are on the Company's own (non-consolidated/solo) basis in every populated year - this is the only basis for which a full three-part cash flow statement (operating/investing/financing) could be found in every report; the Consolidated (Group) statement of financial position was reported each year from FY2019 onwards, but the FY2022 and FY2023 Annual Reports' own primary financial statements do not include a full Group cash flow statement, only a partial 'Net cash flow from operating activities' reconciliation note (Note 25) on the Group basis - see FY2022_GAP_NOTE below. FY2018's own Annual Report only presented Company-only financial statements (no Group/consolidated accounts were filed for FY2018); Group consolidated accounts for Belmont Green Finance Limited first appear in the FY2019 Annual Report, which also restates FY2018's Company-basis Balance Sheet, Cash Flow Statement and Statement of Changes in Equity figures - see FY2018_RESTATEMENT_NOTE below for why this workbook uses those restated figures rather than the originally-filed FY2018 Annual Report's own (much smaller) figures.
-FY2022 is blank on this sheet: neither the FY2022 nor FY2023 Annual Report presents a full three-part Company cash flow statement for FY2022 (checked both directly - https://www.vidabank.co.uk/media/zhoj0swe/annual-report-and-accounts-2023.pdf - and via the FY2023 report's own prior-year comparative column, which is likewise not present.) The FY2023 Annual Report's Note 25 gives only a partial Group-basis operating reconciliation ending at 'Net cash flows from operating activities: £68,297k' for FY2022 - not on the same (Company) basis as every other populated year here and with no investing/financing breakdown at all, so it is not shown rather than presented as a misleadingly partial column.
+ENTITY NOTE: the company (FRN 738741, Companies House 09837692) was named 'Belmont Green Finance Limited' (trading as Vida / Vida Homeloans) through its FY2023 Annual Report, and was renamed 'Vida Bank Limited' after receiving its PRA banking licence on 19 November 2024. This workbook uses 'Vida Bank Limited' throughout since that is its current name. Pre-authorisation (FY2018-FY2023), the business was funded mainly through mortgage securitisation (numerous 'Tower Bridge Funding' special-purpose vehicles) and warehouse facilities rather than retail deposits; the FY2023 Annual Report's own commentary describes the business as still 'preparing for the banking licence'. FY2018-FY2020 the company was regulated only by the FCA (mortgage lending/administration permissions) - not the PRA - and had no banking licence and no deposit-taking business at all; its own FY2019 and FY2020 Annual Reports both still describe the banking licence application as in progress/delayed. Cash flow figures below are on the Company's own (non-consolidated/solo) basis in every populated year - this is the only basis for which a full three-part cash flow statement (operating/investing/financing) could be found in every report; the Consolidated (Group) statement of financial position was reported each year from FY2019 onwards. (CORRECTED 2026-09-18: this note previously said the FY2022 AND FY2023 Annual Reports print only a partial Group operating-activities reconciliation and no full Group cash flow statement. That is true of the FY2023 report; it is NOT true of the FY2022 report, which prints a full three-part CONSOLIDATED Statement of Cash Flows on printed p.117 AND a full three-part COMPANY statement on printed p.161. The claim had been generalised from the one report that was actually opened - see FY2022_FOUND_NOTE.) FY2018's own Annual Report only presented Company-only financial statements (no Group/consolidated accounts were filed for FY2018); Group consolidated accounts for Belmont Green Finance Limited first appear in the FY2019 Annual Report, which also restates FY2018's Company-basis Balance Sheet, Cash Flow Statement and Statement of Changes in Equity figures - see FY2018_RESTATEMENT_NOTE below for why this workbook uses those restated figures rather than the originally-filed FY2018 Annual Report's own (much smaller) figures.
+FY2022 (FILLED 2026-09-18 - IT WAS NEVER A GAP IN THE DISCLOSURE, ONLY IN OUR READING). This sheet previously carried a note saying 'neither the FY2022 nor FY2023 Annual Report presents a full three-part Company cash flow statement for FY2022', with the FY2023 report cited as the document checked. Only the FY2023 report had in fact been checked. Belmont Green Finance Limited's OWN FY2022 Annual Report prints a complete three-part Company cash flow statement - operating, investing and financing, with opening and closing cash - on printed p.161, presented under the running head 'Notes to the Company Financial Statements (continued)' rather than under a title of its own, which is why a heading search for 'Company Statement of Cash Flows' finds nothing in it. (The same report also prints a full CONSOLIDATED Statement of Cash Flows on printed p.117, so the Group-basis claim was wrong for FY2022 too.) The reason it had not been read is a sourcing one, not a disclosure one: vidabank.co.uk's media library carries the 2021, 2023, 2024 and 2025 reports but not 2022, and the Companies House copy (https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzM4Nzk2MDY5OWFkaXF6a2N4/document?format=pdf&amp;download=0) is an image-only scan with a zero-character text layer, so any text search of it returns nothing regardless of content. It was read by OCRing all 164 pages and then confirming the figures against a 300 dpi render of p.161 itself.
+BASIS: Company (non-consolidated), identical to every other populated year here. The same page's 2021 comparative column reproduces this workbook's existing FY2021 column cell for cell (operating (179,449); PPE (190); software (1,567); investing (1,757); shares issued 8,300; deemed loans 169,705; leases (1,407); financing 176,598; net (4,608); opening 18,108; closing 13,500), which confirms both the basis and the transcription.
+TWO DIVERGENCES ARE REPRODUCED RATHER THAN RECONCILED, both verified on the page image:
+(1) The Bank's own FY2022 financing subtotal does not foot. Its three financing lines are nil, (31,392) and (1,365), which sum to (32,757), but the printed 'Net cash (utilised)/generated by financing activities' reads (32,755) - a £2k break in the BANK's own arithmetic. The printed (32,755) is the odd figure out: the printed net increase of 1,419 equals 35,347 - 1,171 - 32,757 and ties exactly to the printed cash balances (13,500 -&gt; 14,919), whereas the printed subtotal would give 1,421. Both the components and the subtotal are transcribed exactly as printed; nothing has been adjusted to make the column foot.
+(2) 'Proceeds from shares issued' is printed as a DASH for FY2022 and is carried here as a literal '-'. A dash is the Bank stating nil, which is a different statement from a blank cell (no such line) and from a typed zero; it is kept as printed. The workbook's block-reconciliation check still reads the column and reports divergence (1) as a financing-block break of exactly £2k (-32,757 summed vs -32,755 printed), which is the intended outcome: the disagreement is the Bank's, and it stays visible.
+FY2022/FY2023 BOUNDARY: FY2022's own report closes cash at 14,919 while the FY2023 column (taken from the FY2024 report's comparative) opens at 14,920 - a £1k cross-edition difference, left as each edition printed it. The FY2022 Annual Report's own Company loss of £(25,453)k was also later restated; this workbook's Statement of Changes in Equity already carries the restated FY2022 figures from the FY2023 report and documents that boundary separately. The cash flow column here is FY2022's own edition throughout.
 FY2018 RESTATEMENT NOTE: Belmont Green Finance Limited's own, originally-filed FY2018 Annual Report (https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzIzMzYzMjc1OWFkaXF6a2N4/document?format=pdf&amp;download=0) reported total Company assets of only £132,973k, Loans to customers of just £450k (almost all mortgage exposure sat in warehouse/securitisation special-purpose vehicles, recognised via 'Other receivables' subordinated loan notes rather than on the Company's own balance sheet), and a full three-part Company cash flow statement with operating activities of £(45,851)k / financing activities of £44,782k. The subsequent FY2019 Annual Report's Note 28(d) explains that this presentation was reassessed: 'following a thorough analysis and in accordance with IFRS9, it has been established that BGFL retains substantial risks and rewards' of the securitised mortgage assets, so the FY2019 Annual Report's own restated FY2018 comparative brings the securitised loan book onto the Company's balance sheet (Loans to customers restated to £1,197,862k) with an offsetting 'Deemed loan due to Group undertakings' liability, and correspondingly grosses up the FY2018 Company cash flow statement's operating and financing activities (to £(763,195)k and £762,125k respectively) with no change to the net cash movement or cash balances. This workbook uses the FY2019 Annual Report's restated FY2018 figures throughout the Balance Sheet, Cash Flow Statement and Statement of Changes in Equity sheets, for consistency with FY2019 onwards' presentation (which uses the same 'Deemed loan due to Group undertakings' convention) - not the originally-filed FY2018 Annual Report's figures, which are noted here for transparency rather than blended in.</t>
         </is>
       </c>
@@ -8220,18 +8251,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8264,36 +8289,6 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -8303,12 +8298,6 @@
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -8322,12 +8311,6 @@
       <c r="C5" s="6" t="n">
         <v>160316</v>
       </c>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -8341,12 +8324,6 @@
       <c r="C6" s="6" t="n">
         <v>160316</v>
       </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -8360,12 +8337,6 @@
       <c r="C7" s="6" t="n">
         <v>160316</v>
       </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -8375,12 +8346,6 @@
       </c>
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -8394,12 +8359,6 @@
       <c r="C9" s="6" t="n">
         <v>986809</v>
       </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -8409,12 +8368,6 @@
       </c>
       <c r="B10" s="6" t="n"/>
       <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -8432,12 +8385,6 @@
           <t>16.2%</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -8455,12 +8402,6 @@
           <t>16.2%</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -8478,12 +8419,6 @@
           <t>16.2%</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -8493,12 +8428,6 @@
       </c>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -8516,12 +8445,6 @@
           <t>1.2%</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -8539,12 +8462,6 @@
           <t>9.2%</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -8554,12 +8471,6 @@
       </c>
       <c r="B17" s="6" t="n"/>
       <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -8577,12 +8488,6 @@
           <t>2.5%</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-      <c r="I18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -8600,12 +8505,6 @@
           <t>1.9%</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -8623,12 +8522,6 @@
           <t>4.4%</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
-      <c r="I20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -8646,12 +8539,6 @@
           <t>13.6%</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -8661,12 +8548,6 @@
       </c>
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
-      <c r="I22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -8680,12 +8561,6 @@
       <c r="C23" s="6" t="n">
         <v>2331835</v>
       </c>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-      <c r="I23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -8703,12 +8578,6 @@
           <t>6.9%</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="n"/>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
-      <c r="I24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -8718,12 +8587,6 @@
       </c>
       <c r="B25" s="6" t="n"/>
       <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="n"/>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
-      <c r="I25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -8737,12 +8600,6 @@
       <c r="C26" s="6" t="n">
         <v>167705</v>
       </c>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
-      <c r="I26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -8756,12 +8613,6 @@
       <c r="C27" s="6" t="n">
         <v>64182</v>
       </c>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-      <c r="I27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -8775,12 +8626,6 @@
       <c r="C28" s="6" t="n">
         <v>205580</v>
       </c>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="6" t="n"/>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="n"/>
-      <c r="I28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -8794,12 +8639,6 @@
       <c r="C29" s="6" t="n">
         <v>16046</v>
       </c>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n"/>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="n"/>
-      <c r="I29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -8817,12 +8656,6 @@
           <t>1,045%</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="6" t="n"/>
-      <c r="G30" s="6" t="n"/>
-      <c r="H30" s="6" t="n"/>
-      <c r="I30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -8832,12 +8665,6 @@
       </c>
       <c r="B31" s="6" t="n"/>
       <c r="C31" s="6" t="n"/>
-      <c r="D31" s="6" t="n"/>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="6" t="n"/>
-      <c r="G31" s="6" t="n"/>
-      <c r="H31" s="6" t="n"/>
-      <c r="I31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -8851,12 +8678,6 @@
       <c r="C32" s="6" t="n">
         <v>2016146</v>
       </c>
-      <c r="D32" s="6" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="n"/>
-      <c r="G32" s="6" t="n"/>
-      <c r="H32" s="6" t="n"/>
-      <c r="I32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -8870,12 +8691,6 @@
       <c r="C33" s="6" t="n">
         <v>1830180</v>
       </c>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="6" t="n"/>
-      <c r="G33" s="6" t="n"/>
-      <c r="H33" s="6" t="n"/>
-      <c r="I33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -8893,12 +8708,6 @@
           <t>110%</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n"/>
-      <c r="E34" s="6" t="n"/>
-      <c r="F34" s="6" t="n"/>
-      <c r="G34" s="6" t="n"/>
-      <c r="H34" s="6" t="n"/>
-      <c r="I34" s="6" t="n"/>
     </row>
     <row r="36" ht="560" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
@@ -8919,7 +8728,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="A36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/VIDA FINANCIALS.xlsx
+++ b/banks/VIDA FINANCIALS.xlsx
@@ -3386,32 +3386,32 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
     </row>
@@ -3545,32 +3545,32 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
     </row>
@@ -3692,32 +3692,32 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
     </row>
@@ -3851,32 +3851,32 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
     </row>
@@ -3998,32 +3998,32 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
     </row>
@@ -4251,32 +4251,32 @@
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
     </row>
@@ -4394,32 +4394,32 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
     </row>
@@ -4441,32 +4441,32 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
     </row>
@@ -4588,32 +4588,32 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
     </row>
@@ -4631,32 +4631,32 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
     </row>
@@ -4678,32 +4678,32 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
     </row>
@@ -4833,32 +4833,32 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
     </row>
@@ -4876,32 +4876,32 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
     </row>
@@ -4923,32 +4923,32 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
     </row>
@@ -5064,42 +5064,42 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not published – Vida Group Holdings Pillar 3 report 2025 and 2024 (9pp each, re-read 2026-09-19) contain no MREL figure or mention</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not published – Vida Group Holdings Pillar 3 report 2025 and 2024 (9pp each, re-read 2026-09-19) contain no MREL figure or mention</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
     </row>
@@ -8829,32 +8829,32 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
     </row>
@@ -8980,32 +8980,32 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
         </is>
       </c>
     </row>

--- a/banks/VIDA FINANCIALS.xlsx
+++ b/banks/VIDA FINANCIALS.xlsx
@@ -1022,12 +1022,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$BE$5:$BL$5</f>
+              <f>'Overview'!$BE$5:$BF$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$BE$6:$BL$6</f>
+              <f>'Overview'!$BE$6:$BF$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1055,12 +1055,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$BE$5:$BL$5</f>
+              <f>'Overview'!$BE$5:$BF$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$BE$7:$BL$7</f>
+              <f>'Overview'!$BE$7:$BF$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1088,12 +1088,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$BE$5:$BL$5</f>
+              <f>'Overview'!$BE$5:$BF$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$BE$8:$BL$8</f>
+              <f>'Overview'!$BE$8:$BF$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1121,12 +1121,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$BE$5:$BL$5</f>
+              <f>'Overview'!$BE$5:$BF$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$BE$9:$BL$9</f>
+              <f>'Overview'!$BE$9:$BF$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1154,12 +1154,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$BE$5:$BL$5</f>
+              <f>'Overview'!$BE$5:$BF$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$BE$10:$BL$10</f>
+              <f>'Overview'!$BE$10:$BF$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1187,12 +1187,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$BE$5:$BL$5</f>
+              <f>'Overview'!$BE$5:$BF$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$BE$11:$BL$11</f>
+              <f>'Overview'!$BE$11:$BF$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1667,7 +1667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL40"/>
+  <dimension ref="A1:BF40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1726,12 +1726,6 @@
     <col hidden="1" width="13" customWidth="1" min="56" max="56"/>
     <col hidden="1" width="13" customWidth="1" min="57" max="57"/>
     <col hidden="1" width="13" customWidth="1" min="58" max="58"/>
-    <col hidden="1" width="13" customWidth="1" min="59" max="59"/>
-    <col hidden="1" width="13" customWidth="1" min="60" max="60"/>
-    <col hidden="1" width="13" customWidth="1" min="61" max="61"/>
-    <col hidden="1" width="13" customWidth="1" min="62" max="62"/>
-    <col hidden="1" width="13" customWidth="1" min="63" max="63"/>
-    <col hidden="1" width="13" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1844,40 +1838,10 @@
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>FY2018</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -1947,10 +1911,10 @@
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="BK6" t="n">
+      <c r="BE6" t="n">
         <v>16.2</v>
       </c>
-      <c r="BL6" t="n">
+      <c r="BF6" t="n">
         <v>15.2</v>
       </c>
     </row>
@@ -2018,10 +1982,10 @@
           <t>Tier 1 Ratio</t>
         </is>
       </c>
-      <c r="BK7" t="n">
+      <c r="BE7" t="n">
         <v>16.2</v>
       </c>
-      <c r="BL7" t="n">
+      <c r="BF7" t="n">
         <v>15.2</v>
       </c>
     </row>
@@ -2059,10 +2023,10 @@
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="BK8" t="n">
+      <c r="BE8" t="n">
         <v>16.2</v>
       </c>
-      <c r="BL8" t="n">
+      <c r="BF8" t="n">
         <v>18.3</v>
       </c>
     </row>
@@ -2130,10 +2094,10 @@
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="BK9" t="n">
+      <c r="BE9" t="n">
         <v>6.9</v>
       </c>
-      <c r="BL9" t="n">
+      <c r="BF9" t="n">
         <v>4.9</v>
       </c>
     </row>
@@ -2143,10 +2107,10 @@
           <t>LCR</t>
         </is>
       </c>
-      <c r="BK10" t="n">
+      <c r="BE10" t="n">
         <v>1045</v>
       </c>
-      <c r="BL10" t="n">
+      <c r="BF10" t="n">
         <v>163</v>
       </c>
     </row>
@@ -2161,10 +2125,10 @@
           <t>NSFR</t>
         </is>
       </c>
-      <c r="BK11" t="n">
+      <c r="BE11" t="n">
         <v>110</v>
       </c>
-      <c r="BL11" t="n">
+      <c r="BF11" t="n">
         <v>138</v>
       </c>
     </row>
@@ -2878,7 +2842,9 @@
       <c r="D26" s="5" t="n">
         <v>65493</v>
       </c>
-      <c r="E26" s="5" t="n"/>
+      <c r="E26" s="5" t="n">
+        <v>35347</v>
+      </c>
       <c r="F26" s="5" t="n">
         <v>-179449</v>
       </c>
@@ -2908,6 +2874,9 @@
       <c r="AW26" t="n">
         <v>-179449</v>
       </c>
+      <c r="AX26" t="n">
+        <v>35347</v>
+      </c>
       <c r="AY26" t="n">
         <v>65493</v>
       </c>
@@ -2933,7 +2902,9 @@
       <c r="D27" s="5" t="n">
         <v>-698</v>
       </c>
-      <c r="E27" s="5" t="n"/>
+      <c r="E27" s="5" t="n">
+        <v>-1171</v>
+      </c>
       <c r="F27" s="5" t="n">
         <v>-1757</v>
       </c>
@@ -2963,6 +2934,9 @@
       <c r="AW27" t="n">
         <v>-1757</v>
       </c>
+      <c r="AX27" t="n">
+        <v>-1171</v>
+      </c>
       <c r="AY27" t="n">
         <v>-698</v>
       </c>
@@ -2988,7 +2962,9 @@
       <c r="D28" s="5" t="n">
         <v>-62554</v>
       </c>
-      <c r="E28" s="5" t="n"/>
+      <c r="E28" s="5" t="n">
+        <v>-32755</v>
+      </c>
       <c r="F28" s="5" t="n">
         <v>176598</v>
       </c>
@@ -3018,6 +2994,9 @@
       <c r="AW28" t="n">
         <v>176598</v>
       </c>
+      <c r="AX28" t="n">
+        <v>-32755</v>
+      </c>
       <c r="AY28" t="n">
         <v>-62554</v>
       </c>
@@ -3043,7 +3022,9 @@
       <c r="D29" s="5" t="n">
         <v>17161</v>
       </c>
-      <c r="E29" s="5" t="n"/>
+      <c r="E29" s="5" t="n">
+        <v>14919</v>
+      </c>
       <c r="F29" s="5" t="n">
         <v>13500</v>
       </c>
@@ -3073,6 +3054,9 @@
       <c r="AW29" t="n">
         <v>13500</v>
       </c>
+      <c r="AX29" t="n">
+        <v>14919</v>
+      </c>
       <c r="AY29" t="n">
         <v>17161</v>
       </c>
@@ -3106,36 +3090,6 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -3153,12 +3107,6 @@
           <t>16.2%</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="6" t="n"/>
-      <c r="G33" s="6" t="n"/>
-      <c r="H33" s="6" t="n"/>
-      <c r="I33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -3176,12 +3124,6 @@
           <t>16.2%</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n"/>
-      <c r="E34" s="6" t="n"/>
-      <c r="F34" s="6" t="n"/>
-      <c r="G34" s="6" t="n"/>
-      <c r="H34" s="6" t="n"/>
-      <c r="I34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -3199,12 +3141,6 @@
           <t>16.2%</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n"/>
-      <c r="E35" s="6" t="n"/>
-      <c r="F35" s="6" t="n"/>
-      <c r="G35" s="6" t="n"/>
-      <c r="H35" s="6" t="n"/>
-      <c r="I35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -3222,12 +3158,6 @@
           <t>6.9%</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n"/>
-      <c r="E36" s="6" t="n"/>
-      <c r="F36" s="6" t="n"/>
-      <c r="G36" s="6" t="n"/>
-      <c r="H36" s="6" t="n"/>
-      <c r="I36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -3245,12 +3175,6 @@
           <t>1,045%</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n"/>
-      <c r="E37" s="6" t="n"/>
-      <c r="F37" s="6" t="n"/>
-      <c r="G37" s="6" t="n"/>
-      <c r="H37" s="6" t="n"/>
-      <c r="I37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -3268,12 +3192,6 @@
           <t>110%</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n"/>
-      <c r="E38" s="6" t="n"/>
-      <c r="F38" s="6" t="n"/>
-      <c r="G38" s="6" t="n"/>
-      <c r="H38" s="6" t="n"/>
-      <c r="I38" s="6" t="n"/>
     </row>
     <row r="40" ht="45" customHeight="1">
       <c r="A40" s="7" t="inlineStr">

--- a/banks/VIDA FINANCIALS.xlsx
+++ b/banks/VIDA FINANCIALS.xlsx
@@ -116,7 +116,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="45" customHeight="1">
+    <row r="40" ht="52" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
           <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. FY2022 cash flow and FY2018-FY2023 Pillar 3 are blank - Vida only became a PRA-authorised bank on 19 November 2024 (no Pillar 3 exists before then; FY2018-FY2020 the entity was regulated only by the FCA, with no banking licence application even complete until later), and FY2022's own Annual Report doesn't present a full cash flow statement on a basis comparable to other years - see the Cash Flow Statement sheet's source note for details. The Balance Sheet/Equity/Cash Flow sheets and the Income Statement/Asset Quality sheets are on different bases (Company vs Group) in most pre-2024 years - see each sheet's own source note.</t>
@@ -3333,14 +3333,14 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: Equal to CET1 capital in both years - Vida has no Additional Tier 1 (AT1) instruments.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="130" customHeight="1">
+    <row r="7" ht="403" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
@@ -3492,7 +3492,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="130" customHeight="1">
+    <row r="6" ht="403" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
@@ -3639,14 +3639,14 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2025 total capital exceeds Tier 1 capital because the Group issued £35m of qualifying Tier 2 capital during the year to support planned balance sheet expansion; FY2024 had no Tier 2 capital.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="130" customHeight="1">
+    <row r="7" ht="403" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
@@ -3798,7 +3798,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="130" customHeight="1">
+    <row r="6" ht="403" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
@@ -3945,7 +3945,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="130" customHeight="1">
+    <row r="6" ht="403" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
@@ -4223,7 +4223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -4388,8 +4388,18 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="130" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="6" ht="117" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Note: 
+ONE LEVERAGE BASIS ONLY - CHECKED AND RECORDED 2026-10-09 (GA-026). Template UK LR2 (LRCom) asks for BOTH leverage measures - rows 24 and UK-25c on the including-claims-on-central-banks basis, UK-24b and 25 on the excluding basis, with the reconciling deduction at UK-24a - and 47 workbooks in this corpus carry both. This sheet carries the excluding side alone because that is all this bank publishes, not because the including side was missed.
+HOW THAT WAS ESTABLISHED: all 4 source URLs cited on this sheet and its KM1 sheet were re-fetched on 2026-10-09 (3 returned a real PDF, %PDF magic bytes checked), and each document's full text was searched for an LR2/LRCom template and for the 'including claims on central banks' wording. No edition contained either. The bank files UK KM1, whose leverage block (rows 13 and 14) asks only for the excluding measure; a KM1 filer that publishes no LR2 therefore discloses one basis.
+THIS IS A RECORDED FINDING, NOT AN UNCHECKED GAP. Do not reopen it on the sheet's shape alone. It should be reopened when a NEW edition appears, since a bank can begin printing LR2 at any time - Aldermore's FY2026 report is the first of its eight editions to do so. And note the method's own limit: the text search is defeated by a figure wrapping into the middle of a label (UBP's KM1 renders as '...excluding claims  4,407,957  on central banks'), so a hit was always read by hand and only a clean zero across every edition supports this finding. </t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="403" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
 FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
@@ -4404,8 +4414,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A7:I7"/>
+  <mergeCells count="2">
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="A6:I6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4625,14 +4636,14 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Note: FY2024's very high LCR (1,045%) reflects a build-up of liquid assets immediately following PRA authorisation on 19 November 2024, per the Group's own Pillar 3 commentary.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="130" customHeight="1">
+    <row r="9" ht="403" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
@@ -4870,7 +4881,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="130" customHeight="1">
+    <row r="8" ht="403" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
@@ -5021,14 +5032,14 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="39" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2025/FY2024: no MREL disclosure (numeric or qualitative) found in either Pillar 3 report - Vida is a small, recently-authorised bank and does not appear to be within scope of an MREL-above-minimum-capital requirement based on its own disclosures. FY2018-FY2023 read 'Not applicable' rather than 'Not disclosed' because the entity held no banking licence in those years, so no MREL requirement could attach to it in the first place - the two are different findings and were previously conflated here.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="130" customHeight="1">
+    <row r="7" ht="403" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
@@ -5867,7 +5878,7 @@
         <v>1245872</v>
       </c>
     </row>
-    <row r="35" ht="180" customHeight="1">
+    <row r="35" ht="351" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
           <t>Sources - Vida Bank Limited's own Company (non-consolidated) Statement of Financial Position, £'000:
@@ -6486,7 +6497,7 @@
         <v>-9019</v>
       </c>
     </row>
-    <row r="24" ht="260" customHeight="1">
+    <row r="24" ht="338" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Sources - £'000. FY2025/FY2024: Vida Bank Limited's own Company Statement of Comprehensive Income. FY2023-FY2018: Group/Consolidated Statement of Profit and Loss and Other Comprehensive Income (Company P&amp;L exempted under s.408 in every one of these years - FY2018's own Annual Report is the sole exception, which did present a Company income statement, but it is not used here for consistency with every other year's Group-basis figures; see ENTITY_NOTE below):
@@ -6518,7 +6529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -7064,7 +7075,7 @@
         <v>177779</v>
       </c>
     </row>
-    <row r="36" ht="260" customHeight="1">
+    <row r="36" ht="351" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
           <t>Sources - Vida Bank Limited's own Company (non-consolidated) Statement of Changes in Equity, £'000:
@@ -7077,15 +7088,23 @@
 FY2019 boundary: same FY2019 Annual Report, Company Statement of Changes in Equity - https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzI4NjAzOTYwNWFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2020 boundary: Belmont Green Finance Limited Annual Report and Accounts 2020, Company Statement of Changes in Equity - https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzMwNjUyMjA5MmFkaXF6a2N4/document?format=pdf&amp;download=0
 Discrepancy flagged, not forced to tie: the FY2024 Annual Report's own opening balance at 1 January 2024 (share capital 204,463 / total equity 122,070) differs by £1k from the FY2023 Annual Report's own closing balance at 31 December 2023 (share capital 204,462 / total equity 122,069) - a genuine £1k rounding artefact between the two source documents, each reproduced exactly as its own report states. A similar £1k share-capital rounding artefact exists between the FY2020 Annual Report's own opening 1 January 2020 row (share capital 168,312) and the FY2019 Annual Report's own closing 31 December 2019 row (share capital 168,313), again reproduced exactly as each report states.
-Larger, unreconciled discrepancy flagged (not forced to tie): the FY2019 Annual Report's own 'Balance as at 1 January 2019' row (129,641 / (29,547) / 100,015) does not internally sum (129,641 - 29,547 = 100,094, not 100,015 as printed) and its own 'At 31 December 2019' row (168,313 / (53,240) / 114,993) likewise differs by £80k from this workbook's own Balance Sheet sheet, which uses the same Annual Report's Company Statement of Financial Position total shareholders' equity of £115,073k for 31 December 2019 - both sets of figures are reproduced exactly as printed on their own source statement rather than corrected or blended.
+Larger, unreconciled discrepancy flagged (not forced to tie): the FY2019 Annual Report's own 'Balance as at 1 January 2019' row (129,641 / (29,547) / 100,015) does not internally sum (129,641 - 29,547 = 100,094, not 100,015 as printed) and its own 'At 31 December 2019' row (168,313 / (53,240) / 114,993) likewise differs by £80k from this workbook's own Balance Sheet sheet, which uses the same Annual Report's Company Statement of Financial Position total shareholders' equity of £115,073k for 31 December 2019 - both sets of figures are reproduced exactly as printed on their own source statement rather than corrected or blended.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="260" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 The FY2025 Statement of Changes in Equity's own "Total comprehensive income" subtotal row is omitted from this ladder: it prints running balances (not that year's movement) in its Retained earnings and Total columns - see the Profit &amp; Loss sheet's own source note for the same issue on that sheet. Every individual movement row above it (Profit for the year, Deferred tax on Gilts, Fair value through OCI reserve, Amounts deferred to cash flow hedge reserve) is reproduced in full and the ladder ties exactly without it.
 Balance Sheet / Statement of Changes in Equity are on Vida Bank Limited's own Company (non-consolidated) basis in every year, matching the Cash Flow Statement sheet's basis (see its own ENTITY_NOTE). Profit &amp; Loss is on the Company basis for FY2025/FY2024 only (Vida's own Company Statement of Comprehensive Income exists for those two years); for FY2023/FY2022/FY2021/FY2020/FY2019, the Company took the section 408 Companies Act 2006 exemption and published no separate Company income statement (only a one-line narrative profit/loss-after-tax figure, which ties to the equity ladder's own movement for that year), so the Group/Consolidated income statement is shown instead for those years. FY2018's own Annual Report did present a Company income statement, but it is not used here either, for consistency with every other pre-2024 year's Group-basis figures (see INCOME_STATEMENT_SOURCES for detail) - a genuine basis difference, not forced to a single basis.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A38:E38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7097,7 +7116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -7643,7 +7662,7 @@
         <v>5680</v>
       </c>
     </row>
-    <row r="24" ht="280" customHeight="1">
+    <row r="24" ht="325" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Sources - all figures are Vida Bank Limited's own Company (non-consolidated) cash flow statement, £'000:
@@ -7655,7 +7674,14 @@
 FY2020: Belmont Green Finance Limited Annual Report and Accounts 2020 (Company Statement of Cash Flows) - https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzMwNjUyMjA5MmFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2019: Belmont Green Finance Limited Annual Report and Accounts 2019 (Company Statement of Cash Flows, Note 35-37 breakdown) - https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzI4NjAzOTYwNWFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2018: taken from the FY2019 Annual Report's own restated FY2018 comparative column (same document/notes as above) - see FY2018_RESTATEMENT_NOTE for why the restated figures are used in place of Belmont Green's originally-filed FY2018 Annual Report (https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzIzMzYzMjc1OWFkaXF6a2N4/document?format=pdf&amp;download=0).
-ENTITY NOTE: the company (FRN 738741, Companies House 09837692) was named 'Belmont Green Finance Limited' (trading as Vida / Vida Homeloans) through its FY2023 Annual Report, and was renamed 'Vida Bank Limited' after receiving its PRA banking licence on 19 November 2024. This workbook uses 'Vida Bank Limited' throughout since that is its current name. Pre-authorisation (FY2018-FY2023), the business was funded mainly through mortgage securitisation (numerous 'Tower Bridge Funding' special-purpose vehicles) and warehouse facilities rather than retail deposits; the FY2023 Annual Report's own commentary describes the business as still 'preparing for the banking licence'. FY2018-FY2020 the company was regulated only by the FCA (mortgage lending/administration permissions) - not the PRA - and had no banking licence and no deposit-taking business at all; its own FY2019 and FY2020 Annual Reports both still describe the banking licence application as in progress/delayed. Cash flow figures below are on the Company's own (non-consolidated/solo) basis in every populated year - this is the only basis for which a full three-part cash flow statement (operating/investing/financing) could be found in every report; the Consolidated (Group) statement of financial position was reported each year from FY2019 onwards. (CORRECTED 2026-09-18: this note previously said the FY2022 AND FY2023 Annual Reports print only a partial Group operating-activities reconciliation and no full Group cash flow statement. That is true of the FY2023 report; it is NOT true of the FY2022 report, which prints a full three-part CONSOLIDATED Statement of Cash Flows on printed p.117 AND a full three-part COMPANY statement on printed p.161. The claim had been generalised from the one report that was actually opened - see FY2022_FOUND_NOTE.) FY2018's own Annual Report only presented Company-only financial statements (no Group/consolidated accounts were filed for FY2018); Group consolidated accounts for Belmont Green Finance Limited first appear in the FY2019 Annual Report, which also restates FY2018's Company-basis Balance Sheet, Cash Flow Statement and Statement of Changes in Equity figures - see FY2018_RESTATEMENT_NOTE below for why this workbook uses those restated figures rather than the originally-filed FY2018 Annual Report's own (much smaller) figures.
+ENTITY NOTE: the company (FRN 738741, Companies House 09837692) was named 'Belmont Green Finance Limited' (trading as Vida / Vida Homeloans) through its FY2023 Annual Report, and was renamed 'Vida Bank Limited' after receiving its PRA banking licence on 19 November 2024. This workbook uses 'Vida Bank Limited' throughout since that is its current name. Pre-authorisation (FY2018-FY2023), the business was funded mainly through mortgage securitisation (numerous 'Tower Bridge Funding' special-purpose vehicles) and warehouse facilities rather than retail deposits; the FY2023 Annual Report's own commentary describes the business as still 'preparing for the banking licence'. FY2018-FY2020 the company was regulated only by the FCA (mortgage lending/administration permissions) - not the PRA - and had no banking licence and no deposit-taking business at all; its own FY2019 and FY2020 Annual Reports both still describe the banking licence application as in progress/delayed. Cash flow figures below are on the Company's own (non-consolidated/solo) basis in every populated year - this is the only basis for which a full three-part cash flow statement (operating/investing/financing) could be found in every report; the Consolidated (Group) statement of financial position was reported each year from FY2019 onwards. (CORRECTED 2026-09-18: this note previously said the FY2022 AND FY2023 Annual Reports print only a partial Group operating-activities reconciliation and no full Group cash flow statement. That is true of the FY2023 report; it is NOT true of the FY2022 report, which prints a full three-part CONSOLIDATED Statement of Cash Flows on printed p.117 AND a full three-part COMPANY statement on printed p.161. The claim had been generalised from the one report that was actually opened - see FY2022_FOUND_NOTE.) FY2018's own Annual Report only presented Company-only financial statements (no Group/consolidated accounts were filed for FY2018); Group consolidated accounts for Belmont Green Finance Limited first appear in the FY2019 Annual Report, which also restates FY2018's Company-basis Balance Sheet, Cash Flow Statement and Statement of Changes in Equity figures - see FY2018_RESTATEMENT_NOTE below for why this workbook uses those restated figures rather than the originally-filed FY2018 Annual Report's own (much smaller) figures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="325" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 FY2022 (FILLED 2026-09-18 - IT WAS NEVER A GAP IN THE DISCLOSURE, ONLY IN OUR READING). This sheet previously carried a note saying 'neither the FY2022 nor FY2023 Annual Report presents a full three-part Company cash flow statement for FY2022', with the FY2023 report cited as the document checked. Only the FY2023 report had in fact been checked. Belmont Green Finance Limited's OWN FY2022 Annual Report prints a complete three-part Company cash flow statement - operating, investing and financing, with opening and closing cash - on printed p.161, presented under the running head 'Notes to the Company Financial Statements (continued)' rather than under a title of its own, which is why a heading search for 'Company Statement of Cash Flows' finds nothing in it. (The same report also prints a full CONSOLIDATED Statement of Cash Flows on printed p.117, so the Group-basis claim was wrong for FY2022 too.) The reason it had not been read is a sourcing one, not a disclosure one: vidabank.co.uk's media library carries the 2021, 2023, 2024 and 2025 reports but not 2022, and the Companies House copy (https://find-and-update.company-information.service.gov.uk/company/09837692/filing-history/MzM4Nzk2MDY5OWFkaXF6a2N4/document?format=pdf&amp;download=0) is an image-only scan with a zero-character text layer, so any text search of it returns nothing regardless of content. It was read by OCRing all 164 pages and then confirming the figures against a 300 dpi render of p.161 itself.
 BASIS: Company (non-consolidated), identical to every other populated year here. The same page's 2021 comparative column reproduces this workbook's existing FY2021 column cell for cell (operating (179,449); PPE (190); software (1,567); investing (1,757); shares issued 8,300; deemed loans 169,705; leases (1,407); financing 176,598; net (4,608); opening 18,108; closing 13,500), which confirms both the basis and the transcription.
 TWO DIVERGENCES ARE REPRODUCED RATHER THAN RECONCILED, both verified on the page image:
@@ -7667,7 +7693,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A26:I26"/>
     <mergeCell ref="A24:I24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8169,7 +8196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -8627,7 +8654,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="560" customHeight="1">
+    <row r="36" ht="409" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
           <t>Sources - Vida's own published UK KM1 'Key metrics' table, reproduced whole in the bank's own row order, row labels and printed precision. Entity/basis: Vida Group Holdings Limited (FY2024 edition) / Vida Group Holdings plc (FY2025 edition) CONSOLIDATED - the CRR consolidation entity, with Vida Bank Limited as its principal regulated subsidiary. Both editions state 'Regulatory ratios are presented on a Group-basis only', so no Vida-Bank-Limited-solo KM1 exists to prefer; this is the same basis every other Pillar 3 sheet in this workbook uses (see the metric sheets' own BASIS DETERMINATION note).
@@ -8636,7 +8663,14 @@
 Each year is taken from its OWN edition. The FY2025 edition also prints a 31 Dec 2024 comparative column and it agrees with the FY2024 edition digit-for-digit on every one of the 23 rows, so nothing here depends on which edition a FY2024 figure came from.
 COLUMN ORDER: both editions print the OLDER year on the LEFT (the FY2025 edition's header block reads '31 Dec 2024   31 Dec 2025'). This sheet keeps the workbook's standard most-recent-first column order, which reorders columns but not rows - no row, label, figure or precision is altered.
 THE TABLE IS UNNUMBERED, AND IT IS STILL THE TEMPLATE. Vida prints no template row numbers at all (no '1', no 'UK 7a'), but the table carries the UK KM1 row set in template order - available own funds, risk-weighted exposure amount, the three capital ratios, the additional own-funds (SREP) requirement, the combined buffer build-up, leverage, LCR and NSFR - and the bank's own sentence above it names it: 'The key metrics table (KM1) covering capital, leverage and liquidity is set out below.' Both editions are reduced-scope Article 433b disclosures ('small and non-complex institution', UK CRR Article 4(145)), and both say 'Specific rows and columns in the tables prescribed by the PRA have been omitted where these are not applicable to the Group' - so the shorter row set is a permitted reduction of the prescribed template, not a different table and not an omission.
-NO MISSING-VALUE GLYPHS: neither edition prints a dash, an 'n/a' or a zero anywhere in this table. Every row the bank printed carries a figure in every column it printed.
+NO MISSING-VALUE GLYPHS: neither edition prints a dash, an 'n/a' or a zero anywhere in this table. Every row the bank printed carries a figure in every column it printed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="409" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 UNITS: the bank declares £'000 on its own block captions ('Available own funds (£’000)', 'Risk-weighted exposure (£’000)') and again on most individual rows. Each amount row below carries its own '(£'000)' so the unit never has to be inferred from how far a lookup walks. The bank's own table mixes a typewriter apostrophe and a typographic one for the same unit within a single page; the typewriter form is used throughout here, which is a glyph choice in an annotation and changes no wording and no figure.
 FY2018-FY2023 ARE BLANK BECAUSE NO PILLAR 3 DISCLOSURE OF ANY KIND EXISTS FOR THEM, on any basis, in any edition. The entity was not PRA-authorised as a deposit-taker until 19 November 2024, so no Pillar 3 obligation could attach to any earlier year; FY2018-FY2020 it was FCA-regulated only. FY2024 is the first year for which any Pillar 3 document exists, and no later edition prints a pre-FY2024 comparative that could fill those columns. This is a structural pre-authorisation absence, not an exemption - see the ENTITY_NOTE on the Cash Flow Statement sheet and the SDDT date-fit note on the metric sheets, which records that Vida's Rule 3.1 SDDT modification began 3 April 2026 and therefore explains none of these blanks.
 LATEST-EDITION CHECK, 2026-09-17: checked Vida's own site (www.vidabank.co.uk -&gt; About Vida Bank -&gt; Investors -&gt; Debt Investors), not a cached citation list. The newest ANNUAL Pillar 3 is the 31 December 2025 edition used above, and the newest Annual Report is the 2025 Annual Report and Accounts already used throughout this workbook - so no year is missing. The site additionally carries an INTERIM Pillar 3 as at 30 June 2026 (https://www.vidabank.co.uk/media/g1vnsxxu/pillar-3-disclosures-30-june-2026.pdf), published alongside a 30 June 2026 Interim Report. It falls outside this workbook's financial years (Vida's year-end is 31 December) and so adds no column, but its 31 Dec 2025 comparative was read as an independent second transcription of the whole FY2025 column.
@@ -8645,7 +8679,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A38:C38"/>
     <mergeCell ref="A36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8776,7 +8811,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="130" customHeight="1">
+    <row r="6" ht="403" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
@@ -8927,7 +8962,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="130" customHeight="1">
+    <row r="6" ht="403" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):

--- a/banks/VIDA FINANCIALS.xlsx
+++ b/banks/VIDA FINANCIALS.xlsx
@@ -13,19 +13,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profitability" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3215,6 +3216,157 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Vida Bank Limited — CET1 Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Vida Group Holdings basis, % of RWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Common Equity Tier 1 (CET1) ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>16.2%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="403" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
+FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
+FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
+BASIS DETERMINATION, made 2026-09-15 by reading section 1.3 'Scope' of both reports directly (they are word-for-word identical on this point). Verbatim: 'VGHL is a financial holding company and it is a CRR consolidation entity. This Pillar 3 report is prepared on a consolidated basis. Vida Bank Limited ("VBL") is the principal regulated subsidiary of the Group. The same basis of consolidation is used for the preparation of the Group's Annual Report and Accounts as is used for regulatory reporting.' Section 1.2 'Basis of Disclosure' adds, equally verbatim: 'Regulatory ratios are presented on a Group-basis only.' Three consequences follow, and they are why the figures above are kept rather than demoted to memo rows. (1) VGHL is not an incidental parent that merely happens to contain the bank - it is the CRR CONSOLIDATION ENTITY, i.e. the level at which the PRA actually sets and measures Vida's regulatory capital requirement, with VBL as the principal regulated subsidiary. This is the smallest regulatory group VBL belongs to. (2) No VBL-solo ratio exists to prefer over it: 'Group-basis only' is the publisher's own statement that the solo figures are not disclosed anywhere, so the choice is between the consolidated figure and nothing at all - not between a group figure and a suppressed entity figure. (3) The Group and the Annual Report use the same basis of consolidation, so these ratios are reconcilable to the accounts in this workbook rather than sitting on an unrelated perimeter. Accordingly every Pillar 3 sheet in this workbook carries the subtitle 'Vida Group Holdings basis' so the reader is never shown a consolidated ratio labelled as an entity one - the project rule this workbook observes is that group figures are never SUBSTITUTED for entity figures unlabelled, which is a different thing from refusing to report the only regulatory ratio that exists. Note also that both reports are reduced-scope Article 433b disclosures ('small and non-complex institution', UK CRR Article 4(145)), which is why the metric set here is narrower than a large bank's - it is a permitted reduction, not an omission.
+No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.
+RE-VERIFIED 2026-09-12 (disclosure audit): the pre-authorisation gap is STRUCTURAL, independently confirmed against the Companies House register rather than the workbook's own prior claim. Company 09837692 was incorporated 22 October 2015 and traded as 'Belmont Green Finance Ltd' (22 Oct 2015 - 10 Jun 2019) and then 'Belmont Green Finance Limited' (10 Jun 2019 - 25 Nov 2024), only taking the name 'Vida Bank Limited' on 25 November 2024 - six days after the 19 November 2024 PRA authorisation. No Pillar 3 obligation can therefore exist for FY2018-FY2023, so those years are blank by regulation, not by omission.
+SDDT - EXPLICIT NEGATIVE, recorded 2026-09-15 (cross-bank SDDT date-fit pass) so that a future pass does not wrongly apply the Small Domestic Deposit Taker exemption to this workbook's gap years. Vida DOES hold the SDDT opt-in, but it is far too recent to explain anything here. The Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv) carries three SDDT rows for FRN 738741, 'Vida Bank Limited': (a) 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub rule 'Ru 3.1', waiver ref 'A00011924P.pdf', START DATE 03/04/2026, no end date; plus two eligibility-criteria modifications under sub rules 'Ru 1.2' and 'Ru 2.1(9)', both ref 'A00010069P.pdf', start 25/03/2026, end 25/03/2029. Only row (a) matters: Rule 3.1 is the actual opt-in that removes the Pillar 3 disclosure obligation, whereas rules 1.2 and 2.1(9) merely modify eligibility CRITERIA (2.1(9) waives the 'any parent undertaking of the firm is a UK undertaking' test) and are not themselves evidence of any disclosure exemption.
+DATE FIT - IT DOES NOT FIT. Vida's accounting reference date is 31 DECEMBER, confirmed at Companies House (company 09837692, an unbroken run of accounts to 31 December from 2019 to 2025). The outstanding Pillar 3 gap years are FY2021, FY2022 and FY2023, which ended 31 December 2021, 2022 and 2023 respectively. The Rule 3.1 modification began 3 APRIL 2026 - between two and four and a half years AFTER every one of those year-ends, and after the FY2025 year-end too. A modification cannot explain a gap that predates it, so the SDDT regime explains NONE of the FY2021-FY2023 blanks.
+Those gaps already have a different and fully sufficient explanation, set out immediately above, and it is left exactly as it stands: the entity was not PRA-authorised as a deposit-taker until 19 November 2024, so no Pillar 3 obligation existed in any of those years. That is a structural pre-authorisation absence, not an exemption. The register finding changes no cell in this workbook. Its only forward-looking value is that from 3 April 2026 Vida is an SDDT, so Pillar 3 documents of the kind used for FY2024 and FY2025 should not be expected for FY2026 onward. Note finally that this is the SDDT DISCLOSURE exemption, which is in force now - not the separate SDDT CAPITAL regime that begins 1 January 2027; the two are easy to conflate and must not be.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:I6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3364,7 +3516,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3515,7 +3667,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3665,157 +3817,6 @@
   <mergeCells count="2">
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A7:I7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Vida Bank Limited — Total Capital Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Vida Group Holdings basis, % of RWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Total capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>18.3%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>16.2%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="403" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
-FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
-FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-BASIS DETERMINATION, made 2026-09-15 by reading section 1.3 'Scope' of both reports directly (they are word-for-word identical on this point). Verbatim: 'VGHL is a financial holding company and it is a CRR consolidation entity. This Pillar 3 report is prepared on a consolidated basis. Vida Bank Limited ("VBL") is the principal regulated subsidiary of the Group. The same basis of consolidation is used for the preparation of the Group's Annual Report and Accounts as is used for regulatory reporting.' Section 1.2 'Basis of Disclosure' adds, equally verbatim: 'Regulatory ratios are presented on a Group-basis only.' Three consequences follow, and they are why the figures above are kept rather than demoted to memo rows. (1) VGHL is not an incidental parent that merely happens to contain the bank - it is the CRR CONSOLIDATION ENTITY, i.e. the level at which the PRA actually sets and measures Vida's regulatory capital requirement, with VBL as the principal regulated subsidiary. This is the smallest regulatory group VBL belongs to. (2) No VBL-solo ratio exists to prefer over it: 'Group-basis only' is the publisher's own statement that the solo figures are not disclosed anywhere, so the choice is between the consolidated figure and nothing at all - not between a group figure and a suppressed entity figure. (3) The Group and the Annual Report use the same basis of consolidation, so these ratios are reconcilable to the accounts in this workbook rather than sitting on an unrelated perimeter. Accordingly every Pillar 3 sheet in this workbook carries the subtitle 'Vida Group Holdings basis' so the reader is never shown a consolidated ratio labelled as an entity one - the project rule this workbook observes is that group figures are never SUBSTITUTED for entity figures unlabelled, which is a different thing from refusing to report the only regulatory ratio that exists. Note also that both reports are reduced-scope Article 433b disclosures ('small and non-complex institution', UK CRR Article 4(145)), which is why the metric set here is narrower than a large bank's - it is a permitted reduction, not an omission.
-No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.
-RE-VERIFIED 2026-09-12 (disclosure audit): the pre-authorisation gap is STRUCTURAL, independently confirmed against the Companies House register rather than the workbook's own prior claim. Company 09837692 was incorporated 22 October 2015 and traded as 'Belmont Green Finance Ltd' (22 Oct 2015 - 10 Jun 2019) and then 'Belmont Green Finance Limited' (10 Jun 2019 - 25 Nov 2024), only taking the name 'Vida Bank Limited' on 25 November 2024 - six days after the 19 November 2024 PRA authorisation. No Pillar 3 obligation can therefore exist for FY2018-FY2023, so those years are blank by regulation, not by omission.
-SDDT - EXPLICIT NEGATIVE, recorded 2026-09-15 (cross-bank SDDT date-fit pass) so that a future pass does not wrongly apply the Small Domestic Deposit Taker exemption to this workbook's gap years. Vida DOES hold the SDDT opt-in, but it is far too recent to explain anything here. The Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv) carries three SDDT rows for FRN 738741, 'Vida Bank Limited': (a) 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub rule 'Ru 3.1', waiver ref 'A00011924P.pdf', START DATE 03/04/2026, no end date; plus two eligibility-criteria modifications under sub rules 'Ru 1.2' and 'Ru 2.1(9)', both ref 'A00010069P.pdf', start 25/03/2026, end 25/03/2029. Only row (a) matters: Rule 3.1 is the actual opt-in that removes the Pillar 3 disclosure obligation, whereas rules 1.2 and 2.1(9) merely modify eligibility CRITERIA (2.1(9) waives the 'any parent undertaking of the firm is a UK undertaking' test) and are not themselves evidence of any disclosure exemption.
-DATE FIT - IT DOES NOT FIT. Vida's accounting reference date is 31 DECEMBER, confirmed at Companies House (company 09837692, an unbroken run of accounts to 31 December from 2019 to 2025). The outstanding Pillar 3 gap years are FY2021, FY2022 and FY2023, which ended 31 December 2021, 2022 and 2023 respectively. The Rule 3.1 modification began 3 APRIL 2026 - between two and four and a half years AFTER every one of those year-ends, and after the FY2025 year-end too. A modification cannot explain a gap that predates it, so the SDDT regime explains NONE of the FY2021-FY2023 blanks.
-Those gaps already have a different and fully sufficient explanation, set out immediately above, and it is left exactly as it stands: the entity was not PRA-authorised as a deposit-taker until 19 November 2024, so no Pillar 3 obligation existed in any of those years. That is a structural pre-authorisation absence, not an exemption. The register finding changes no cell in this workbook. Its only forward-looking value is that from 3 April 2026 Vida is an SDDT, so Pillar 3 documents of the kind used for FY2024 and FY2025 should not be expected for FY2026 onward. Note finally that this is the SDDT DISCLOSURE exemption, which is in force now - not the separate SDDT CAPITAL regime that begins 1 January 2027; the two are easy to conflate and must not be.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:I6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3844,14 +3845,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Vida Bank Limited — Total RWAs</t>
+          <t>Vida Bank Limited — Total Capital Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Vida Group Holdings basis, £'000</t>
+          <t>Vida Group Holdings basis, % of RWA</t>
         </is>
       </c>
     </row>
@@ -3905,14 +3906,18 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk-weighted exposure amount</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>1105780</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>986809</v>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>18.3%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>16.2%</t>
+        </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
@@ -3969,6 +3974,153 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Vida Bank Limited — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Vida Group Holdings basis, £'000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1105780</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>986809</v>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="403" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
+FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
+FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
+BASIS DETERMINATION, made 2026-09-15 by reading section 1.3 'Scope' of both reports directly (they are word-for-word identical on this point). Verbatim: 'VGHL is a financial holding company and it is a CRR consolidation entity. This Pillar 3 report is prepared on a consolidated basis. Vida Bank Limited ("VBL") is the principal regulated subsidiary of the Group. The same basis of consolidation is used for the preparation of the Group's Annual Report and Accounts as is used for regulatory reporting.' Section 1.2 'Basis of Disclosure' adds, equally verbatim: 'Regulatory ratios are presented on a Group-basis only.' Three consequences follow, and they are why the figures above are kept rather than demoted to memo rows. (1) VGHL is not an incidental parent that merely happens to contain the bank - it is the CRR CONSOLIDATION ENTITY, i.e. the level at which the PRA actually sets and measures Vida's regulatory capital requirement, with VBL as the principal regulated subsidiary. This is the smallest regulatory group VBL belongs to. (2) No VBL-solo ratio exists to prefer over it: 'Group-basis only' is the publisher's own statement that the solo figures are not disclosed anywhere, so the choice is between the consolidated figure and nothing at all - not between a group figure and a suppressed entity figure. (3) The Group and the Annual Report use the same basis of consolidation, so these ratios are reconcilable to the accounts in this workbook rather than sitting on an unrelated perimeter. Accordingly every Pillar 3 sheet in this workbook carries the subtitle 'Vida Group Holdings basis' so the reader is never shown a consolidated ratio labelled as an entity one - the project rule this workbook observes is that group figures are never SUBSTITUTED for entity figures unlabelled, which is a different thing from refusing to report the only regulatory ratio that exists. Note also that both reports are reduced-scope Article 433b disclosures ('small and non-complex institution', UK CRR Article 4(145)), which is why the metric set here is narrower than a large bank's - it is a permitted reduction, not an omission.
+No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.
+RE-VERIFIED 2026-09-12 (disclosure audit): the pre-authorisation gap is STRUCTURAL, independently confirmed against the Companies House register rather than the workbook's own prior claim. Company 09837692 was incorporated 22 October 2015 and traded as 'Belmont Green Finance Ltd' (22 Oct 2015 - 10 Jun 2019) and then 'Belmont Green Finance Limited' (10 Jun 2019 - 25 Nov 2024), only taking the name 'Vida Bank Limited' on 25 November 2024 - six days after the 19 November 2024 PRA authorisation. No Pillar 3 obligation can therefore exist for FY2018-FY2023, so those years are blank by regulation, not by omission.
+SDDT - EXPLICIT NEGATIVE, recorded 2026-09-15 (cross-bank SDDT date-fit pass) so that a future pass does not wrongly apply the Small Domestic Deposit Taker exemption to this workbook's gap years. Vida DOES hold the SDDT opt-in, but it is far too recent to explain anything here. The Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv) carries three SDDT rows for FRN 738741, 'Vida Bank Limited': (a) 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub rule 'Ru 3.1', waiver ref 'A00011924P.pdf', START DATE 03/04/2026, no end date; plus two eligibility-criteria modifications under sub rules 'Ru 1.2' and 'Ru 2.1(9)', both ref 'A00010069P.pdf', start 25/03/2026, end 25/03/2029. Only row (a) matters: Rule 3.1 is the actual opt-in that removes the Pillar 3 disclosure obligation, whereas rules 1.2 and 2.1(9) merely modify eligibility CRITERIA (2.1(9) waives the 'any parent undertaking of the firm is a UK undertaking' test) and are not themselves evidence of any disclosure exemption.
+DATE FIT - IT DOES NOT FIT. Vida's accounting reference date is 31 DECEMBER, confirmed at Companies House (company 09837692, an unbroken run of accounts to 31 December from 2019 to 2025). The outstanding Pillar 3 gap years are FY2021, FY2022 and FY2023, which ended 31 December 2021, 2022 and 2023 respectively. The Rule 3.1 modification began 3 APRIL 2026 - between two and four and a half years AFTER every one of those year-ends, and after the FY2025 year-end too. A modification cannot explain a gap that predates it, so the SDDT regime explains NONE of the FY2021-FY2023 blanks.
+Those gaps already have a different and fully sufficient explanation, set out immediately above, and it is left exactly as it stands: the entity was not PRA-authorised as a deposit-taker until 19 November 2024, so no Pillar 3 obligation existed in any of those years. That is a structural pre-authorisation absence, not an exemption. The register finding changes no cell in this workbook. Its only forward-looking value is that from 3 April 2026 Vida is an SDDT, so Pillar 3 documents of the kind used for FY2024 and FY2025 should not be expected for FY2026 onward. Note finally that this is the SDDT DISCLOSURE exemption, which is in force now - not the separate SDDT CAPITAL regime that begins 1 January 2027; the two are easy to conflate and must not be.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:I6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4217,7 +4369,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4422,7 +4574,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4667,7 +4819,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4899,165 +5051,6 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A8:I8"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Vida Bank Limited — MREL Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Vida Group Holdings basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>MREL ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – Vida Group Holdings Pillar 3 report 2025 and 2024 (9pp each, re-read 2026-09-19) contain no MREL figure or mention</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – Vida Group Holdings Pillar 3 report 2025 and 2024 (9pp each, re-read 2026-09-19) contain no MREL figure or mention</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="39" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2025/FY2024: no MREL disclosure (numeric or qualitative) found in either Pillar 3 report - Vida is a small, recently-authorised bank and does not appear to be within scope of an MREL-above-minimum-capital requirement based on its own disclosures. FY2018-FY2023 read 'Not applicable' rather than 'Not disclosed' because the entity held no banking licence in those years, so no MREL requirement could attach to it in the first place - the two are different findings and were previously conflated here.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="403" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
-FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
-FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-BASIS DETERMINATION, made 2026-09-15 by reading section 1.3 'Scope' of both reports directly (they are word-for-word identical on this point). Verbatim: 'VGHL is a financial holding company and it is a CRR consolidation entity. This Pillar 3 report is prepared on a consolidated basis. Vida Bank Limited ("VBL") is the principal regulated subsidiary of the Group. The same basis of consolidation is used for the preparation of the Group's Annual Report and Accounts as is used for regulatory reporting.' Section 1.2 'Basis of Disclosure' adds, equally verbatim: 'Regulatory ratios are presented on a Group-basis only.' Three consequences follow, and they are why the figures above are kept rather than demoted to memo rows. (1) VGHL is not an incidental parent that merely happens to contain the bank - it is the CRR CONSOLIDATION ENTITY, i.e. the level at which the PRA actually sets and measures Vida's regulatory capital requirement, with VBL as the principal regulated subsidiary. This is the smallest regulatory group VBL belongs to. (2) No VBL-solo ratio exists to prefer over it: 'Group-basis only' is the publisher's own statement that the solo figures are not disclosed anywhere, so the choice is between the consolidated figure and nothing at all - not between a group figure and a suppressed entity figure. (3) The Group and the Annual Report use the same basis of consolidation, so these ratios are reconcilable to the accounts in this workbook rather than sitting on an unrelated perimeter. Accordingly every Pillar 3 sheet in this workbook carries the subtitle 'Vida Group Holdings basis' so the reader is never shown a consolidated ratio labelled as an entity one - the project rule this workbook observes is that group figures are never SUBSTITUTED for entity figures unlabelled, which is a different thing from refusing to report the only regulatory ratio that exists. Note also that both reports are reduced-scope Article 433b disclosures ('small and non-complex institution', UK CRR Article 4(145)), which is why the metric set here is narrower than a large bank's - it is a permitted reduction, not an omission.
-No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.
-RE-VERIFIED 2026-09-12 (disclosure audit): the pre-authorisation gap is STRUCTURAL, independently confirmed against the Companies House register rather than the workbook's own prior claim. Company 09837692 was incorporated 22 October 2015 and traded as 'Belmont Green Finance Ltd' (22 Oct 2015 - 10 Jun 2019) and then 'Belmont Green Finance Limited' (10 Jun 2019 - 25 Nov 2024), only taking the name 'Vida Bank Limited' on 25 November 2024 - six days after the 19 November 2024 PRA authorisation. No Pillar 3 obligation can therefore exist for FY2018-FY2023, so those years are blank by regulation, not by omission.
-SDDT - EXPLICIT NEGATIVE, recorded 2026-09-15 (cross-bank SDDT date-fit pass) so that a future pass does not wrongly apply the Small Domestic Deposit Taker exemption to this workbook's gap years. Vida DOES hold the SDDT opt-in, but it is far too recent to explain anything here. The Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv) carries three SDDT rows for FRN 738741, 'Vida Bank Limited': (a) 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub rule 'Ru 3.1', waiver ref 'A00011924P.pdf', START DATE 03/04/2026, no end date; plus two eligibility-criteria modifications under sub rules 'Ru 1.2' and 'Ru 2.1(9)', both ref 'A00010069P.pdf', start 25/03/2026, end 25/03/2029. Only row (a) matters: Rule 3.1 is the actual opt-in that removes the Pillar 3 disclosure obligation, whereas rules 1.2 and 2.1(9) merely modify eligibility CRITERIA (2.1(9) waives the 'any parent undertaking of the firm is a UK undertaking' test) and are not themselves evidence of any disclosure exemption.
-DATE FIT - IT DOES NOT FIT. Vida's accounting reference date is 31 DECEMBER, confirmed at Companies House (company 09837692, an unbroken run of accounts to 31 December from 2019 to 2025). The outstanding Pillar 3 gap years are FY2021, FY2022 and FY2023, which ended 31 December 2021, 2022 and 2023 respectively. The Rule 3.1 modification began 3 APRIL 2026 - between two and four and a half years AFTER every one of those year-ends, and after the FY2025 year-end too. A modification cannot explain a gap that predates it, so the SDDT regime explains NONE of the FY2021-FY2023 blanks.
-Those gaps already have a different and fully sufficient explanation, set out immediately above, and it is left exactly as it stands: the entity was not PRA-authorised as a deposit-taker until 19 November 2024, so no Pillar 3 obligation existed in any of those years. That is a structural pre-authorisation absence, not an exemption. The register finding changes no cell in this workbook. Its only forward-looking value is that from 3 April 2026 Vida is an SDDT, so Pillar 3 documents of the kind used for FY2024 and FY2025 should not be expected for FY2026 onward. Note finally that this is the SDDT DISCLOSURE exemption, which is in force now - not the separate SDDT CAPITAL regime that begins 1 January 2027; the two are easy to conflate and must not be.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A7:I7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5900,6 +5893,165 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A35:I35"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Vida Bank Limited — MREL Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Vida Group Holdings basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>MREL ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – Vida Group Holdings Pillar 3 report 2025 and 2024 (9pp each, re-read 2026-09-19) contain no MREL figure or mention</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – Vida Group Holdings Pillar 3 report 2025 and 2024 (9pp each, re-read 2026-09-19) contain no MREL figure or mention</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="39" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2025/FY2024: no MREL disclosure (numeric or qualitative) found in either Pillar 3 report - Vida is a small, recently-authorised bank and does not appear to be within scope of an MREL-above-minimum-capital requirement based on its own disclosures. FY2018-FY2023 read 'Not applicable' rather than 'Not disclosed' because the entity held no banking licence in those years, so no MREL requirement could attach to it in the first place - the two are different findings and were previously conflated here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="403" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
+FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
+FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
+BASIS DETERMINATION, made 2026-09-15 by reading section 1.3 'Scope' of both reports directly (they are word-for-word identical on this point). Verbatim: 'VGHL is a financial holding company and it is a CRR consolidation entity. This Pillar 3 report is prepared on a consolidated basis. Vida Bank Limited ("VBL") is the principal regulated subsidiary of the Group. The same basis of consolidation is used for the preparation of the Group's Annual Report and Accounts as is used for regulatory reporting.' Section 1.2 'Basis of Disclosure' adds, equally verbatim: 'Regulatory ratios are presented on a Group-basis only.' Three consequences follow, and they are why the figures above are kept rather than demoted to memo rows. (1) VGHL is not an incidental parent that merely happens to contain the bank - it is the CRR CONSOLIDATION ENTITY, i.e. the level at which the PRA actually sets and measures Vida's regulatory capital requirement, with VBL as the principal regulated subsidiary. This is the smallest regulatory group VBL belongs to. (2) No VBL-solo ratio exists to prefer over it: 'Group-basis only' is the publisher's own statement that the solo figures are not disclosed anywhere, so the choice is between the consolidated figure and nothing at all - not between a group figure and a suppressed entity figure. (3) The Group and the Annual Report use the same basis of consolidation, so these ratios are reconcilable to the accounts in this workbook rather than sitting on an unrelated perimeter. Accordingly every Pillar 3 sheet in this workbook carries the subtitle 'Vida Group Holdings basis' so the reader is never shown a consolidated ratio labelled as an entity one - the project rule this workbook observes is that group figures are never SUBSTITUTED for entity figures unlabelled, which is a different thing from refusing to report the only regulatory ratio that exists. Note also that both reports are reduced-scope Article 433b disclosures ('small and non-complex institution', UK CRR Article 4(145)), which is why the metric set here is narrower than a large bank's - it is a permitted reduction, not an omission.
+No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.
+RE-VERIFIED 2026-09-12 (disclosure audit): the pre-authorisation gap is STRUCTURAL, independently confirmed against the Companies House register rather than the workbook's own prior claim. Company 09837692 was incorporated 22 October 2015 and traded as 'Belmont Green Finance Ltd' (22 Oct 2015 - 10 Jun 2019) and then 'Belmont Green Finance Limited' (10 Jun 2019 - 25 Nov 2024), only taking the name 'Vida Bank Limited' on 25 November 2024 - six days after the 19 November 2024 PRA authorisation. No Pillar 3 obligation can therefore exist for FY2018-FY2023, so those years are blank by regulation, not by omission.
+SDDT - EXPLICIT NEGATIVE, recorded 2026-09-15 (cross-bank SDDT date-fit pass) so that a future pass does not wrongly apply the Small Domestic Deposit Taker exemption to this workbook's gap years. Vida DOES hold the SDDT opt-in, but it is far too recent to explain anything here. The Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv) carries three SDDT rows for FRN 738741, 'Vida Bank Limited': (a) 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub rule 'Ru 3.1', waiver ref 'A00011924P.pdf', START DATE 03/04/2026, no end date; plus two eligibility-criteria modifications under sub rules 'Ru 1.2' and 'Ru 2.1(9)', both ref 'A00010069P.pdf', start 25/03/2026, end 25/03/2029. Only row (a) matters: Rule 3.1 is the actual opt-in that removes the Pillar 3 disclosure obligation, whereas rules 1.2 and 2.1(9) merely modify eligibility CRITERIA (2.1(9) waives the 'any parent undertaking of the firm is a UK undertaking' test) and are not themselves evidence of any disclosure exemption.
+DATE FIT - IT DOES NOT FIT. Vida's accounting reference date is 31 DECEMBER, confirmed at Companies House (company 09837692, an unbroken run of accounts to 31 December from 2019 to 2025). The outstanding Pillar 3 gap years are FY2021, FY2022 and FY2023, which ended 31 December 2021, 2022 and 2023 respectively. The Rule 3.1 modification began 3 APRIL 2026 - between two and four and a half years AFTER every one of those year-ends, and after the FY2025 year-end too. A modification cannot explain a gap that predates it, so the SDDT regime explains NONE of the FY2021-FY2023 blanks.
+Those gaps already have a different and fully sufficient explanation, set out immediately above, and it is left exactly as it stands: the entity was not PRA-authorised as a deposit-taker until 19 November 2024, so no Pillar 3 obligation existed in any of those years. That is a structural pre-authorisation absence, not an exemption. The register finding changes no cell in this workbook. Its only forward-looking value is that from 3 April 2026 Vida is an SDDT, so Pillar 3 documents of the kind used for FY2024 and FY2025 should not be expected for FY2026 onward. Note finally that this is the SDDT DISCLOSURE exemption, which is in force now - not the separate SDDT CAPITAL regime that begins 1 January 2027; the two are easy to conflate and must not be.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A7:I7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8196,507 +8348,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="72" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Vida Bank Limited — KM1 Key Metrics</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Vida Group Holdings (CRR consolidation entity) basis - the bank's own published UK KM1 table, reproduced whole in its own row order, labels and precision. The bank prints no template row numbers; amounts £'000, ratios as printed. FY2018-FY2023 are blank because no Pillar 3 disclosure of any kind exists for them (pre-authorisation) - see source note.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Available own funds (£'000)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital (£'000)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>168319</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>160316</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 capital (£'000)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>168319</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>160316</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Total capital (£'000)</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>202429</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>160316</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Risk-weighted exposure (£'000)</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Total risk-weighted exposure amount (£'000)</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>1105780</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>986809</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Capital ratios</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 ratio (%)</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>16.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 ratio (%)</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>16.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Total capital ratio (%)</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>18.3%</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>16.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Additional own funds requirements</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Additional own funds requirements (%)</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Total own funds requirements (%)</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>9.2%</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>9.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Combined buffer requirement</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Capital conservation buffer (%)</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Institution specific countercyclical capital buffer (%)</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Combined buffer requirement (%)</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Overall capital requirements (%)</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>13.6%</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>13.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Leverage ratio</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Total exposure measure excluding claims on central banks (£'000)</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n">
-        <v>3440332</v>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>2331835</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Leverage ratio excluding claims on central banks (%)</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>4.9%</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>6.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Liquidity coverage ratio</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Total high-quality liquid assets (HQLA) (weighted value - average) (£'000)</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n">
-        <v>1073005</v>
-      </c>
-      <c r="C26" s="6" t="n">
-        <v>167705</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Cash outflows - total weighted value (£'000)</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n">
-        <v>747252</v>
-      </c>
-      <c r="C27" s="6" t="n">
-        <v>64182</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Cash inflows - total weighted value (£'000)</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n">
-        <v>77815</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>205580</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Total net cash outflows (adjusted value) (£'000)</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n">
-        <v>669438</v>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>16046</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Liquidity coverage ratio (%)</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>163%</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>1,045%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Net stable funding ratio</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="6" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Total available stable funding (£'000)</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n">
-        <v>2377496</v>
-      </c>
-      <c r="C32" s="6" t="n">
-        <v>2016146</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>Total required stable funding (£'000)</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n">
-        <v>1719626</v>
-      </c>
-      <c r="C33" s="6" t="n">
-        <v>1830180</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Net stable funding ratio (%)</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>138%</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>110%</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="409" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Vida's own published UK KM1 'Key metrics' table, reproduced whole in the bank's own row order, row labels and printed precision. Entity/basis: Vida Group Holdings Limited (FY2024 edition) / Vida Group Holdings plc (FY2025 edition) CONSOLIDATED - the CRR consolidation entity, with Vida Bank Limited as its principal regulated subsidiary. Both editions state 'Regulatory ratios are presented on a Group-basis only', so no Vida-Bank-Limited-solo KM1 exists to prefer; this is the same basis every other Pillar 3 sheet in this workbook uses (see the metric sheets' own BASIS DETERMINATION note).
-FY2025: Vida Group Holdings Limited Pillar 3 Disclosures 31 December 2025, section 3.1 'Key Metrics', PRINTED PAGE 5 (the page's own footer reads '5|Page') - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
-FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 31 December 2024, section 3.1 'Key Metrics', PRINTED PAGE 5 (footer '5|Page') - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-Each year is taken from its OWN edition. The FY2025 edition also prints a 31 Dec 2024 comparative column and it agrees with the FY2024 edition digit-for-digit on every one of the 23 rows, so nothing here depends on which edition a FY2024 figure came from.
-COLUMN ORDER: both editions print the OLDER year on the LEFT (the FY2025 edition's header block reads '31 Dec 2024   31 Dec 2025'). This sheet keeps the workbook's standard most-recent-first column order, which reorders columns but not rows - no row, label, figure or precision is altered.
-THE TABLE IS UNNUMBERED, AND IT IS STILL THE TEMPLATE. Vida prints no template row numbers at all (no '1', no 'UK 7a'), but the table carries the UK KM1 row set in template order - available own funds, risk-weighted exposure amount, the three capital ratios, the additional own-funds (SREP) requirement, the combined buffer build-up, leverage, LCR and NSFR - and the bank's own sentence above it names it: 'The key metrics table (KM1) covering capital, leverage and liquidity is set out below.' Both editions are reduced-scope Article 433b disclosures ('small and non-complex institution', UK CRR Article 4(145)), and both say 'Specific rows and columns in the tables prescribed by the PRA have been omitted where these are not applicable to the Group' - so the shorter row set is a permitted reduction of the prescribed template, not a different table and not an omission.
-NO MISSING-VALUE GLYPHS: neither edition prints a dash, an 'n/a' or a zero anywhere in this table. Every row the bank printed carries a figure in every column it printed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="409" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>(continued)
-UNITS: the bank declares £'000 on its own block captions ('Available own funds (£’000)', 'Risk-weighted exposure (£’000)') and again on most individual rows. Each amount row below carries its own '(£'000)' so the unit never has to be inferred from how far a lookup walks. The bank's own table mixes a typewriter apostrophe and a typographic one for the same unit within a single page; the typewriter form is used throughout here, which is a glyph choice in an annotation and changes no wording and no figure.
-FY2018-FY2023 ARE BLANK BECAUSE NO PILLAR 3 DISCLOSURE OF ANY KIND EXISTS FOR THEM, on any basis, in any edition. The entity was not PRA-authorised as a deposit-taker until 19 November 2024, so no Pillar 3 obligation could attach to any earlier year; FY2018-FY2020 it was FCA-regulated only. FY2024 is the first year for which any Pillar 3 document exists, and no later edition prints a pre-FY2024 comparative that could fill those columns. This is a structural pre-authorisation absence, not an exemption - see the ENTITY_NOTE on the Cash Flow Statement sheet and the SDDT date-fit note on the metric sheets, which records that Vida's Rule 3.1 SDDT modification began 3 April 2026 and therefore explains none of these blanks.
-LATEST-EDITION CHECK, 2026-09-17: checked Vida's own site (www.vidabank.co.uk -&gt; About Vida Bank -&gt; Investors -&gt; Debt Investors), not a cached citation list. The newest ANNUAL Pillar 3 is the 31 December 2025 edition used above, and the newest Annual Report is the 2025 Annual Report and Accounts already used throughout this workbook - so no year is missing. The site additionally carries an INTERIM Pillar 3 as at 30 June 2026 (https://www.vidabank.co.uk/media/g1vnsxxu/pillar-3-disclosures-30-june-2026.pdf), published alongside a 30 June 2026 Interim Report. It falls outside this workbook's financial years (Vida's year-end is 31 December) and so adds no column, but its 31 Dec 2025 comparative was read as an independent second transcription of the whole FY2025 column.
-WHAT THAT SECOND OPINION FOUND - RECORDED, NOT RECONCILED. The interim edition reproduces the FY2025 capital and leverage block exactly: CET1 168,319, Tier 1 168,319, Total capital 202,429, RWEA 1,105,780, ratios 15.2% / 15.2% / 18.3%, leverage exposure 3,440,332 and leverage ratio 4.9%. It differs in two places, both of which are the interim edition changing how it MEASURES a row rather than correcting a figure, so the FY2025 column below stays exactly as Vida's own FY2025 edition printed it. (1) The SREP block is presented differently: the FY2025 edition prints one combined 'Additional own funds requirements (%)' of 1.2% and a 9.2% total, while the interim edition splits the same requirement into 'Additional CET1 SREP requirements 0.66% / Additional AT1 SREP requirements 0.22% / Additional T2 SREP requirements 0.30%' with a 9.18% total - the components sum to 1.18%, i.e. the same requirement shown to two decimals instead of one. (2) The LIQUIDITY rows are on a different averaging window. The interim edition footnotes its LCR as 'the simple average of month end observations over the preceding 12 months' and its NSFR as 'the simple average of quarter end observations over the preceding 4 quarter ends', and on that basis restates 31 Dec 2025 to HQLA 612,552 / outflows 330,304 / inflows 101,370 / net outflows 252,077 / LCR 528%, and NSFR 2,327,088 / 1,646,865 / 142%, against the 1,073,005 / 747,252 / 77,815 / 669,438 / 163% and 2,377,496 / 1,719,626 / 138% that the FY2025 annual edition printed for the same date. Two printings of one date on two bases is a documented divergence, not a transcription error in either; each year's own edition governs its own column.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A36:C36"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -8710,14 +8365,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Vida Bank Limited — CET1 Capital</t>
+          <t>Vida Bank Limited — Profitability</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Vida Group Holdings basis, £'000</t>
+          <t>Return on equity and return on assets in per cent, computed from this workbook's own Balance Sheet and Profit &amp; Loss sheets.</t>
         </is>
       </c>
     </row>
@@ -8771,64 +8426,748 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
+          <t>Return on equity - average equity basis</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>7.64%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>4.48%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>4.80%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>1.54%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>3.71%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>-5.30%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>-28.96%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - year-end equity basis</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>7.37%</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>3.90%</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>4.97%</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>1.51%</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>3.68%</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>-5.10%</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>-27.08%</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>-9.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - average assets basis</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>0.47%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>0.33%</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>0.34%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>0.11%</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>0.26%</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>-2.15%</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - year-end assets basis</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>0.31%</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>0.34%</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>0.11%</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>0.25%</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>-0.37%</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>-1.89%</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>-0.72%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Vida Bank Limited's own published return</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="143" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Note: COMPUTED, NOT PUBLISHED. Vida Bank Limited publishes no actual ROE, ROA or RoTE figure in its Annual Report and Accounts 2025 (94 pages, born-digital). Whole-report searches for RoTE, standalone ROE and standalone ROA returned no matches. 'Return on' hits are narrative only: the outlook says Vida will 'drive a higher return on equity' in 2026 and the financial review refers to 'stronger core equity returns'; neither reports a value. The report instead gives PBT GBP12.5m, total income GBP54m and cost:income 74%. Every percentage above is therefore this project's own arithmetic on the figures printed on this workbook's statement sheets, and is labelled as such. That the bank publishes none is a POSITIVE FINDING, recorded in research/profitability/published_returns.jsonl, and not a failed search: for this bank the computed figure is the only figure there is.
+WHY TWO BASES ARE PRINTED FOR EACH RATIO, AND NEITHER IS PREFERRED. The average basis divides by the mean of the opening and closing balance and is the fairer measure of a year in which the balance sheet moved a long way; the year-end basis divides by the closing balance alone and is what most outside sources quote. Both are shown so the reader can see which question a figure answers. They are not averaged and neither is 'the' return. The two diverge most in FY2019, where return on equity is -28.96% on an average basis and -27.08% on a year-end basis.
+FY2018 HAS NO AVERAGE-BASIS RATIO, AND THAT IS CORRECT. An average denominator needs an opening balance, and FY2018 is the oldest column this workbook carries, so there is no prior year to open from. The blank is structural, not a missing figure. The year-end basis is shown for FY2018 because it needs only the closing balance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="170" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Computed by this workbook's own build script from the Profit &amp; Loss and Balance Sheet sheets of this same workbook - the Profit &amp; Loss row “profit for the year” and the Balance Sheet rows “total shareholders' equity” and “total assets”, resolved BY LABEL at build time through the shared resolver scripts/profitability_rows.py, so this sheet cannot drift from the statements it summarises. Those rows are themselves transcribed from Vida Bank Limited's Annual Report and Accounts for each year; see the source cells on the Balance Sheet and Profit &amp; Loss sheets for the exact document, page and table behind every input to every percentage above.
+The finding that Vida Bank Limited publishes no return of its own is recorded in research/profitability/published_returns.jsonl under ‘VIDA’, verified against the bank's own annual report rendered at 300 dpi.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A11:I11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Vida Bank Limited — KM1 Key Metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Vida Group Holdings (CRR consolidation entity) basis - the bank's own published UK KM1 table, reproduced whole in its own row order, labels and precision. The bank prints no template row numbers; amounts £'000, ratios as printed. FY2018-FY2023 are blank because no Pillar 3 disclosure of any kind exists for them (pre-authorisation) - see source note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Available own funds (£'000)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Common Equity Tier 1 (CET1) capital (£'000)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>168319</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C5" s="6" t="n">
         <v>160316</v>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – not a PRA-authorised bank until 19 Nov 2024, so no CRR Pillar 3 duty; FY2019/FY2020 ARs (Companies House 09837692) show the licence application still pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="403" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Vida Group Holdings Limited/plc Pillar 3 disclosures (Table 3.1 KM1 - Key Metrics; the smallest regulatory group Vida Bank Limited is consolidated into - no Vida-Bank-Limited-only Pillar 3 disclosure is separately published):
-FY2025: Vida Group Holdings plc Pillar 3 Disclosures 2025, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
-FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 2024, p.5 (3.1 Key Metrics / Table KM1) - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
-BASIS DETERMINATION, made 2026-09-15 by reading section 1.3 'Scope' of both reports directly (they are word-for-word identical on this point). Verbatim: 'VGHL is a financial holding company and it is a CRR consolidation entity. This Pillar 3 report is prepared on a consolidated basis. Vida Bank Limited ("VBL") is the principal regulated subsidiary of the Group. The same basis of consolidation is used for the preparation of the Group's Annual Report and Accounts as is used for regulatory reporting.' Section 1.2 'Basis of Disclosure' adds, equally verbatim: 'Regulatory ratios are presented on a Group-basis only.' Three consequences follow, and they are why the figures above are kept rather than demoted to memo rows. (1) VGHL is not an incidental parent that merely happens to contain the bank - it is the CRR CONSOLIDATION ENTITY, i.e. the level at which the PRA actually sets and measures Vida's regulatory capital requirement, with VBL as the principal regulated subsidiary. This is the smallest regulatory group VBL belongs to. (2) No VBL-solo ratio exists to prefer over it: 'Group-basis only' is the publisher's own statement that the solo figures are not disclosed anywhere, so the choice is between the consolidated figure and nothing at all - not between a group figure and a suppressed entity figure. (3) The Group and the Annual Report use the same basis of consolidation, so these ratios are reconcilable to the accounts in this workbook rather than sitting on an unrelated perimeter. Accordingly every Pillar 3 sheet in this workbook carries the subtitle 'Vida Group Holdings basis' so the reader is never shown a consolidated ratio labelled as an entity one - the project rule this workbook observes is that group figures are never SUBSTITUTED for entity figures unlabelled, which is a different thing from refusing to report the only regulatory ratio that exists. Note also that both reports are reduced-scope Article 433b disclosures ('small and non-complex institution', UK CRR Article 4(145)), which is why the metric set here is narrower than a large bank's - it is a permitted reduction, not an omission.
-No Pillar 3 disclosure exists for FY2018-FY2023: Pillar 3 only applies once PRA-authorised as a deposit-taker, which happened 19 November 2024 (see ENTITY_NOTE on the Cash Flow Statement sheet). FY2018-FY2020 the company was FCA-regulated only (not PRA-authorised at all, no banking licence); its FY2019 and FY2020 Annual Reports confirm the banking licence application was still in progress/delayed those years.
-RE-VERIFIED 2026-09-12 (disclosure audit): the pre-authorisation gap is STRUCTURAL, independently confirmed against the Companies House register rather than the workbook's own prior claim. Company 09837692 was incorporated 22 October 2015 and traded as 'Belmont Green Finance Ltd' (22 Oct 2015 - 10 Jun 2019) and then 'Belmont Green Finance Limited' (10 Jun 2019 - 25 Nov 2024), only taking the name 'Vida Bank Limited' on 25 November 2024 - six days after the 19 November 2024 PRA authorisation. No Pillar 3 obligation can therefore exist for FY2018-FY2023, so those years are blank by regulation, not by omission.
-SDDT - EXPLICIT NEGATIVE, recorded 2026-09-15 (cross-bank SDDT date-fit pass) so that a future pass does not wrongly apply the Small Domestic Deposit Taker exemption to this workbook's gap years. Vida DOES hold the SDDT opt-in, but it is far too recent to explain anything here. The Bank of England consolidated list of waivers and modifications granted to PRA-authorised firms (downloaded 2026-09-15, https://www.bankofengland.co.uk/-/media/boe/files/prudential-regulation/authorisations/waivers-and-modifications-of-rules/consolidated-waivers-pra-firms.csv) carries three SDDT rows for FRN 738741, 'Vida Bank Limited': (a) 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub rule 'Ru 3.1', waiver ref 'A00011924P.pdf', START DATE 03/04/2026, no end date; plus two eligibility-criteria modifications under sub rules 'Ru 1.2' and 'Ru 2.1(9)', both ref 'A00010069P.pdf', start 25/03/2026, end 25/03/2029. Only row (a) matters: Rule 3.1 is the actual opt-in that removes the Pillar 3 disclosure obligation, whereas rules 1.2 and 2.1(9) merely modify eligibility CRITERIA (2.1(9) waives the 'any parent undertaking of the firm is a UK undertaking' test) and are not themselves evidence of any disclosure exemption.
-DATE FIT - IT DOES NOT FIT. Vida's accounting reference date is 31 DECEMBER, confirmed at Companies House (company 09837692, an unbroken run of accounts to 31 December from 2019 to 2025). The outstanding Pillar 3 gap years are FY2021, FY2022 and FY2023, which ended 31 December 2021, 2022 and 2023 respectively. The Rule 3.1 modification began 3 APRIL 2026 - between two and four and a half years AFTER every one of those year-ends, and after the FY2025 year-end too. A modification cannot explain a gap that predates it, so the SDDT regime explains NONE of the FY2021-FY2023 blanks.
-Those gaps already have a different and fully sufficient explanation, set out immediately above, and it is left exactly as it stands: the entity was not PRA-authorised as a deposit-taker until 19 November 2024, so no Pillar 3 obligation existed in any of those years. That is a structural pre-authorisation absence, not an exemption. The register finding changes no cell in this workbook. Its only forward-looking value is that from 3 April 2026 Vida is an SDDT, so Pillar 3 documents of the kind used for FY2024 and FY2025 should not be expected for FY2026 onward. Note finally that this is the SDDT DISCLOSURE exemption, which is in force now - not the separate SDDT CAPITAL regime that begins 1 January 2027; the two are easy to conflate and must not be.</t>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 capital (£'000)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>168319</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>160316</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Total capital (£'000)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>202429</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>160316</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Risk-weighted exposure (£'000)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount (£'000)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>1105780</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>986809</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Capital ratios</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Common Equity Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>16.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>16.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Total capital ratio (%)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>18.3%</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>16.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Additional own funds requirements</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Additional own funds requirements (%)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Total own funds requirements (%)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>9.2%</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>9.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Combined buffer requirement</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Capital conservation buffer (%)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Institution specific countercyclical capital buffer (%)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Combined buffer requirement (%)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Overall capital requirements (%)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>13.6%</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>13.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Leverage ratio</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Total exposure measure excluding claims on central banks (£'000)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>3440332</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>2331835</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Leverage ratio excluding claims on central banks (%)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>4.9%</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>6.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Liquidity coverage ratio</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Total high-quality liquid assets (HQLA) (weighted value - average) (£'000)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>1073005</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>167705</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Cash outflows - total weighted value (£'000)</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>747252</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>64182</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Cash inflows - total weighted value (£'000)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>77815</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>205580</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Total net cash outflows (adjusted value) (£'000)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>669438</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>16046</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Liquidity coverage ratio (%)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>163%</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>1,045%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Net stable funding ratio</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Total available stable funding (£'000)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>2377496</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>2016146</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Total required stable funding (£'000)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>1719626</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>1830180</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Net stable funding ratio (%)</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>138%</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>110%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="409" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Vida's own published UK KM1 'Key metrics' table, reproduced whole in the bank's own row order, row labels and printed precision. Entity/basis: Vida Group Holdings Limited (FY2024 edition) / Vida Group Holdings plc (FY2025 edition) CONSOLIDATED - the CRR consolidation entity, with Vida Bank Limited as its principal regulated subsidiary. Both editions state 'Regulatory ratios are presented on a Group-basis only', so no Vida-Bank-Limited-solo KM1 exists to prefer; this is the same basis every other Pillar 3 sheet in this workbook uses (see the metric sheets' own BASIS DETERMINATION note).
+FY2025: Vida Group Holdings Limited Pillar 3 Disclosures 31 December 2025, section 3.1 'Key Metrics', PRINTED PAGE 5 (the page's own footer reads '5|Page') - https://www.vidabank.co.uk/media/od2lpxc0/vghl-pillar-3-report-2025-final.pdf
+FY2024: Vida Group Holdings Limited Pillar 3 Disclosures 31 December 2024, section 3.1 'Key Metrics', PRINTED PAGE 5 (footer '5|Page') - https://www.vidabank.co.uk/media/mucbqgwi/vghl-pillar-3-report-2024-final.pdf
+Each year is taken from its OWN edition. The FY2025 edition also prints a 31 Dec 2024 comparative column and it agrees with the FY2024 edition digit-for-digit on every one of the 23 rows, so nothing here depends on which edition a FY2024 figure came from.
+COLUMN ORDER: both editions print the OLDER year on the LEFT (the FY2025 edition's header block reads '31 Dec 2024   31 Dec 2025'). This sheet keeps the workbook's standard most-recent-first column order, which reorders columns but not rows - no row, label, figure or precision is altered.
+THE TABLE IS UNNUMBERED, AND IT IS STILL THE TEMPLATE. Vida prints no template row numbers at all (no '1', no 'UK 7a'), but the table carries the UK KM1 row set in template order - available own funds, risk-weighted exposure amount, the three capital ratios, the additional own-funds (SREP) requirement, the combined buffer build-up, leverage, LCR and NSFR - and the bank's own sentence above it names it: 'The key metrics table (KM1) covering capital, leverage and liquidity is set out below.' Both editions are reduced-scope Article 433b disclosures ('small and non-complex institution', UK CRR Article 4(145)), and both say 'Specific rows and columns in the tables prescribed by the PRA have been omitted where these are not applicable to the Group' - so the shorter row set is a permitted reduction of the prescribed template, not a different table and not an omission.
+NO MISSING-VALUE GLYPHS: neither edition prints a dash, an 'n/a' or a zero anywhere in this table. Every row the bank printed carries a figure in every column it printed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="409" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+UNITS: the bank declares £'000 on its own block captions ('Available own funds (£’000)', 'Risk-weighted exposure (£’000)') and again on most individual rows. Each amount row below carries its own '(£'000)' so the unit never has to be inferred from how far a lookup walks. The bank's own table mixes a typewriter apostrophe and a typographic one for the same unit within a single page; the typewriter form is used throughout here, which is a glyph choice in an annotation and changes no wording and no figure.
+FY2018-FY2023 ARE BLANK BECAUSE NO PILLAR 3 DISCLOSURE OF ANY KIND EXISTS FOR THEM, on any basis, in any edition. The entity was not PRA-authorised as a deposit-taker until 19 November 2024, so no Pillar 3 obligation could attach to any earlier year; FY2018-FY2020 it was FCA-regulated only. FY2024 is the first year for which any Pillar 3 document exists, and no later edition prints a pre-FY2024 comparative that could fill those columns. This is a structural pre-authorisation absence, not an exemption - see the ENTITY_NOTE on the Cash Flow Statement sheet and the SDDT date-fit note on the metric sheets, which records that Vida's Rule 3.1 SDDT modification began 3 April 2026 and therefore explains none of these blanks.
+LATEST-EDITION CHECK, 2026-09-17: checked Vida's own site (www.vidabank.co.uk -&gt; About Vida Bank -&gt; Investors -&gt; Debt Investors), not a cached citation list. The newest ANNUAL Pillar 3 is the 31 December 2025 edition used above, and the newest Annual Report is the 2025 Annual Report and Accounts already used throughout this workbook - so no year is missing. The site additionally carries an INTERIM Pillar 3 as at 30 June 2026 (https://www.vidabank.co.uk/media/g1vnsxxu/pillar-3-disclosures-30-june-2026.pdf), published alongside a 30 June 2026 Interim Report. It falls outside this workbook's financial years (Vida's year-end is 31 December) and so adds no column, but its 31 Dec 2025 comparative was read as an independent second transcription of the whole FY2025 column.
+WHAT THAT SECOND OPINION FOUND - RECORDED, NOT RECONCILED. The interim edition reproduces the FY2025 capital and leverage block exactly: CET1 168,319, Tier 1 168,319, Total capital 202,429, RWEA 1,105,780, ratios 15.2% / 15.2% / 18.3%, leverage exposure 3,440,332 and leverage ratio 4.9%. It differs in two places, both of which are the interim edition changing how it MEASURES a row rather than correcting a figure, so the FY2025 column below stays exactly as Vida's own FY2025 edition printed it. (1) The SREP block is presented differently: the FY2025 edition prints one combined 'Additional own funds requirements (%)' of 1.2% and a 9.2% total, while the interim edition splits the same requirement into 'Additional CET1 SREP requirements 0.66% / Additional AT1 SREP requirements 0.22% / Additional T2 SREP requirements 0.30%' with a 9.18% total - the components sum to 1.18%, i.e. the same requirement shown to two decimals instead of one. (2) The LIQUIDITY rows are on a different averaging window. The interim edition footnotes its LCR as 'the simple average of month end observations over the preceding 12 months' and its NSFR as 'the simple average of quarter end observations over the preceding 4 quarter ends', and on that basis restates 31 Dec 2025 to HQLA 612,552 / outflows 330,304 / inflows 101,370 / net outflows 252,077 / LCR 528%, and NSFR 2,327,088 / 1,646,865 / 142%, against the 1,073,005 / 747,252 / 77,815 / 669,438 / 163% and 2,377,496 / 1,719,626 / 138% that the FY2025 annual edition printed for the same date. Two printings of one date on two bases is a documented divergence, not a transcription error in either; each year's own edition governs its own column.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:I6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8857,14 +9196,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Vida Bank Limited — CET1 Ratio</t>
+          <t>Vida Bank Limited — CET1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Vida Group Holdings basis, % of RWA</t>
+          <t>Vida Group Holdings basis, £'000</t>
         </is>
       </c>
     </row>
@@ -8918,18 +9257,14 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Common Equity Tier 1 (CET1) ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>16.2%</t>
-        </is>
+          <t>Common Equity Tier 1 (CET1) capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>168319</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>160316</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
